--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_整合測試計畫.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_整合測試計畫.xlsx
@@ -47,7 +47,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'附錄B 規格完整'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'附錄C 測試分析'!$A$4:$G$26</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'附錄C 測試分析'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'元件標籤字典'!$A$4:$H$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'元件標籤字典'!$A$4:$I$105</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'元件標籤字典'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -1024,21 +1024,21 @@
       <c r="G5" s="13" t="inlineStr">
         <is>
           <t>環境：SIT LINE 測試頻道、對應品牌與可查詢後台案件的帳號。
-正常資料：有效簽章的短文字、照片與超過 4900 字訊息，另準備同內容的錯誤簽章版本。
+正常資料：有效簽章的短文字、照片與超過 4900 字訊息；Chatlock/其他品牌各一組拍照引導；另備錯誤簽章與未知 photo-guide key。
 反例資料：錯誤簽章、同一事件重送、急件、知識庫找不到答案的問題與另一品牌/客戶資料（依本項擇用）。</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
           <t>1. 記錄操作前的資料/畫面狀態。
-2. 執行正常流程：分別送出有效短文字、照片、超長文字與錯誤簽章請求，再重送同一事件。
+2. 執行正常流程：送出文字、照片、超長文字、兩品牌拍照引導與錯誤簽章，再重送同一事件並測未知/殘缺 guide marker。
 3. 每次只更改一個邊界、權限、重送或故障條件後重跑。
 4. 比對每次操作後的畫面/API、資料與稽核紀錄。</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>功能判準：有效文字/照片皆有明確回覆；超長內容截斷至 4900 字以內；錯誤簽章回 400 且不產生處理紀錄。
+          <t>功能判準：有效文字/照片皆有明確回覆；只有 Chatlock 附核准樣本圖，其他品牌純文字；未知標記不外洩；超長內容截斷至 4900 字內；錯誤簽章回 400 且不產生處理紀錄。
 副作用判準：被拒絕或重送時不得多出回覆、問題卡、轉人紀錄或跨客戶記憶。</t>
         </is>
       </c>
@@ -1190,21 +1190,21 @@
       <c r="G7" s="13" t="inlineStr">
         <is>
           <t>環境：SIT LINE 測試頻道、對應品牌與可查詢後台案件的帳號。
-正常資料：一題案例庫可明確命中、一題需查知識庫、一題無法回答，並準備「已釐清/尚未釐清」回覆。
+正常資料：一題可明確回答、一題缺兩個必要欄位；另備明確要求真人、急迫派工、金錢詢問、連續兩次不滿，以及一般補資料/單次不滿反例。
 反例資料：錯誤簽章、同一事件重送、急件、知識庫找不到答案的問題與另一品牌/客戶資料（依本項擇用）。</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
           <t>1. 記錄操作前的資料/畫面狀態。
-2. 執行正常流程：逐題提問並檢查系統來源；對無法回答的題目連續 3 次回覆「尚未釐清」。
+2. 執行正常流程：先驗證缺項是否一次列齊，再逐一送出四種轉真人不可違反條件與三種非觸發反例，不使用固定追問輪數。
 3. 每次只更改一個邊界、權限、重送或故障條件後重跑。
 4. 比對每次操作後的畫面/API、資料與稽核紀錄。</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
-          <t>功能判準：案例庫命中與知識庫回答來源正確；系統會詢問是否已釐清；第 3 次未釐清後建立後台案件並轉真人。
+          <t>功能判準：回答來源正確；缺項一次列齊；四種不可違反條件一命中即建立後台案件並轉真人；一般補資料、單次不滿與可回答問題不得因輪數誤轉。
 副作用判準：被拒絕或重送時不得多出回覆、問題卡、轉人紀錄或跨客戶記憶。</t>
         </is>
       </c>
@@ -1771,21 +1771,21 @@
       <c r="G14" s="14" t="inlineStr">
         <is>
           <t>環境：SIT LINE 測試頻道、對應品牌與可查詢後台案件的帳號。
-正常資料：1.5 秒內連發 3 則訊息、1.5 秒後的第 4 則訊息，以及同一事件 ID 的重送請求。
+正常資料：5.0 秒內連發 3 則訊息、視窗後的第 4 則訊息，以及同一 webhook event ID 的重送請求。
 反例資料：錯誤簽章、同一事件重送、急件、知識庫找不到答案的問題與另一品牌/客戶資料（依本項擇用）。</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
           <t>1. 記錄操作前的資料/畫面狀態。
-2. 執行正常流程：依時間間隔送出四則訊息，再於 24 小時內重送同一事件 ID。
+2. 執行正常流程：依時間間隔送出四則訊息，再重送同一 event ID 並模擬第一次處理失敗。
 3. 每次只更改一個邊界、權限、重送或故障條件後重跑。
 4. 比對每次操作後的畫面/API、資料與稽核紀錄。</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>功能判準：1.5 秒內的三則訊息合併為一次處理；第四則另開一次處理；24 小時內重送不產生第二次回覆或案件。
+          <t>功能判準：5.0 秒內的三則訊息合併為一次處理；第四則另開一次處理；reserve-first 永久主鍵使重送不產生第二次回覆或案件。
 副作用判準：被拒絕或重送時不得多出回覆、問題卡、轉人紀錄或跨客戶記憶。</t>
         </is>
       </c>
@@ -1937,21 +1937,21 @@
       <c r="G16" s="14" t="inlineStr">
         <is>
           <t>環境：SIT API、可查詢操作前後狀態的資料庫/稽核紀錄與外部服務替身。
-正常資料：agent ingest 或客服建卡。
+正常資料：同一對話近 24 小時有 7 張照片、窗外 1 張，另備重送與媒體反查失敗情境。
 反例資料：非法狀態、門檻前/等於/後數值、同一請求重送、無權角色與逾時（依本項擇用）。</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
           <t>1. 記錄操作前的資料/畫面狀態。
-2. 執行正常流程：AI 草擬卡（source='ai_line'）→ 客服補全 → 資料完整度 ≥ 0.85 confirmed。
+2. 執行正常流程：由對話建立 AI 草擬問題卡，再重送相同建卡請求並模擬媒體查詢失敗。
 3. 每次只更改一個邊界、權限、重送或故障條件後重跑。
 4. 比對每次操作後的畫面/API、資料與稽核紀錄。</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>功能判準：AI 不得自行建立工單；confirm/convert 走客服認證端點。
+          <t>功能判準：只附同對話近 24 小時最多 5 張照片且時間正序、append-only；重送不重複建卡，照片旁路失敗不阻斷主要流程程。
 副作用判準：被拒絕或重送時不得多出狀態變更、事件、帳本或重複稽核紀錄。</t>
         </is>
       </c>
@@ -2020,21 +2020,21 @@
       <c r="G17" s="13" t="inlineStr">
         <is>
           <t>環境：SIT API、可查詢操作前後狀態的資料庫/稽核紀錄與外部服務替身。
-正常資料：PC confirmed。
+正常資料：customer_sent、已同意、已拒絕、已過期、找不到與無權報價各一。
 反例資料：非法狀態、門檻前/等於/後數值、同一請求重送、無權角色與逾時（依本項擇用）。</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
           <t>1. 記錄操作前的資料/畫面狀態。
-2. 執行正常流程：draft → internal_approved → customer_sent（POST /quotes/{id}:send-to-customer）→ LIFF customer-confirm（Idempotency-Key + confirm_token TTL=48h）。
+2. 執行正常流程：送同決定重播、相反決定、過期、404、403 與非 JSON 錯誤，核對 API 與 LINE。
 3. 每次只更改一個邊界、權限、重送或故障條件後重跑。
 4. 比對每次操作後的畫面/API、資料與稽核紀錄。</t>
         </is>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
-          <t>功能判準：sender_role=ai_agent AND case_type∈{warranty,project} → 403 AI_FORBIDDEN_WARRANTY_PROJECT；quote 內外雙視圖（客戶端不含成本欄）。
+          <t>功能判準：同決定安全回放；相反終態回 QUOTE_ALREADY_DECIDED、過期回 QUOTE_EXPIRED；LINE 依 error_code 分流，未知格式友善降級。
 副作用判準：被拒絕或重送時不得多出狀態變更、事件、帳本或重複稽核紀錄。</t>
         </is>
       </c>
@@ -2186,21 +2186,21 @@
       <c r="G19" s="13" t="inlineStr">
         <is>
           <t>環境：SIT API、可查詢操作前後狀態的資料庫/稽核紀錄與外部服務替身。
-正常資料：Quote.customer_confirmed 或急件。
+正常資料：問題卡含客戶姓名、電話、地址、品牌、型號、serial 與照片，報價已確認。
 反例資料：非法狀態、門檻前/等於/後數值、同一請求重送、無權角色與逾時（依本項擇用）。</t>
         </is>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
           <t>1. 記錄操作前的資料/畫面狀態。
-2. 執行正常流程：工單 Tool draft → CS 1-click → created（§2.2.4 阻擋條件）。
+2. 執行正常流程：客服將問題卡轉為工單，再以相同冪等鍵重送。
 3. 每次只更改一個邊界、權限、重送或故障條件後重跑。
 4. 比對每次操作後的畫面/API、資料與稽核紀錄。</t>
         </is>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
-          <t>功能判準：create_trigger 記錄 AI/CS 路徑；idempotency_key 防重。
+          <t>功能判準：工單完整承接問題卡欄位含 serial；只有客服操作可開單；重送不新增第二張工單。
 副作用判準：被拒絕或重送時不得多出狀態變更、事件、帳本或重複稽核紀錄。</t>
         </is>
       </c>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>功能判準：一般通知送達 P95 ≤ 30 秒、急件 P95 ≤ 15 秒；候選池為空時 100% 進入 dispatch_pending 並觸發警示；急件排序降低距離權重、提高評分權重。。
+          <t>功能判準：一般通知送達 P95 ≤ 30 秒、急件 P95 ≤ 15 秒；候選池為空時 100% 進入 dispatch_pending 並觸發警示；急件排序降低距離權重、提高評分權重。
 副作用判準：被拒絕或重送時不得多出狀態變更、事件、帳本或重複稽核紀錄。</t>
         </is>
       </c>
@@ -2518,21 +2518,21 @@
       <c r="G23" s="13" t="inlineStr">
         <is>
           <t>環境：SIT API、可查詢操作前後狀態的資料庫/稽核紀錄與外部服務替身。
-正常資料：WO in_progress。
+正常資料：有/無 LINE 綁定工單、三段 consent、不同租戶/角色與有效/無效 public token。
 反例資料：非法狀態、門檻前/等於/後數值、同一請求重送、無權角色與逾時（依本項擇用）。</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
           <t>1. 記錄操作前的資料/畫面狀態。
-2. 執行正常流程：到場證明、施工照上傳（Evidence sha256 主鍵 + envelope 加密）、材料登錄（主鎖 + &gt;1000 零件強制 serial）、客戶簽名。
+2. 執行正常流程：上傳證據並發送簽署連結；重送、跨租戶/越權，再以 public token 完成同意。
 3. 每次只更改一個邊界、權限、重送或故障條件後重跑。
 4. 比對每次操作後的畫面/API、資料與稽核紀錄。</t>
         </is>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
-          <t>功能判準：結案前證據齊備檢核；scope change 走 §2.2.5 分層。
+          <t>功能判準：有 LINE 時推播、無 LINE 時回可複製連結；重送安全、越權拒絕；token 只存 hash，三段同意正確 upsert 並受結案 gate 檢查。
 副作用判準：被拒絕或重送時不得多出狀態變更、事件、帳本或重複稽核紀錄。</t>
         </is>
       </c>
@@ -3680,21 +3680,21 @@
       <c r="G37" s="13" t="inlineStr">
         <is>
           <t>環境：SIT 前後端、各站點模式與可切換權限的測試帳號。
-正常資料：派工小編登入。
+正常資料：對話、問題卡與工單含需認證照片；時間軸含有姓名與無姓名技師。
 反例資料：無權角色、錯站點模式、403、斷網、即時連線中斷與鍵盤操作（依本項擇用）。</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
           <t>1. 記錄操作前的資料/畫面狀態。
-2. 執行正常流程：工單看板 / 派工佇列 / 即時即時連線訂閱（斷線 backoff 重連、未設定靜默降級不阻塞頁面）。
+2. 執行正常流程：開縮圖/lightbox、注入 401/403，再核對技師名稱與 accepted_at。
 3. 每次只更改一個邊界、權限、重送或故障條件後重跑。
 4. 比對每次操作後的畫面/API、資料與稽核紀錄。</t>
         </is>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>功能判準：即時降級 100% 不當機。
+          <t>功能判準：授權 fetch→Blob 正常顯示且可關閉/revoke；錯誤只顯示佔位不崩潰；姓名與時間軸資料正確，缺名走明確備援處理。
 副作用判準：畫面不得顯示假成功；後端未成功時資料不得變更。</t>
         </is>
       </c>
@@ -3929,21 +3929,21 @@
       <c r="G40" s="14" t="inlineStr">
         <is>
           <t>環境：SIT 前後端、各站點模式與可切換權限的測試帳號。
-正常資料：line_binding 有效。
+正常資料：有/無 LINE 綁定工單、三段免責狀態與有效/過期 token。
 反例資料：無權角色、錯站點模式、403、斷網、即時連線中斷與鍵盤操作（依本項擇用）。</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
           <t>1. 記錄操作前的資料/畫面狀態。
-2. 執行正常流程：報價明細 + 條款 progressive disclosure + 確認 checkbox；工單進度追蹤。
+2. 執行正常流程：從工作台發送或複製連結，客戶開啟公開頁並提交三段同意。
 3. 每次只更改一個邊界、權限、重送或故障條件後重跑。
 4. 比對每次操作後的畫面/API、資料與稽核紀錄。</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>功能判準：customer_consent_method 區分 liff_full / flex_simple_fallback。
+          <t>功能判準：兩種交付路徑都可完成同意；過期/錯誤 token 顯示明確錯誤；畫面不暴露 token hash 或非必要個資。
 副作用判準：畫面不得顯示假成功；後端未成功時資料不得變更。</t>
         </is>
       </c>
@@ -4012,21 +4012,21 @@
       <c r="G41" s="13" t="inlineStr">
         <is>
           <t>環境：SIT 前後端、各站點模式與可切換權限的測試帳號。
-正常資料：建立可完成「錯誤 / 離線頁」的正常資料。
+正常資料：主要 API/網路/頁面錯誤，以及受保護媒體 401/403。
 反例資料：無權角色、錯站點模式、403、斷網、即時連線中斷與鍵盤操作（依本項擇用）。</t>
         </is>
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
           <t>1. 記錄操作前的資料/畫面狀態。
-2. 執行正常流程：全域 error boundary + 離線提示。
+2. 執行正常流程：逐一注入錯誤並操作重試、回傳與照片預覽。
 3. 每次只更改一個邊界、權限、重送或故障條件後重跑。
 4. 比對每次操作後的畫面/API、資料與稽核紀錄。</t>
         </is>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
-          <t>功能判準：任何 API 失敗有友善 UI。
+          <t>功能判準：每種錯誤都有可理解提示與下一步；照片失敗顯示佔位，任何單點錯誤都不造成整站崩潰或假成功。
 副作用判準：畫面不得顯示假成功；後端未成功時資料不得變更。</t>
         </is>
       </c>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>功能判準：主通道採唯讀 API 增量汲取，事件處理即時增量，每日批次 reconciliation 補齊遺漏資料；來源來源追溯資料完整率 100%，同一 source_id 重跑不得產生重複資料。。
+          <t>功能判準：主通道採唯讀 API 增量汲取，事件處理即時增量，每日批次 reconciliation 補齊遺漏資料；來源追溯資料完整率 100%，同一 source_id 重跑不得產生重複資料。
 副作用判準：未核可、拒絕、錯來源或錯租戶內容寫入筆數必須為 0。</t>
         </is>
       </c>
@@ -6426,7 +6426,7 @@
       <c r="H70" s="14" t="inlineStr">
         <is>
           <t>1. 先跑一次可重現的基準並保存原始值。
-2. 執行文件指定驗證：k6 50 位並行使用者、15 分鐘穩定負載；輸出 p95/p99、錯誤率與逾時分布。
+2. 執行文件指定驗證：k6 load 50 位並行使用者（實測依本表受控判準）。
 3. 增加邊界、拒絕或故障情境後重跑。
 4. 將每次實測值與目標逐項比對，超出目標即失敗。</t>
         </is>
@@ -6754,14 +6754,14 @@
       <c r="H74" s="14" t="inlineStr">
         <is>
           <t>1. 先跑一次可重現的基準並保存原始值。
-2. 執行文件指定驗證：k6 + APM（SigNoz），依端點輸出 latency/error 分布。
+2. 執行文件指定驗證：APM（SigNoz）。
 3. 增加邊界、拒絕或故障情境後重跑。
 4. 將每次實測值與目標逐項比對，超出目標即失敗。</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>通過標準：p95 &lt; 300ms；50 位並行使用者、15 分鐘穩定負載，錯誤率 &lt; 1%。</t>
+          <t>通過標準：p95 &lt; 300ms；本次為受控設計門檻，必須保存實測報表後才可標示通過。</t>
         </is>
       </c>
       <c r="J74" s="14" t="inlineStr">
@@ -6918,14 +6918,14 @@
       <c r="H76" s="14" t="inlineStr">
         <is>
           <t>1. 先跑一次可重現的基準並保存原始值。
-2. 執行文件指定驗證：k6 + read replica 路由驗證；保存資料集版本與查詢計畫。
+2. 執行文件指定驗證：k6 + read replica 路由驗證。
 3. 增加邊界、拒絕或故障情境後重跑。
 4. 將每次實測值與目標逐項比對，超出目標即失敗。</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>通過標準：p95 &lt; 300ms；10,000 筆技師基準資料、50 位並行使用者、15 分鐘穩定負載，錯誤率 &lt; 1%。</t>
+          <t>通過標準：POST /technicians:match p95 &lt; 300ms；本次為受控設計門檻，必須保存讀取路由與實測報表後才可標示通過。</t>
         </is>
       </c>
       <c r="J76" s="14" t="inlineStr">
@@ -7246,14 +7246,14 @@
       <c r="H80" s="14" t="inlineStr">
         <is>
           <t>1. 先跑一次可重現的基準並保存原始值。
-2. 執行文件指定驗證：Lighthouse CI + RUM P75 交叉驗證。
+2. 執行文件指定驗證：Lighthouse / RUM。
 3. 增加邊界、拒絕或故障情境後重跑。
 4. 將每次實測值與目標逐項比對，超出目標即失敗。</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>通過標準：≤ 3s；Lighthouse mobile / Fast 4G / 4× CPU slowdown，5 次測試中位數。</t>
+          <t>通過標準：web 首次內容繪製 FCP ≤ 3s；以各站 Lighthouse 或 RUM 結果逐站裁定。</t>
         </is>
       </c>
       <c r="J80" s="14" t="inlineStr">
@@ -10280,14 +10280,14 @@
       <c r="H117" s="13" t="inlineStr">
         <is>
           <t>1. 先跑一次可重現的基準並保存原始值。
-2. 執行文件指定驗證：正常、錯 issuer、錯 audience、過期、撤銷五類整合測試。
+2. 執行文件指定驗證：整合測試。
 3. 增加邊界、拒絕或故障情境後重跑。
 4. 將每次實測值與目標逐項比對，超出目標即失敗。</t>
         </is>
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
-          <t>通過標準：agent → api X-Internal-Token（api 側驗證失敗時一律拒絕、常數時間比對）；品牌 api → 技師媒合服務採 Casdoor 登入憑證 OAuth 2.0 client_credentials，JWT 必驗 issuer/audience/expiry，無效或過期憑證 100% 回 401。</t>
+          <t>通過標準：agent → api 使用 X-Internal-Token，驗證失敗即拒絕且採常數時間比對；品牌 api → OHS 仍屬 TO-BE，服務憑證機制未經 ADR 定版與負向測試前，本項只能標示阻擋，不得標示通過。</t>
         </is>
       </c>
       <c r="J117" s="13" t="inlineStr">
@@ -12658,14 +12658,14 @@
       <c r="H146" s="14" t="inlineStr">
         <is>
           <t>1. 先跑一次可重現的基準並保存原始值。
-2. 執行文件指定驗證：依風險分層抽樣人工審核 + 發布阻擋條件報表。
+2. 執行文件指定驗證：抽樣人工審核。
 3. 增加邊界、拒絕或故障情境後重跑。
 4. 將每次實測值與目標逐項比對，超出目標即失敗。</t>
         </is>
       </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>通過標準：上線候選內容 100% 經人工審核；每版不足 100 筆時全驗，否則至少抽驗 100 筆且不低於該版 10%；一般內容誤放率 ≤ 1%，高風險內容誤放 1 筆即阻擋發布。</t>
+          <t>通過標準：每次發布須保存人工審核筆數、核可通過率與抽樣誤放率；Data 負責人尚未核定數值門檻前，本項只能標示阻擋，不得標示通過。</t>
         </is>
       </c>
       <c r="J146" s="14" t="inlineStr">
@@ -13396,14 +13396,14 @@
       <c r="H155" s="13" t="inlineStr">
         <is>
           <t>1. 先跑一次可重現的基準並保存原始值。
-2. 執行文件指定驗證：每季按來源類型抽 10 筆從 raw 重建 bronze，hash/來源追溯資料 100% 一致。
+2. 執行文件指定驗證：保存位置文件化。
 3. 增加邊界、拒絕或故障情境後重跑。
 4. 將每次實測值與目標逐項比對，超出目標即失敗。</t>
         </is>
       </c>
       <c r="I155" s="13" t="inlineStr">
         <is>
-          <t>通過標準：原始資產 100% 原樣落 raw object storage，保存 content hash、source URI、acquired_at；至少保留 1 年或至衍生 bronze 退役（取較長者）。</t>
+          <t>通過標準：raw 原始資產須有核准的保存位置、期限、不可變性與刪除例外規則；四項任一未定版即阻擋 raw → bronze 可重建驗收。</t>
         </is>
       </c>
       <c r="J155" s="13" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="C163" s="13" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D163" s="13" t="inlineStr">
@@ -14052,14 +14052,14 @@
       <c r="H163" s="13" t="inlineStr">
         <is>
           <t>1. 先跑一次可重現的基準並保存原始值。
-2. 執行文件指定驗證：E2E CI；任一關鍵流失敗即阻擋 RC。
+2. 執行文件指定驗證：E2E CI。
 3. 增加邊界、拒絕或故障情境後重跑。
 4. 將每次實測值與目標逐項比對，超出目標即失敗。</t>
         </is>
       </c>
       <c r="I163" s="13" t="inlineStr">
         <is>
-          <t>通過標準：每個 RC 以 Playwright 100% 涵蓋九條關鍵流：LINE 建案、報價同意、付款、派工時限目標、技師接拒單/到場/現場重新報價、結算退款、跨租戶拒絕、知識人工審核發布、租戶開站/使用授權。</t>
+          <t>通過標準：Playwright 至少涵蓋登入、品牌後台關鍵頁、問題卡／工單主要流程、錯誤回復及技師接案→到場→完工；CI 任一關鍵案例失敗即阻擋發布。</t>
         </is>
       </c>
       <c r="J163" s="13" t="inlineStr">
@@ -15416,22 +15416,22 @@
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>QTM-FR-AGT-01 → 指定 TC：TC-CS-AI-01/02</t>
+          <t>QTM-FR-AGT-01 → 指定 TC：TC-CS-AI-01/02/11</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>line_gateway; AgentLoop; AgentRunner</t>
+          <t>line_gateway; Photo Guide resolver; Quote postback message mapper; WebhookIdempotencyStore; AgentLoop; AgentRunner</t>
         </is>
       </c>
       <c r="J5" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L138–149</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K5" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
     </row>
@@ -15478,17 +15478,17 @@
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>line_gateway; AgentLoop; AgentRunner</t>
+          <t>line_gateway; Photo Guide resolver; Quote postback message mapper; WebhookIdempotencyStore; AgentLoop; AgentRunner</t>
         </is>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L138–149</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K6" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>已釐清寫 clarification_confirmed_at；連續 3 次未釐清升級轉真人</t>
+          <t>缺項依情境一次列齊；明確要求真人、急迫派工、金錢相關或連續兩次不滿時立即轉真人；一般補資料、單次不滿或可回答知識題不得因固定輪數誤轉。</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -15530,22 +15530,22 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>QTM-FR-AGT-03 → 指定 TC：TC-CS-AI-03</t>
+          <t>QTM-FR-AGT-03 → 指定 TC：TC-CS-AI-03/12</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
-          <t>AgentLoop; AgentRunner; ToolRegistry; EscalationStore</t>
+          <t>AgentLoop; AgentRunner; ReplyGuard; SentimentClassifier; ToolRegistry; EscalationStore</t>
         </is>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K7" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
     </row>
@@ -15592,17 +15592,17 @@
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>AgentLoop; AgentRunner; ToolRegistry; EscalationStore</t>
+          <t>AgentLoop; AgentRunner; ReplyGuard; SentimentClassifier; ToolRegistry; EscalationStore</t>
         </is>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K8" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
     </row>
@@ -15649,17 +15649,17 @@
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>AgentLoop; AgentRunner; ToolRegistry; EscalationStore</t>
+          <t>AgentLoop; AgentRunner; ReplyGuard; SentimentClassifier; ToolRegistry; EscalationStore</t>
         </is>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K9" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
     </row>
@@ -15706,17 +15706,17 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>ContextBuilder; MemoryManager + Store; SkillsLoader + 2 builtin skills; 記憶 DB</t>
+          <t>ContextBuilder; MemoryManager + Store; SkillsLoader + 2 builtin skills; SkillSync; 記憶 DB</t>
         </is>
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L147–149</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K10" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374</t>
+          <t>15_SDS §5.1</t>
         </is>
       </c>
     </row>
@@ -15763,17 +15763,17 @@
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
-          <t>ContextBuilder; MemoryManager + Store; SkillsLoader + 2 builtin skills; 記憶 DB</t>
+          <t>ContextBuilder; MemoryManager + Store; SkillsLoader + 2 builtin skills; SkillSync; 記憶 DB</t>
         </is>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L147–149</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K11" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374</t>
+          <t>15_SDS §5.1</t>
         </is>
       </c>
     </row>
@@ -15825,12 +15825,12 @@
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148; §9 L395, L407</t>
+          <t>12_SAD §4.1、§9</t>
         </is>
       </c>
       <c r="K12" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L369–374; §5.4</t>
+          <t>15_SDS §5.1、§5.4</t>
         </is>
       </c>
     </row>
@@ -15877,17 +15877,17 @@
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
-          <t>AgentLoop; AgentRunner; ToolRegistry; EscalationStore</t>
+          <t>AgentLoop; AgentRunner; ReplyGuard; SentimentClassifier; ToolRegistry; EscalationStore</t>
         </is>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K13" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
     </row>
@@ -15934,17 +15934,17 @@
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>line_gateway; AgentLoop; AgentRunner</t>
+          <t>line_gateway; Photo Guide resolver; Quote postback message mapper; WebhookIdempotencyStore; AgentLoop; AgentRunner</t>
         </is>
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L138–149</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
     </row>
@@ -15996,12 +15996,12 @@
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148; §9 L395, L407</t>
+          <t>12_SAD §4.1、§9</t>
         </is>
       </c>
       <c r="K15" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L369–374; §5.4</t>
+          <t>15_SDS §5.1、§5.4</t>
         </is>
       </c>
     </row>
@@ -16043,22 +16043,22 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>QTM-FR-API-01 → 指定 TC：TC-WO-01/03 + TC-QUOTE-06</t>
+          <t>QTM-FR-API-01 → 指定 TC：TC-WO-01/03/13 + TC-QUOTE-06</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>tenant-scoped routers; Service Layer（problem_card / quote）; core/db.py</t>
+          <t>tenant-scoped routers; Service Layer（problem_card / quote）; Conversation media collector; core/db.py</t>
         </is>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
     </row>
@@ -16100,22 +16100,22 @@
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>QTM-FR-API-02 → 指定 TC：TC-QUOTE-01~08</t>
+          <t>QTM-FR-API-02 → 指定 TC：TC-QUOTE-01~09</t>
         </is>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
-          <t>tenant-scoped routers; Service Layer（problem_card / quote）; core/db.py</t>
+          <t>tenant-scoped routers; Service Layer（problem_card / quote）; Conversation media collector; core/db.py</t>
         </is>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="K17" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
     </row>
@@ -16162,17 +16162,17 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>tenant-scoped routers; Service Layer（problem_card / quote）; core/db.py</t>
+          <t>tenant-scoped routers; Service Layer（problem_card / quote）; Conversation media collector; core/db.py</t>
         </is>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
     </row>
@@ -16214,22 +16214,22 @@
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
-          <t>QTM-FR-API-04 → 指定 TC：TC-WO-01~03/08/09</t>
+          <t>QTM-FR-API-04 → 指定 TC：TC-WO-01~03/08/09/13</t>
         </is>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
-          <t>Service Layer（work_order）; Flow DSL executor; domain blocks / primitives; core/db.py</t>
+          <t>Service Layer（work_order）; Consent link service; Flow DSL executor; domain blocks / primitives; core/db.py</t>
         </is>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L397</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K19" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
+          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
         </is>
       </c>
     </row>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -16276,17 +16276,17 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>Service Layer（dispatch）; Redis pub/sub; Kafka; 分散式排程</t>
+          <t>Service Layer（dispatch）; dispatch_service candidate scoring; Redis pub/sub; Kafka; PG Advisory Cron Leader; 分散式排程</t>
         </is>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §8.1–8.2 L353–372</t>
+          <t>12_SAD §4.2、§8</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660</t>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
         </is>
       </c>
     </row>
@@ -16333,17 +16333,17 @@
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
-          <t>Service Layer（dispatch）; Redis pub/sub; Kafka; 分散式排程</t>
+          <t>Service Layer（dispatch）; dispatch_service candidate scoring; Redis pub/sub; Kafka; PG Advisory Cron Leader; 分散式排程</t>
         </is>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §8.1–8.2 L353–372</t>
+          <t>12_SAD §4.2、§8</t>
         </is>
       </c>
       <c r="K21" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660</t>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
         </is>
       </c>
     </row>
@@ -16390,17 +16390,17 @@
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>Service Layer（dispatch）; Redis pub/sub; Kafka; 分散式排程</t>
+          <t>Service Layer（dispatch）; dispatch_service candidate scoring; Redis pub/sub; Kafka; PG Advisory Cron Leader; 分散式排程</t>
         </is>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §8.1–8.2 L353–372</t>
+          <t>12_SAD §4.2、§8</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660</t>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
         </is>
       </c>
     </row>
@@ -16442,22 +16442,22 @@
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
-          <t>QTM-FR-API-08 → 指定 TC：TC-ONSITE-01~05 + TC-WO-04~07</t>
+          <t>QTM-FR-API-08 → 指定 TC：TC-ONSITE-01~05 + TC-WO-04~07/14</t>
         </is>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
-          <t>Service Layer（work_order）; Flow DSL executor; domain blocks / primitives; core/db.py</t>
+          <t>Service Layer（work_order）; Consent link service; Flow DSL executor; domain blocks / primitives; core/db.py</t>
         </is>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L397</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K23" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
+          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
         </is>
       </c>
     </row>
@@ -16504,17 +16504,17 @@
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>Service Layer（work_order）; Flow DSL executor; domain blocks / primitives; core/db.py</t>
+          <t>Service Layer（work_order）; Consent link service; Flow DSL executor; domain blocks / primitives; core/db.py</t>
         </is>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L397</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
+          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
         </is>
       </c>
     </row>
@@ -16566,12 +16566,12 @@
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L401</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K25" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560</t>
+          <t>15_SDS §4.2、§6.1、§7.3</t>
         </is>
       </c>
     </row>
@@ -16623,12 +16623,12 @@
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L401</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K26" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560</t>
+          <t>15_SDS §4.2、§6.1、§7.3</t>
         </is>
       </c>
     </row>
@@ -16680,12 +16680,12 @@
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L401</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K27" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560</t>
+          <t>15_SDS §4.2、§6.1、§7.3</t>
         </is>
       </c>
     </row>
@@ -16732,17 +16732,17 @@
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; Kafka; line_push_service + outbox worker</t>
+          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; EventBusProducer; Kafka; line_push_service + outbox worker</t>
         </is>
       </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="K28" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677</t>
+          <t>15_SDS §6.1–6.3、§11</t>
         </is>
       </c>
     </row>
@@ -16789,17 +16789,17 @@
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
-          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; Kafka; line_push_service + outbox worker</t>
+          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; EventBusProducer; Kafka; line_push_service + outbox worker</t>
         </is>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="K29" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677</t>
+          <t>15_SDS §6.1–6.3、§11</t>
         </is>
       </c>
     </row>
@@ -16846,17 +16846,17 @@
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; Kafka; line_push_service + outbox worker</t>
+          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; EventBusProducer; Kafka; line_push_service + outbox worker</t>
         </is>
       </c>
       <c r="J30" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="K30" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677</t>
+          <t>15_SDS §6.1–6.3、§11</t>
         </is>
       </c>
     </row>
@@ -16903,17 +16903,17 @@
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
-          <t>守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
+          <t>API_SURFACE router filter; Three-DB Connection Router; DBPoolScopeMiddleware; DEKService + PII blind index + purge ledger; 守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
         </is>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L393</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K31" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L428–472; §6.4 L494–499</t>
+          <t>15_SDS §6.1、§6.4</t>
         </is>
       </c>
     </row>
@@ -16960,17 +16960,17 @@
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>tenant-scoped routers; Service Layer（problem_card / quote）; core/db.py</t>
+          <t>tenant-scoped routers; Service Layer（problem_card / quote）; Conversation media collector; core/db.py</t>
         </is>
       </c>
       <c r="J32" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="K32" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
     </row>
@@ -17017,17 +17017,17 @@
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
-          <t>守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
+          <t>API_SURFACE router filter; Three-DB Connection Router; DBPoolScopeMiddleware; DEKService + PII blind index + purge ledger; 守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
         </is>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L393</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K33" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L428–472; §6.4 L494–499</t>
+          <t>15_SDS §6.1、§6.4</t>
         </is>
       </c>
     </row>
@@ -17074,17 +17074,17 @@
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>tenant-scoped routers; Service Layer（problem_card / quote）; core/db.py</t>
+          <t>tenant-scoped routers; Service Layer（problem_card / quote）; Conversation media collector; core/db.py</t>
         </is>
       </c>
       <c r="J34" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="K34" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
     </row>
@@ -17136,12 +17136,12 @@
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="K35" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599</t>
+          <t>15_SDS §8.1–8.3</t>
         </is>
       </c>
     </row>
@@ -17193,12 +17193,12 @@
       </c>
       <c r="J36" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="K36" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599</t>
+          <t>15_SDS §8.1–8.3</t>
         </is>
       </c>
     </row>
@@ -17240,22 +17240,22 @@
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
-          <t>QTM-FR-WEB-03 → 指定 TC：TC-DISPATCH-03/04 + WS E2E</t>
+          <t>QTM-FR-WEB-03 → 指定 TC：TC-DISPATCH-03/04 + TC-WEB-MEDIA-01 + TC-WEB-OPS-01 + WS E2E</t>
         </is>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>api client; cache; realtime</t>
+          <t>api client; cache; realtime; AuthImage / AuthImageLightbox; ConsentPanel</t>
         </is>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="K37" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L575–578; §8.3 L593–599</t>
+          <t>15_SDS §8.1、§8.3</t>
         </is>
       </c>
     </row>
@@ -17302,17 +17302,17 @@
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>api client; cache; realtime</t>
+          <t>api client; cache; realtime; AuthImage / AuthImageLightbox; ConsentPanel</t>
         </is>
       </c>
       <c r="J38" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="K38" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L575–578; §8.3 L593–599</t>
+          <t>15_SDS §8.1、§8.3</t>
         </is>
       </c>
     </row>
@@ -17364,12 +17364,12 @@
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="K39" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L570–578</t>
+          <t>15_SDS §8.1</t>
         </is>
       </c>
     </row>
@@ -17411,22 +17411,22 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>QTM-FR-WEB-06 → 指定 TC：TC-QUOTE-01/04/05/07/08 + TC-A11Y-01</t>
+          <t>QTM-FR-WEB-06 → 指定 TC：TC-QUOTE-01/04/05/07/08 + TC-WO-14 + TC-A11Y-01</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>api client; cache; realtime</t>
+          <t>api client; cache; realtime; AuthImage / AuthImageLightbox; ConsentPanel</t>
         </is>
       </c>
       <c r="J40" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="K40" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L575–578; §8.3 L593–599</t>
+          <t>15_SDS §8.1、§8.3</t>
         </is>
       </c>
     </row>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
-          <t>QTM-FR-WEB-07 → 指定 TC：error-boundary/offline E2E</t>
+          <t>QTM-FR-WEB-07 → 指定 TC：TC-WEB-MEDIA-01 + error-boundary/offline E2E</t>
         </is>
       </c>
       <c r="I41" s="13" t="inlineStr">
@@ -17478,12 +17478,12 @@
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="K41" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599</t>
+          <t>15_SDS §8.1–8.3</t>
         </is>
       </c>
     </row>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="J42" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.6 L199–208</t>
+          <t>12_SAD §4.6</t>
         </is>
       </c>
       <c r="K42" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L611–613; 附錄 L736</t>
+          <t>15_SDS §9.1；附錄</t>
         </is>
       </c>
     </row>
@@ -17587,17 +17587,17 @@
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; forward-only migrations; platform schema; core/db.py</t>
+          <t>SQL/Schema*.sql; forward-only migrations; platform schema; Tech DB router + mirror; core/db.py</t>
         </is>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>12_SAD §4.2、§4.6</t>
         </is>
       </c>
       <c r="K43" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451</t>
+          <t>15_SDS §3.1、§6.1</t>
         </is>
       </c>
     </row>
@@ -17644,17 +17644,17 @@
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; forward-only migrations; platform schema; core/db.py</t>
+          <t>SQL/Schema*.sql; forward-only migrations; platform schema; Tech DB router + mirror; core/db.py</t>
         </is>
       </c>
       <c r="J44" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>12_SAD §4.2、§4.6</t>
         </is>
       </c>
       <c r="K44" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451</t>
+          <t>15_SDS §3.1、§6.1</t>
         </is>
       </c>
     </row>
@@ -17706,12 +17706,12 @@
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §8.1 L353–361; §9 L407</t>
+          <t>12_SAD §5、§8–9</t>
         </is>
       </c>
       <c r="K45" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L376; §9.1 L617–619; §11.3 L677</t>
+          <t>15_SDS §5.1、§9.1、§11.3</t>
         </is>
       </c>
     </row>
@@ -17763,12 +17763,12 @@
       </c>
       <c r="J46" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
         </is>
       </c>
       <c r="K46" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677</t>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
         </is>
       </c>
     </row>
@@ -17820,12 +17820,12 @@
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
         </is>
       </c>
       <c r="K47" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677</t>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
         </is>
       </c>
     </row>
@@ -17847,12 +17847,12 @@
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>主通道採唯讀 API 增量汲取，事件處理即時增量，每日批次 reconciliation 補齊遺漏資料；來源 provenance 完整率 100%，同一 source_id 重跑不得產生重複資料。</t>
+          <t>主通道採唯讀 API 增量汲取，事件處理即時增量，每日批次 reconciliation 補齊遺漏資料；provenance 完整率 100%，同一 source_id 重跑不得產生重複資料。</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -17877,12 +17877,12 @@
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L179–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="K48" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L603–613; §9.3 L631–635</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
     </row>
@@ -17934,12 +17934,12 @@
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="K49" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L614–615; §9.3 L631–635</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
     </row>
@@ -17986,17 +17986,17 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>Draft Queue; 審核 UI backend</t>
+          <t>Draft Queue; 審核 UI backend; Casdoor reviewer auth</t>
         </is>
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="K50" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L615–616; §9.2 L621–629</t>
+          <t>15_SDS §9.1–9.2</t>
         </is>
       </c>
     </row>
@@ -18043,17 +18043,17 @@
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
-          <t>Publisher; 品牌庫 pgvector; SkillsLoader + 2 builtin skills</t>
+          <t>Publisher; behavior patch artifact; LiveSkill DB ingest; 品牌庫 pgvector; SkillsLoader + 2 builtin skills</t>
         </is>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="K51" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L617–619; §9.3 L631–635</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
     </row>
@@ -18100,17 +18100,17 @@
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>Draft Queue; 審核 UI backend</t>
+          <t>Draft Queue; 審核 UI backend; Casdoor reviewer auth</t>
         </is>
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="K52" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L615–616; §9.2 L621–629</t>
+          <t>15_SDS §9.1–9.2</t>
         </is>
       </c>
     </row>
@@ -18157,17 +18157,17 @@
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
-          <t>self-service routers; 守衛鏈; technician_service; certification/kyc_service; lock_tech</t>
+          <t>API_SURFACE router filter; self-service routers; 守衛鏈; technician_service; certification/kyc_service; Tech DB router + mirror; lock_tech</t>
         </is>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="K53" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
+          <t>15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
     </row>
@@ -18214,17 +18214,17 @@
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>self-service routers; 守衛鏈; technician_service; certification/kyc_service; lock_tech</t>
+          <t>API_SURFACE router filter; self-service routers; 守衛鏈; technician_service; certification/kyc_service; Tech DB router + mirror; lock_tech</t>
         </is>
       </c>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="K54" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
+          <t>15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
     </row>
@@ -18271,17 +18271,17 @@
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
-          <t>OHS API routers; matching_service; schedule_service; WebSocket 端點; 事件層</t>
+          <t>OHS API routers; dispatch_service candidate scoring; schedule_service; WebSocket 端點; 事件層</t>
         </is>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="K55" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
+          <t>15_SDS §4.4、§7.1–7.2</t>
         </is>
       </c>
     </row>
@@ -18328,17 +18328,17 @@
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>OHS API routers; matching_service; schedule_service; WebSocket 端點; 事件層</t>
+          <t>OHS API routers; dispatch_service candidate scoring; schedule_service; WebSocket 端點; 事件層</t>
         </is>
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="K56" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
+          <t>15_SDS §4.4、§7.1–7.2</t>
         </is>
       </c>
     </row>
@@ -18385,17 +18385,17 @@
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
-          <t>事件層; 技師工單 read-model; WebSocket 端點</t>
+          <t>事件層; EventConsumerWorker; technician_workorder_projection; 技師工單 read-model; WebSocket 端點</t>
         </is>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L193–197; §8.2 L369, L372</t>
+          <t>12_SAD §4.5、§8.2</t>
         </is>
       </c>
       <c r="K57" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L513–518; §7.3 L554–560; §11.1 L648–660</t>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
     </row>
@@ -18442,17 +18442,17 @@
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>commission_settlement_service; 技師工單 read-model; Kafka</t>
+          <t>technician settlement services; technician_commission_projection; EventConsumerWorker; Kafka</t>
         </is>
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197; §9 L401</t>
+          <t>12_SAD §4.5、§9</t>
         </is>
       </c>
       <c r="K58" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L515–518; §7.3 L554–560; §11.1 L648–660</t>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
     </row>
@@ -18499,17 +18499,17 @@
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
-          <t>OHS API routers; matching_service; schedule_service; WebSocket 端點; 事件層</t>
+          <t>OHS API routers; dispatch_service candidate scoring; schedule_service; WebSocket 端點; 事件層</t>
         </is>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="K59" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
+          <t>15_SDS §4.4、§7.1–7.2</t>
         </is>
       </c>
     </row>
@@ -18556,17 +18556,17 @@
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>self-service routers; 守衛鏈; technician_service; certification/kyc_service; lock_tech</t>
+          <t>API_SURFACE router filter; self-service routers; 守衛鏈; technician_service; certification/kyc_service; Tech DB router + mirror; lock_tech</t>
         </is>
       </c>
       <c r="J60" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="K60" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
+          <t>15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
     </row>
@@ -18613,17 +18613,17 @@
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
-          <t>Casdoor; 平台維運 console; 守衛鏈; License provisioning</t>
+          <t>Casdoor; 平台維運 console; 守衛鏈; License Entitlement Gate; License provisioning</t>
         </is>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="K61" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
         </is>
       </c>
     </row>
@@ -18670,17 +18670,17 @@
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>Casdoor; 平台維運 console; 守衛鏈; License provisioning</t>
+          <t>Casdoor; 平台維運 console; 守衛鏈; License Entitlement Gate; License provisioning</t>
         </is>
       </c>
       <c r="J62" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="K62" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
         </is>
       </c>
     </row>
@@ -18727,17 +18727,17 @@
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
-          <t>Casdoor; 平台維運 console; 守衛鏈; License provisioning</t>
+          <t>Casdoor; 平台維運 console; 守衛鏈; License Entitlement Gate; License provisioning</t>
         </is>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="K63" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
         </is>
       </c>
     </row>
@@ -18789,12 +18789,12 @@
       </c>
       <c r="J64" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L164; §8.1–8.2 L353–372; §9 L394</t>
+          <t>12_SAD §4.2、§8–9</t>
         </is>
       </c>
       <c r="K64" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L453–466; §6.3 L484–492; §11 L648–677</t>
+          <t>15_SDS §6.1、§6.3、§11</t>
         </is>
       </c>
     </row>
@@ -18846,12 +18846,12 @@
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L146; §9 L395, L407</t>
+          <t>12_SAD §4.1、§9</t>
         </is>
       </c>
       <c r="K65" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §2.2 L68; §5.1 L370; §13 L707</t>
+          <t>15_SDS §2.2、§5.1、§13</t>
         </is>
       </c>
     </row>
@@ -18898,17 +18898,17 @@
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>SigNoz; OPIK; OpenTelemetry</t>
+          <t>SigNoz; OPIK; OpenTelemetry; PIIScrubSpanProcessor</t>
         </is>
       </c>
       <c r="J66" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §8.2 L363–372; §9 L389</t>
+          <t>12_SAD §8.2、§9</t>
         </is>
       </c>
       <c r="K66" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §12 L681–696（韌性與觀測證據使用面）</t>
+          <t>15_SDS §12</t>
         </is>
       </c>
     </row>
@@ -18960,12 +18960,12 @@
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §9 L396–398</t>
+          <t>12_SAD §9</t>
         </is>
       </c>
       <c r="K67" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L36–59; §3.2–3.7 L126–205; §10 L639–644</t>
+          <t>15_SDS §2.1、§3.2–3.7、§10</t>
         </is>
       </c>
     </row>
@@ -19012,17 +19012,17 @@
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>Agent Configuration Studio / Config Registry; Vertical Pack; HITL 審核骨架</t>
+          <t>Agent Configuration Studio / Config Registry; M18 Config Registry; Skill Revision Registry; Vertical Pack; HITL 審核骨架</t>
         </is>
       </c>
       <c r="J68" s="17" t="inlineStr">
         <is>
-          <t>12_SAD §9 L396, L398, L400</t>
+          <t>12_SAD §9</t>
         </is>
       </c>
       <c r="K68" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §3.2 L126–142; §10 L639–644; §13 L704–709</t>
+          <t>15_SDS §3.2、§10、§13</t>
         </is>
       </c>
     </row>
@@ -19069,17 +19069,17 @@
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
-          <t>Agent Configuration Studio / Config Registry; Vertical Pack; HITL 審核骨架</t>
+          <t>Agent Configuration Studio / Config Registry; M18 Config Registry; Skill Revision Registry; Vertical Pack; HITL 審核骨架</t>
         </is>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §9 L396, L398, L400</t>
+          <t>12_SAD §9</t>
         </is>
       </c>
       <c r="K69" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §3.2 L126–142; §10 L639–644; §13 L704–709</t>
+          <t>15_SDS §3.2、§10、§13</t>
         </is>
       </c>
     </row>
@@ -19106,7 +19106,7 @@
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -19329,12 +19329,12 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>p95 &lt; 300ms；50 位並行使用者、15 分鐘穩定負載，錯誤率 &lt; 1%</t>
+          <t>p95 &lt; 300ms；本次為受控設計門檻，必須保存實測報表後才可標示通過</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -19386,7 +19386,7 @@
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>&lt; 1s（同實例）；跨實例經 Redis pub/sub（🔜 規劃中）</t>
+          <t>&lt; 1s（同實例）；跨實例經 Redis pub/sub（ ）</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
@@ -19443,12 +19443,12 @@
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>p95 &lt; 300ms；10,000 筆技師基準資料、50 位並行使用者、15 分鐘穩定負載，錯誤率 &lt; 1%</t>
+          <t>POST /technicians:match p95 &lt; 300ms；本次為受控設計門檻，必須保存讀取路由與實測報表後才可標示通過</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
@@ -19500,7 +19500,7 @@
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>&lt; 2s（跨 Kafka + WS）</t>
+          <t>&lt; 2s（跨 Kafka + 即時連線）</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
@@ -19671,12 +19671,12 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>≤ 3s；Lighthouse mobile / Fast 4G / 4× CPU slowdown，5 次測試中位數</t>
+          <t>web 首次內容繪製 FCP ≤ 3s；以各站 Lighthouse 或 RUM 結果逐站裁定</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
@@ -19899,7 +19899,7 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>≥ 99.9%（含 24h dedup + DLQ 重試）</t>
+          <t>≥ 99.9%（含 24h 相同事件不得重複處理 + DLQ 重試）</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
@@ -20127,7 +20127,7 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>OHS API + lock_tech HA（媒合不可用 = 全品牌派工受阻）</t>
+          <t>技師媒合服務 API + lock_tech HA（媒合不可用 = 全品牌派工受阻）</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
@@ -20355,7 +20355,7 @@
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>WS 未設定/斷線 100% 靜默降級，不阻塞頁面</t>
+          <t>即時連線未設定/斷線 100% 靜默降級，不阻塞頁面</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="D105" s="13" t="inlineStr">
         <is>
-          <t>新增品牌 = 新 OHS 消費者 + Kafka 訂閱者；技師平台不需 per-brand 複製</t>
+          <t>新增品牌 = 新技師媒合服務消費者 + Kafka 訂閱者；技師平台不需 per-brand 複製</t>
         </is>
       </c>
       <c r="E105" s="13" t="inlineStr">
@@ -21153,7 +21153,7 @@
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>WS 走 Redis pub/sub 水平擴展（🔜 規劃中）</t>
+          <t>即時連線走 Redis pub/sub 水平擴展（ ）</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
@@ -21267,7 +21267,7 @@
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>Casdoor OIDC 統一 token（授權碼流；token httpOnly cookie / 安全儲存）（🔜 規劃中全面 OIDC 化）</t>
+          <t>Casdoor 登入憑證統一 token（授權碼流；token httpOnly cookie / 安全儲存）（ 全面登入憑證化）</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
@@ -21324,7 +21324,7 @@
       </c>
       <c r="D109" s="13" t="inlineStr">
         <is>
-          <t>四方 RBAC resource-level enforce，預設拒絕；未授權寫入 100% 403；SoD 任二角色相同 → 403</t>
+          <t>四方角色權限 resource-level enforce，預設拒絕；未授權寫入 100% 403；職能分離任二角色相同 → 403</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
@@ -21780,12 +21780,12 @@
       </c>
       <c r="D117" s="13" t="inlineStr">
         <is>
-          <t>agent → api X-Internal-Token（api 側驗證失敗即拒絕、常數時間比對）；品牌 api → OHS 採 Casdoor OIDC OAuth 2.0 client_credentials，JWT 必驗 issuer/audience/expiry，無效或過期憑證 100% 回 401</t>
+          <t>agent → api 使用 X-Internal-Token，驗證失敗即拒絕且採常數時間比對；品牌 api → OHS 仍屬 TO-BE，服務憑證機制未經 ADR 定版與負向測試前，本項只能標示阻擋，不得標示通過</t>
         </is>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
       <c r="F117" s="13" t="inlineStr">
@@ -22749,7 +22749,7 @@
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>&lt; 30min；Agent config 還原 ≤ 1min（前版保留 ≥ 24h）</t>
+          <t>&lt; 30min；Agent config 還原上一版 ≤ 1min（前版保留 ≥ 24h）</t>
         </is>
       </c>
       <c r="E134" s="14" t="inlineStr">
@@ -22863,7 +22863,7 @@
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>append-only、JSON + trace_id、retention eternal；audit_events hash chain 完整性可驗證</t>
+          <t>只增不刪、JSON + trace_id、retention eternal；稽核紀錄_events hash chain 完整性可驗證</t>
         </is>
       </c>
       <c r="E136" s="14" t="inlineStr">
@@ -23034,7 +23034,7 @@
       </c>
       <c r="D139" s="13" t="inlineStr">
         <is>
-          <t>100% 覆核、不可篡改、SLA ≤ 24h</t>
+          <t>100% 覆核、不可篡改、時限目標 ≤ 24h</t>
         </is>
       </c>
       <c r="E139" s="13" t="inlineStr">
@@ -23205,7 +23205,7 @@
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>稽核員唯讀存取入同一 audit stream；flagged item full deny + log</t>
+          <t>稽核員唯讀存取入同一稽核紀錄 stream；flagged item full deny + log</t>
         </is>
       </c>
       <c r="E142" s="14" t="inlineStr">
@@ -23433,12 +23433,12 @@
       </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>上線候選內容 100% 經人工審核；每版不足 100 筆時全驗，否則至少抽驗 100 筆且不低於該版 10%；一般內容誤放率 ≤ 1%，高風險內容誤放 1 筆即阻擋發布</t>
+          <t>每次發布須保存人工審核筆數、核可通過率與抽樣誤放率；Data 負責人尚未核定數值門檻前，本項只能標示阻擋，不得標示通過</t>
         </is>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
       <c r="F146" s="14" t="inlineStr">
@@ -23490,7 +23490,7 @@
       </c>
       <c r="D147" s="13" t="inlineStr">
         <is>
-          <t>draft 未經人工審核核可，0 筆寫入 pgvector / skill</t>
+          <t>draft 未經人工審核核可，0 筆寫入向量知識庫 / skill</t>
         </is>
       </c>
       <c r="E147" s="13" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="D149" s="13" t="inlineStr">
         <is>
-          <t>CI 同源檢查通過（🔜 規劃中）</t>
+          <t>CI 同源檢查通過（ ）</t>
         </is>
       </c>
       <c r="E149" s="13" t="inlineStr">
@@ -23775,7 +23775,7 @@
       </c>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>schema_migrations 表為唯一真相；registry drift CI 警示（🔜 規劃中）</t>
+          <t>schema_migrations 表為唯一真相；registry drift CI 警示（ ）</t>
         </is>
       </c>
       <c r="E152" s="14" t="inlineStr">
@@ -23946,12 +23946,12 @@
       </c>
       <c r="D155" s="13" t="inlineStr">
         <is>
-          <t>原始資產 100% 原樣落 raw object storage，保存 content hash、source URI、acquired_at；至少保留 1 年或至衍生 bronze 退役（取較長者）</t>
+          <t>raw 原始資產須有核准的保存位置、期限、不可變性與刪除例外規則；四項任一未定版即阻擋 raw → bronze 可重建驗收</t>
         </is>
       </c>
       <c r="E155" s="13" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
       <c r="F155" s="13" t="inlineStr">
@@ -24174,7 +24174,7 @@
       </c>
       <c r="D159" s="13" t="inlineStr">
         <is>
-          <t>重大架構決策 100% 有 ADR（append-only；新決策以新 ADR 取代，不改舊文）</t>
+          <t>重大架構決策 100% 有 ADR（只增不刪；新決策以新 ADR 取代，不改舊文）</t>
         </is>
       </c>
       <c r="E159" s="13" t="inlineStr">
@@ -24288,7 +24288,7 @@
       </c>
       <c r="D161" s="13" t="inlineStr">
         <is>
-          <t>品牌 api ↔ OHS API + Kafka event schema 走 consumer-driven contract test（🔜 規劃中）</t>
+          <t>品牌 api ↔ 技師媒合服務 API + Kafka event schema 走 consumer-driven contract test（ ）</t>
         </is>
       </c>
       <c r="E161" s="13" t="inlineStr">
@@ -24402,12 +24402,12 @@
       </c>
       <c r="D163" s="13" t="inlineStr">
         <is>
-          <t>每個 RC 以 Playwright 100% 涵蓋九條關鍵流：LINE 建案、報價同意、付款、派工 SLA、技師接拒單/到場/requote、結算退款、跨租戶拒絕、知識人工審核發布、租戶開站/License</t>
+          <t>Playwright 至少涵蓋登入、品牌後台關鍵頁、問題卡／工單主要流程、錯誤回復及技師接案→到場→完工；CI 任一關鍵案例失敗即阻擋發布</t>
         </is>
       </c>
       <c r="E163" s="13" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
       <c r="F163" s="13" t="inlineStr">
@@ -24915,7 +24915,7 @@
       </c>
       <c r="D172" s="14" t="inlineStr">
         <is>
-          <t>forget ≤ 7d、retention 分級、visibility 驗證失敗即拒絕（§5）</t>
+          <t>forget ≤ 7d、retention 分級、visibility 驗證失敗時一律拒絕（§5）</t>
         </is>
       </c>
       <c r="E172" s="14" t="inlineStr">
@@ -25628,7 +25628,7 @@
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>TC-CS-AI-01/02</t>
+          <t>TC-CS-AI-01/02/11</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>已釐清寫 clarification_confirmed_at；連續 3 次未釐清升級轉真人</t>
+          <t>缺項依情境一次列齊；明確要求真人、急迫派工、金錢相關或連續兩次不滿時立即轉真人；一般補資料、單次不滿或可回答知識題不得因固定輪數誤轉。</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
@@ -25752,7 +25752,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>TC-CS-AI-03</t>
+          <t>TC-CS-AI-03/12</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -26310,7 +26310,7 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>TC-WO-01/03 + TC-QUOTE-06</t>
+          <t>TC-WO-01/03/13 + TC-QUOTE-06</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
@@ -26372,7 +26372,7 @@
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>TC-QUOTE-01~08</t>
+          <t>TC-QUOTE-01~09</t>
         </is>
       </c>
       <c r="I17" s="13" t="inlineStr">
@@ -26496,7 +26496,7 @@
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
-          <t>TC-WO-01~03/08/09</t>
+          <t>TC-WO-01~03/08/09/13</t>
         </is>
       </c>
       <c r="I19" s="13" t="inlineStr">
@@ -26578,7 +26578,7 @@
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
     </row>
@@ -26744,7 +26744,7 @@
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
-          <t>TC-ONSITE-01~05 + TC-WO-04~07</t>
+          <t>TC-ONSITE-01~05 + TC-WO-04~07/14</t>
         </is>
       </c>
       <c r="I23" s="13" t="inlineStr">
@@ -27612,7 +27612,7 @@
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
-          <t>TC-DISPATCH-03/04 + WS E2E</t>
+          <t>TC-DISPATCH-03/04 + TC-WEB-MEDIA-01 + TC-WEB-OPS-01 + WS E2E</t>
         </is>
       </c>
       <c r="I37" s="13" t="inlineStr">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>TC-QUOTE-01/04/05/07/08 + TC-A11Y-01</t>
+          <t>TC-QUOTE-01/04/05/07/08 + TC-WO-14 + TC-A11Y-01</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
@@ -27860,7 +27860,7 @@
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
-          <t>error-boundary/offline E2E</t>
+          <t>TC-WEB-MEDIA-01 + error-boundary/offline E2E</t>
         </is>
       </c>
       <c r="I41" s="13" t="inlineStr">
@@ -28284,7 +28284,7 @@
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>主通道採唯讀 API 增量汲取，事件處理即時增量，每日批次 reconciliation 補齊遺漏資料；來源 provenance 完整率 100%，同一 source_id 重跑不得產生重複資料。</t>
+          <t>主通道採唯讀 API 增量汲取，事件處理即時增量，每日批次 reconciliation 補齊遺漏資料；provenance 完整率 100%，同一 source_id 重跑不得產生重複資料。</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -28314,7 +28314,7 @@
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
     </row>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>TC-PERF-01/02 ｜ 驗證：k6 50 位並行使用者、15 分鐘穩定負載；輸出 p95/p99、錯誤率與逾時分布</t>
+          <t>TC-PERF-01/02 ｜ 驗證：k6 load 50 位並行使用者（實測依本表受控判準）</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
@@ -29678,7 +29678,7 @@
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
     </row>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>p95 &lt; 300ms；50 位並行使用者、15 分鐘穩定負載，錯誤率 &lt; 1%</t>
+          <t>p95 &lt; 300ms；本次為受控設計門檻，必須保存實測報表後才可標示通過</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -29906,7 +29906,7 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>TC-NFR-Perf-005（受控 NFR 驗證設計） ｜ 驗證：k6 + APM（SigNoz），依端點輸出 latency/error 分布</t>
+          <t>TC-NFR-Perf-005（受控 NFR 驗證設計） ｜ 驗證：APM（SigNoz）</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
@@ -29926,7 +29926,7 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
     </row>
@@ -29958,7 +29958,7 @@
       </c>
       <c r="F75" s="13" t="inlineStr">
         <is>
-          <t>&lt; 1s（同實例）；跨實例經 Redis pub/sub（🔜 規劃中）</t>
+          <t>&lt; 1s（同實例）；跨實例經 Redis pub/sub（ ）</t>
         </is>
       </c>
       <c r="G75" s="13" t="inlineStr">
@@ -30020,7 +30020,7 @@
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>p95 &lt; 300ms；10,000 筆技師基準資料、50 位並行使用者、15 分鐘穩定負載，錯誤率 &lt; 1%</t>
+          <t>POST /technicians:match p95 &lt; 300ms；本次為受控設計門檻，必須保存讀取路由與實測報表後才可標示通過</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -30030,7 +30030,7 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>TC-PERF-03 ｜ 驗證：k6 + read replica 路由驗證；保存資料集版本與查詢計畫</t>
+          <t>TC-PERF-03 ｜ 驗證：k6 + read replica 路由驗證</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
@@ -30050,7 +30050,7 @@
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
     </row>
@@ -30082,7 +30082,7 @@
       </c>
       <c r="F77" s="13" t="inlineStr">
         <is>
-          <t>&lt; 2s（跨 Kafka + WS）</t>
+          <t>&lt; 2s（跨 Kafka + 即時連線）</t>
         </is>
       </c>
       <c r="G77" s="13" t="inlineStr">
@@ -30268,7 +30268,7 @@
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>≤ 3s；Lighthouse mobile / Fast 4G / 4× CPU slowdown，5 次測試中位數</t>
+          <t>web 首次內容繪製 FCP ≤ 3s；以各站 Lighthouse 或 RUM 結果逐站裁定</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -30278,7 +30278,7 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>TC-NFR-Perf-011（受控 NFR 驗證設計） ｜ 驗證：Lighthouse CI + RUM P75 交叉驗證</t>
+          <t>TC-NFR-Perf-011（受控 NFR 驗證設計） ｜ 驗證：Lighthouse / RUM</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
@@ -30298,7 +30298,7 @@
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
     </row>
@@ -30516,7 +30516,7 @@
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>≥ 99.9%（含 24h dedup + DLQ 重試）</t>
+          <t>≥ 99.9%（含 24h 相同事件不得重複處理 + DLQ 重試）</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -30764,7 +30764,7 @@
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>OHS API + lock_tech HA（媒合不可用 = 全品牌派工受阻）</t>
+          <t>技師媒合服務 API + lock_tech HA（媒合不可用 = 全品牌派工受阻）</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -30898,7 +30898,7 @@
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>TC-NFR-Avail-009（受控 NFR 驗證設計） ｜ 驗證：重播演練（🔜 規劃中）</t>
+          <t>TC-NFR-Avail-009（受控 NFR 驗證設計） ｜ 驗證：重播演練（ ）</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
@@ -31012,7 +31012,7 @@
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>WS 未設定/斷線 100% 靜默降級，不阻塞頁面</t>
+          <t>即時連線未設定/斷線 100% 靜默降級，不阻塞頁面</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
@@ -31208,7 +31208,7 @@
       </c>
       <c r="H95" s="13" t="inlineStr">
         <is>
-          <t>TC-NFR-Rel-003（受控 NFR 驗證設計） ｜ 驗證：整合測試 + escalation 對帳</t>
+          <t>TC-NFR-Rel-003（受控 NFR 驗證設計） ｜ 驗證：整合測試 + 轉真人案件對帳</t>
         </is>
       </c>
       <c r="I95" s="13" t="inlineStr">
@@ -31818,7 +31818,7 @@
       </c>
       <c r="F105" s="13" t="inlineStr">
         <is>
-          <t>新增品牌 = 新 OHS 消費者 + Kafka 訂閱者；技師平台不需 per-brand 複製</t>
+          <t>新增品牌 = 新技師媒合服務消費者 + Kafka 訂閱者；技師平台不需 per-brand 複製</t>
         </is>
       </c>
       <c r="G105" s="13" t="inlineStr">
@@ -31880,7 +31880,7 @@
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>WS 走 Redis pub/sub 水平擴展（🔜 規劃中）</t>
+          <t>即時連線走 Redis pub/sub 水平擴展（ ）</t>
         </is>
       </c>
       <c r="G106" s="14" t="inlineStr">
@@ -31890,7 +31890,7 @@
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>TC-NFR-Scal-008（受控 NFR 驗證設計） ｜ 驗證：k6 WS 併發測試</t>
+          <t>TC-NFR-Scal-008（受控 NFR 驗證設計） ｜ 驗證：k6 即時連線併發測試</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>Casdoor OIDC 統一 token（授權碼流；token httpOnly cookie / 安全儲存）（🔜 規劃中全面 OIDC 化）</t>
+          <t>Casdoor 登入憑證統一 token（授權碼流；token httpOnly cookie / 安全儲存）（ 全面登入憑證化）</t>
         </is>
       </c>
       <c r="G108" s="14" t="inlineStr">
@@ -32066,7 +32066,7 @@
       </c>
       <c r="F109" s="13" t="inlineStr">
         <is>
-          <t>四方 RBAC resource-level enforce，預設拒絕；未授權寫入 100% 403；SoD 任二角色相同 → 403</t>
+          <t>四方角色權限 resource-level enforce，預設拒絕；未授權寫入 100% 403；職能分離任二角色相同 → 403</t>
         </is>
       </c>
       <c r="G109" s="13" t="inlineStr">
@@ -32448,7 +32448,7 @@
       </c>
       <c r="H115" s="13" t="inlineStr">
         <is>
-          <t>TC-COMPLIANCE-06 ｜ 驗證：webhook + runtime double-gate + 稽核</t>
+          <t>TC-COMPLIANCE-06 ｜ 驗證：webhook + runtime double-阻擋條件 + 稽核</t>
         </is>
       </c>
       <c r="I115" s="13" t="inlineStr">
@@ -32562,7 +32562,7 @@
       </c>
       <c r="F117" s="13" t="inlineStr">
         <is>
-          <t>agent → api X-Internal-Token（api 側驗證失敗即拒絕、常數時間比對）；品牌 api → OHS 採 Casdoor OIDC OAuth 2.0 client_credentials，JWT 必驗 issuer/audience/expiry，無效或過期憑證 100% 回 401</t>
+          <t>agent → api 使用 X-Internal-Token，驗證失敗即拒絕且採常數時間比對；品牌 api → OHS 仍屬 TO-BE，服務憑證機制未經 ADR 定版與負向測試前，本項只能標示阻擋，不得標示通過</t>
         </is>
       </c>
       <c r="G117" s="13" t="inlineStr">
@@ -32572,7 +32572,7 @@
       </c>
       <c r="H117" s="13" t="inlineStr">
         <is>
-          <t>TC-SEC-INT-01 ｜ 驗證：正常、錯 issuer、錯 audience、過期、撤銷五類整合測試</t>
+          <t>TC-SEC-INT-01 ｜ 驗證：整合測試</t>
         </is>
       </c>
       <c r="I117" s="13" t="inlineStr">
@@ -32592,7 +32592,7 @@
       </c>
       <c r="L117" s="13" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
     </row>
@@ -32696,7 +32696,7 @@
       </c>
       <c r="H119" s="13" t="inlineStr">
         <is>
-          <t>TC-NFR-Sec-013（受控 NFR 驗證設計） ｜ 驗證：secret scan + audit</t>
+          <t>TC-NFR-Sec-013（受控 NFR 驗證設計） ｜ 驗證：secret scan + 稽核紀錄</t>
         </is>
       </c>
       <c r="I119" s="13" t="inlineStr">
@@ -32882,7 +32882,7 @@
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
-          <t>TC-NFR-Priv-002（受控 NFR 驗證設計） ｜ 驗證：api GDPR cron + audit</t>
+          <t>TC-NFR-Priv-002（受控 NFR 驗證設計） ｜ 驗證：api GDPR cron + 稽核紀錄</t>
         </is>
       </c>
       <c r="I122" s="14" t="inlineStr">
@@ -33006,7 +33006,7 @@
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
-          <t>TC-NFR-Priv-004（受控 NFR 驗證設計） ｜ 驗證：audit + ADR 流程</t>
+          <t>TC-NFR-Priv-004（受控 NFR 驗證設計） ｜ 驗證：稽核紀錄 + ADR 流程</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr">
@@ -33068,7 +33068,7 @@
       </c>
       <c r="H125" s="13" t="inlineStr">
         <is>
-          <t>TC-COMPLIANCE-01/02 ｜ 驗證：forget 流程端到端測試 + audit</t>
+          <t>TC-COMPLIANCE-01/02 ｜ 驗證：forget 流程端到端測試 + 稽核紀錄</t>
         </is>
       </c>
       <c r="I125" s="13" t="inlineStr">
@@ -33254,7 +33254,7 @@
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
-          <t>TC-COMPLIANCE-01/04 ｜ 驗證：purge phase audit（purge_audit.entry）</t>
+          <t>TC-COMPLIANCE-01/04 ｜ 驗證：purge phase 稽核紀錄（purge_稽核紀錄.entry）</t>
         </is>
       </c>
       <c r="I128" s="14" t="inlineStr">
@@ -33616,7 +33616,7 @@
       </c>
       <c r="F134" s="14" t="inlineStr">
         <is>
-          <t>&lt; 30min；Agent config 還原 ≤ 1min（前版保留 ≥ 24h）</t>
+          <t>&lt; 30min；Agent config 還原上一版 ≤ 1min（前版保留 ≥ 24h）</t>
         </is>
       </c>
       <c r="G134" s="14" t="inlineStr">
@@ -33740,7 +33740,7 @@
       </c>
       <c r="F136" s="14" t="inlineStr">
         <is>
-          <t>append-only、JSON + trace_id、retention eternal；audit_events hash chain 完整性可驗證</t>
+          <t>只增不刪、JSON + trace_id、retention eternal；稽核紀錄_events hash chain 完整性可驗證</t>
         </is>
       </c>
       <c r="G136" s="14" t="inlineStr">
@@ -33926,7 +33926,7 @@
       </c>
       <c r="F139" s="13" t="inlineStr">
         <is>
-          <t>100% 覆核、不可篡改、SLA ≤ 24h</t>
+          <t>100% 覆核、不可篡改、時限目標 ≤ 24h</t>
         </is>
       </c>
       <c r="G139" s="13" t="inlineStr">
@@ -34060,7 +34060,7 @@
       </c>
       <c r="H141" s="13" t="inlineStr">
         <is>
-          <t>TC-NFR-Aud-006（受控 NFR 驗證設計） ｜ 驗證：audit log API + cron retention check</t>
+          <t>TC-NFR-Aud-006（受控 NFR 驗證設計） ｜ 驗證：稽核紀錄 log API + cron retention check</t>
         </is>
       </c>
       <c r="I141" s="13" t="inlineStr">
@@ -34112,7 +34112,7 @@
       </c>
       <c r="F142" s="14" t="inlineStr">
         <is>
-          <t>稽核員唯讀存取入同一 audit stream；flagged item full deny + log</t>
+          <t>稽核員唯讀存取入同一稽核紀錄 stream；flagged item full deny + log</t>
         </is>
       </c>
       <c r="G142" s="14" t="inlineStr">
@@ -34184,7 +34184,7 @@
       </c>
       <c r="H143" s="13" t="inlineStr">
         <is>
-          <t>TC-COMPLIANCE-08 ｜ 驗證：Publisher 匯入前 source 允許清單驗證 + 抽查</t>
+          <t>TC-COMPLIANCE-08 ｜ 驗證：發布服務匯入前 source 允許清單驗證 + 抽查</t>
         </is>
       </c>
       <c r="I143" s="13" t="inlineStr">
@@ -34360,7 +34360,7 @@
       </c>
       <c r="F146" s="14" t="inlineStr">
         <is>
-          <t>上線候選內容 100% 經人工審核；每版不足 100 筆時全驗，否則至少抽驗 100 筆且不低於該版 10%；一般內容誤放率 ≤ 1%，高風險內容誤放 1 筆即阻擋發布</t>
+          <t>每次發布須保存人工審核筆數、核可通過率與抽樣誤放率；Data 負責人尚未核定數值門檻前，本項只能標示阻擋，不得標示通過</t>
         </is>
       </c>
       <c r="G146" s="14" t="inlineStr">
@@ -34370,7 +34370,7 @@
       </c>
       <c r="H146" s="14" t="inlineStr">
         <is>
-          <t>TC-NFR-DQ-004（受控 NFR 驗證設計） ｜ 驗證：依風險分層抽樣人工審核 + 發布 gate 報表</t>
+          <t>TC-NFR-DQ-004（受控 NFR 驗證設計） ｜ 驗證：抽樣人工審核</t>
         </is>
       </c>
       <c r="I146" s="14" t="inlineStr">
@@ -34390,7 +34390,7 @@
       </c>
       <c r="L146" s="14" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
     </row>
@@ -34422,7 +34422,7 @@
       </c>
       <c r="F147" s="13" t="inlineStr">
         <is>
-          <t>draft 未經人工審核核可，0 筆寫入 pgvector / skill</t>
+          <t>draft 未經人工審核核可，0 筆寫入向量知識庫 / skill</t>
         </is>
       </c>
       <c r="G147" s="13" t="inlineStr">
@@ -34432,7 +34432,7 @@
       </c>
       <c r="H147" s="13" t="inlineStr">
         <is>
-          <t>TC-NFR-PUB-001（受控 NFR 驗證設計） ｜ 驗證：Publisher gate 測試</t>
+          <t>TC-NFR-PUB-001（受控 NFR 驗證設計） ｜ 驗證：發布服務阻擋條件測試</t>
         </is>
       </c>
       <c r="I147" s="13" t="inlineStr">
@@ -34546,7 +34546,7 @@
       </c>
       <c r="F149" s="13" t="inlineStr">
         <is>
-          <t>CI 同源檢查通過（🔜 規劃中）</t>
+          <t>CI 同源檢查通過（ ）</t>
         </is>
       </c>
       <c r="G149" s="13" t="inlineStr">
@@ -34732,7 +34732,7 @@
       </c>
       <c r="F152" s="14" t="inlineStr">
         <is>
-          <t>schema_migrations 表為唯一真相；registry drift CI 警示（🔜 規劃中）</t>
+          <t>schema_migrations 表為唯一真相；registry drift CI 警示（ ）</t>
         </is>
       </c>
       <c r="G152" s="14" t="inlineStr">
@@ -34918,7 +34918,7 @@
       </c>
       <c r="F155" s="13" t="inlineStr">
         <is>
-          <t>原始資產 100% 原樣落 raw object storage，保存 content hash、source URI、acquired_at；至少保留 1 年或至衍生 bronze 退役（取較長者）</t>
+          <t>raw 原始資產須有核准的保存位置、期限、不可變性與刪除例外規則；四項任一未定版即阻擋 raw → bronze 可重建驗收</t>
         </is>
       </c>
       <c r="G155" s="13" t="inlineStr">
@@ -34928,7 +34928,7 @@
       </c>
       <c r="H155" s="13" t="inlineStr">
         <is>
-          <t>TC-NFR-Rep-002（受控 NFR 驗證設計） ｜ 驗證：每季按來源類型抽 10 筆從 raw 重建 bronze，hash/provenance 100% 一致</t>
+          <t>TC-NFR-Rep-002（受控 NFR 驗證設計） ｜ 驗證：保存位置文件化</t>
         </is>
       </c>
       <c r="I155" s="13" t="inlineStr">
@@ -34948,7 +34948,7 @@
       </c>
       <c r="L155" s="13" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
     </row>
@@ -35166,7 +35166,7 @@
       </c>
       <c r="F159" s="13" t="inlineStr">
         <is>
-          <t>重大架構決策 100% 有 ADR（append-only；新決策以新 ADR 取代，不改舊文）</t>
+          <t>重大架構決策 100% 有 ADR（只增不刪；新決策以新 ADR 取代，不改舊文）</t>
         </is>
       </c>
       <c r="G159" s="13" t="inlineStr">
@@ -35290,7 +35290,7 @@
       </c>
       <c r="F161" s="13" t="inlineStr">
         <is>
-          <t>品牌 api ↔ OHS API + Kafka event schema 走 consumer-driven contract test（🔜 規劃中）</t>
+          <t>品牌 api ↔ 技師媒合服務 API + Kafka event schema 走 consumer-driven contract test（ ）</t>
         </is>
       </c>
       <c r="G161" s="13" t="inlineStr">
@@ -35389,7 +35389,7 @@
     <row r="163" ht="36" customHeight="1">
       <c r="A163" s="13" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="B163" s="13" t="inlineStr">
@@ -35414,7 +35414,7 @@
       </c>
       <c r="F163" s="13" t="inlineStr">
         <is>
-          <t>每個 RC 以 Playwright 100% 涵蓋九條關鍵流：LINE 建案、報價同意、付款、派工 SLA、技師接拒單/到場/requote、結算退款、跨租戶拒絕、知識人工審核發布、租戶開站/License</t>
+          <t>Playwright 至少涵蓋登入、品牌後台關鍵頁、問題卡／工單主要流程、錯誤回復及技師接案→到場→完工；CI 任一關鍵案例失敗即阻擋發布</t>
         </is>
       </c>
       <c r="G163" s="13" t="inlineStr">
@@ -35424,7 +35424,7 @@
       </c>
       <c r="H163" s="13" t="inlineStr">
         <is>
-          <t>TC-NFR-Maint-008（受控 NFR 驗證設計） ｜ 驗證：E2E CI；任一關鍵流失敗即阻擋 RC</t>
+          <t>TC-NFR-Maint-008（受控 NFR 驗證設計） ｜ 驗證：E2E CI</t>
         </is>
       </c>
       <c r="I163" s="13" t="inlineStr">
@@ -35444,7 +35444,7 @@
       </c>
       <c r="L163" s="13" t="inlineStr">
         <is>
-          <t>✅ 驗收、測試設計與追溯映射已完整</t>
+          <t>⛔ 上游門檻需治理決策；不得執行通過簽核</t>
         </is>
       </c>
     </row>
@@ -35920,7 +35920,7 @@
       </c>
       <c r="H171" s="13" t="inlineStr">
         <is>
-          <t>TC-COMPLIANCE-06 ｜ 驗證：double-gate 稽核（同 NFR-Sec-009）</t>
+          <t>TC-COMPLIANCE-06 ｜ 驗證：double-阻擋條件稽核（同對應品質門檻）</t>
         </is>
       </c>
       <c r="I171" s="13" t="inlineStr">
@@ -35972,7 +35972,7 @@
       </c>
       <c r="F172" s="14" t="inlineStr">
         <is>
-          <t>forget ≤ 7d、retention 分級、visibility 驗證失敗即拒絕（§5）</t>
+          <t>forget ≤ 7d、retention 分級、visibility 驗證失敗時一律拒絕（§5）</t>
         </is>
       </c>
       <c r="G172" s="14" t="inlineStr">
@@ -36308,7 +36308,7 @@
         <is>
           <t>1. 有效簽章應受理；錯誤簽章應拒絕且不建案。
 2. 能從知識庫找到答案的問題應引用正確來源；無法回答時應詢問或轉人，不得編造。
-3. 連續 3 次未釐清或判定為急件時，應建立後台案件並轉真人。
+3. 缺項應依情境一次列齊；明確要求真人、急迫派工、金錢相關或連續兩次不滿時，應建立後台案件並轉真人，不採固定三輪計數。
 4. 不同品牌/客戶不得讀到對方對話與記憶。
 5. 同一事件重送不得重複回覆、建案或轉人。</t>
         </is>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>正常訊息有回覆且只處理一次；錯誤簽章不建案；三次未釐清與急件均建立後台案件並轉真人。 
+          <t>正常訊息有回覆且只處理一次；錯誤簽章不建案；缺項依情境一次列齊，命中明確真人、急迫派工、金錢或連續兩次不滿任一不可違反條件即建立後台案件並轉真人。 
  測試類型：功能 / 安全 / 故障恢復</t>
         </is>
       </c>
@@ -37175,7 +37175,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -37183,9 +37183,10 @@
     <col width="72" customWidth="1" min="3" max="3"/>
     <col width="68" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="58" customWidth="1" min="7" max="7"/>
-    <col width="80" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -37230,17 +37231,22 @@
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
+          <t>Code reality</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
           <t>SAD 定位</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>SDS 定位</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>能力群相關實作路徑 / 規劃狀態</t>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>實作證據路徑</t>
         </is>
       </c>
     </row>
@@ -37257,7 +37263,7 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>LINE 通道閘道：接收 webhook、驗證 X-Line-Signature、分派訊息/事件，並將回覆送回 LINE。</t>
+          <t>LINE 通道閘道：接收 webhook、驗證 X-Line-Signature、分派文字/照片/postback，並將文字與核准圖片回覆送回 LINE。</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -37270,17 +37276,22 @@
           <t>AGT·CHN</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L138–149</t>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G5" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
@@ -37289,217 +37300,242 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>AgentLoop</t>
+          <t>Photo Guide resolver</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>LockCore runtime（產品層）</t>
+          <t>品牌照片樣本圖解析器</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>產品層 Turn 狀態機：恢復 session、組上下文、執行、儲存並產生一次回覆。</t>
+          <t>解析 AI 回覆文末的 photo-guide 標記、剝除內部標記並按設定附加 LINE ImageMessage；目前只核准 Chatlock 安裝前樣本圖。</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>編排一次對話 Turn；不直接實作通用 tool-using LLM 迴圈。</t>
+          <t>只呈現預先核准的品牌靜態圖片；不讀取或辨識客戶照片，也不允許未設定品牌自行附圖。</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>AGT·CHN、AGT·RES</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L138–149 ｜ 12_SAD §4.1 L145–148</t>
+          <t>AGT·CHN</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374 ｜ 15_SDS §5.1 L367–374; §5.3</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py ｜ agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>AgentRunner</t>
+          <t>Quote postback message mapper</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>LockCore runtime（通用執行層）</t>
+          <t>報價回覆錯誤回覆內容分類器</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>通用 Agent 執行器：在有界迴圈內呼叫模型、處理 tool calls，並在每輪執行上下文治理。</t>
+          <t>依 QUOTE_EXPIRED、QUOTE_ALREADY_DECIDED、NOT_FOUND、FORBIDDEN 等 API error_code 產生對客戶可理解的 LINE 回覆。</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>不知道報價、派工等產品流程；產品狀態由 AgentLoop、Skill 與 API 約束。</t>
+          <t>只映射終態與錯誤回覆內容；報價狀態機、權限與冪等仍由品牌 API 執行。</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>AGT·CHN、AGT·GOV、AGT·RES</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L138–149 ｜ 12_SAD §4.1 L145–148 ｜ 12_SAD §4.1 L145–148; §9 L395, L407</t>
+          <t>AGT·CHN</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374 ｜ 15_SDS §5.1 L367–374; §5.3 ｜ 15_SDS §5.1 L369–374; §5.4</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py ｜ agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>ContextBuilder</t>
+          <t>WebhookIdempotencyStore</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>LockCore runtime（上下文層）</t>
+          <t>LINE webhook 冪等保留庫</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>上下文組裝器：依序組合 identity、Customer Memory、always-skills 與 skill 摘要。</t>
+          <t>在處理 LINE event 前以 mark-first 方式保留 event ID，重送時直接略過，避免重複回覆或建卡。</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>只建立模型輸入上下文；不負責永久儲存或模型供應商路由。</t>
+          <t>只治理 webhook 重播；不代替報價、工單與金流 mutation 的 Idempotency-Key。</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>AGT·KNW</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L147–149</t>
+          <t>AGT·CHN</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374</t>
-        </is>
-      </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>LiteLLMProvider + FallbackProvider</t>
+          <t>AgentLoop</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LockCore runtime（產品層）</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>模型供應商層：以 model 字串路由多家 LLM，並在主供應商失敗時切換備援。</t>
+          <t>產品層 Turn 狀態機：恢復 session、組上下文、執行、儲存並產生一次回覆。</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>處理模型呼叫、重試與備援切換；不承載業務規則或產品決策。</t>
+          <t>編排一次對話 Turn；不直接實作通用 tool-using LLM 迴圈。</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>AGT·GOV、PLT·LLM</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L145–148; §9 L395, L407 ｜ 12_SAD §4.1 L146; §9 L395, L407</t>
+          <t>AGT·CHN、AGT·RES</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §2.2 L68; §5.1 L370; §13 L707 ｜ 15_SDS §5.1 L369–374; §5.4</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/providers/{litellm_provider,fallback_provider}.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py ｜ agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>Model Orchestration Layer</t>
+          <t>AgentRunner</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LockCore runtime（通用執行層）</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>供應商無關的模型編排層：集中管理路由、備援處理、逾時、快取與呼叫效率。</t>
+          <t>通用 Agent 執行器：在有界迴圈內呼叫模型、處理 tool calls，並在每輪執行上下文治理。</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>是技術治理層，不是 Agent 產品流程、Skill 或知識庫。</t>
+          <t>不知道報價、派工等產品流程；產品狀態由 AgentLoop、Skill 與 API 約束。</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>PLT·LLM</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L146; §9 L395, L407</t>
+          <t>AGT·CHN、AGT·GOV、AGT·RES</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §2.2 L68; §5.1 L370; §13 L707</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>agent/lockcore/providers/{litellm_provider,fallback_provider}.py</t>
+          <t>12_SAD §4.1 ｜ 12_SAD §4.1、§9</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3 ｜ 15_SDS §5.1、§5.4</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py ｜ agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>ToolRegistry</t>
+          <t>ReplyGuard</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -37509,207 +37545,232 @@
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Agent 工具登錄與允許清單：定義哪些工具可被模型呼叫，並治理呼叫邊界。</t>
+          <t>Agent 回覆出口守衛：攔截確定金額、錯誤型號、假稱已轉真人等違規輸出，必要時重生或轉人工。</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>不自行決定何時呼叫工具，也不向模型暴露未登錄的任意程式。</t>
+          <t>是模型輸出的最後安全層；不取代 API 的報價、派工與權限硬閘。</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>AGT·GOV、AGT·RES</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L145–148 ｜ 12_SAD §4.1 L145–148; §9 L395, L407</t>
+          <t>AGT·RES</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3 ｜ 15_SDS §5.1 L369–374; §5.4</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>MemoryManager + Store</t>
+          <t>SentimentClassifier</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Memory</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>長期記憶管理與存儲層：載入/寫回客戶已確認事實，讀寫必須同帶 tenant_id + user_id。</t>
+          <t>在不阻斷主回覆的前提下判定負面情緒並產生警示所需資料。</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>不等於當次 session 原始對話，不可跨租戶或使用者共用。</t>
+          <t>只做情緒分類與旁路警示；不單獨決定報價、派工或工單狀態。</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>AGT·KNW</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L147–149</t>
+          <t>AGT·RES</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EscalationStore</t>
+          <t>ContextBuilder</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LockCore runtime（上下文層）</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>轉真人稽核存儲：記錄轉接理由、已知事實快照與必要追溯資料。</t>
+          <t>上下文組裝器：依序組合 identity、Customer Memory、always-skills 與 skill 摘要。</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>保證轉人事件不遺漏；不是正式工單庫，也不代替 API 的開單 gate。</t>
+          <t>只建立模型輸入上下文；不負責永久儲存或模型供應商路由。</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>AGT·RES</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L145–148</t>
+          <t>AGT·KNW</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>SkillsLoader + 2 builtin skills</t>
+          <t>LiteLLMProvider + FallbackProvider</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Agent 行為規範載入器：載入 product-knowledge 與 cs-sop，定義判斷、查資料、轉真人與不可違反條件。</t>
+          <t>模型供應商層：以 model 字串路由多家 LLM，並在主供應商失敗時切換備援。</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>管「怎麼做」；不是長期對話記憶，也不是所有長尾事實的唯一資料庫。</t>
+          <t>處理模型呼叫、重試與備援切換；不承載業務規則或產品決策。</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>AGT·GOV、AGT·KNW、REF·PUB</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L145–148; §9 L395, L407 ｜ 12_SAD §4.1 L147–149 ｜ 12_SAD §4.4 L183–187</t>
+          <t>AGT·GOV、PLT·LLM</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374 ｜ 15_SDS §5.1 L369–374; §5.4 ｜ 15_SDS §9.1 L617–619; §9.3 L631–635</t>
-        </is>
-      </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/ ｜ agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ knowledge-pipeline/refinery/; agent/lockcore/skills/*/references/</t>
+          <t>12_SAD §4.1、§9</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §2.2、§5.1、§13 ｜ 15_SDS §5.1、§5.4</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/providers/{litellm_provider,fallback_provider}.py</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>記憶 DB</t>
+          <t>Model Orchestration Layer</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>Memory backend</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>Agent 長期記憶的永久化後端，設計上使用 Postgres schema agent.*。</t>
+          <t>供應商無關的模型編排層：集中管理路由、備援處理、逾時、快取與呼叫效率。</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>只存 Agent 記憶與相關稽核；不是品牌業務庫、平台庫或技師權威庫。</t>
+          <t>是技術治理層，不是 Agent 產品流程、Skill 或知識庫。</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>AGT·KNW</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L147–149</t>
+          <t>PLT·LLM</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374</t>
-        </is>
-      </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
+          <t>12_SAD §4.1、§9</t>
+        </is>
+      </c>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §2.2、§5.1、§13</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/providers/{litellm_provider,fallback_provider}.py</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>tenant-scoped routers</t>
+          <t>ToolRegistry</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -37719,81 +37780,91 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>以 /tenants/{tid}/... 暴露品牌業務的 FastAPI 路由層，負責 HTTP 入口、輸入驗證與授權依賴。</t>
+          <t>Agent 工具登錄與允許清單：定義哪些工具可被模型呼叫，並治理呼叫邊界。</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>不在 router 堆疊主要 SQL/業務邏輯；租戶與角色檢查交給標準守衛鏈。</t>
+          <t>不自行決定何時呼叫工具，也不向模型暴露未登錄的任意程式。</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>API·CASE</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>AGT·GOV、AGT·RES</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>api/routers/; api/services/; api/core/db.py</t>
+          <t>12_SAD §4.1 ｜ 12_SAD §4.1、§9</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3 ｜ 15_SDS §5.1、§5.4</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Service Layer（problem_card / quote）</t>
+          <t>MemoryManager + Store</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Memory</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>問題卡與報價服務層：管理診斷卡 gate、報價狀態、版本與不可否認快照。</t>
+          <t>長期記憶管理與存儲層：載入/寫回客戶已確認事實，讀寫必須同帶 tenant_id + user_id；預設 SQLite，可設定 PostgreSQL。</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>不讓 Agent 或技師端直接定價；品牌 API 仍是報價權威。</t>
+          <t>不等於當次 session 原始對話，不可跨租戶或使用者共用。</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>API·CASE</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>AGT·KNW</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
-        </is>
-      </c>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>api/routers/; api/services/; api/core/db.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H17" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>Service Layer（work_order）</t>
+          <t>EscalationStore</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -37803,81 +37874,91 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>工單服務層：建立工單、驗狀態轉移/gate、寫入時間軸並觸發副作用。</t>
+          <t>轉真人稽核存儲：記錄轉接理由、已知事實快照與必要追溯資料。</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>不允許 AI 繞過客戶確認與人工審核直接轉工單。</t>
+          <t>保證轉人事件不遺漏；不是正式工單庫，也不代替 API 的開單 gate。</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>API·WO</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L397</t>
+          <t>AGT·RES</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
-        </is>
-      </c>
-      <c r="H18" s="14" t="inlineStr">
-        <is>
-          <t>api/services/work_order_service.py; api/routers/; api/core/db.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H18" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>Service Layer（dispatch）</t>
+          <t>SkillsLoader + 2 builtin skills</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>派工服務層：執行候選查詢、指派、接單 SLA、擴大範圍與狀態更新。</t>
+          <t>Agent 行為規範載入器：載入 product-knowledge 與 cs-sop，定義判斷、查資料、轉真人與不可違反條件。</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>不在品牌庫雙寫技師權威資料；媒合應經 OHS 與事件契約。</t>
+          <t>管「怎麼做」；不是長期對話記憶，也不是所有長尾事實的唯一資料庫。</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>API·DISP</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §8.1–8.2 L353–372</t>
+          <t>AGT·GOV、AGT·KNW、REF·PUB</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ PARTIAL（LiveSkill 預設路徑需 token；git 為備援處理）</t>
         </is>
       </c>
       <c r="G19" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="inlineStr">
-        <is>
-          <t>api/services/dispatch*; api/realtime/; Kafka integration</t>
+          <t>12_SAD §4.1 ｜ 12_SAD §4.1、§9 ｜ 12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H19" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1 ｜ 15_SDS §5.1、§5.4 ｜ 15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/ ｜ agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Service Layer（invoice / settlement）</t>
+          <t>SkillSync</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -37887,81 +37968,91 @@
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>帳單、收付、對帳與結算邏輯：管理金額狀態、冪等、reversal 與帳本一致性。</t>
+          <t>輪詢品牌庫已發布的 skill revision，以原子交換同步到 workspace overlay，讓新版本在執行期生效。</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Billing 真相留品牌側；跨品牌技師 Settlement 由 technician-platform 匯總。</t>
+          <t>只同步已發布版本且失敗時保留舊版；不自行核准 draft，也不覆寫平台保護層。</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>API·FIN</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L401</t>
+          <t>AGT·KNW</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560</t>
-        </is>
-      </c>
-      <c r="H20" s="14" t="inlineStr">
-        <is>
-          <t>api/services/{invoice,settlement}*; api/core/db.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>core/db.py</t>
+          <t>記憶 DB</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Memory backend</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>API 資料庫基礎層：管理連線池、交易邊界與讀寫分離。</t>
+          <t>Agent 長期記憶的永久化後端，設計上使用 Postgres schema agent.*。</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>不放領域流程決策；業務交易應由 service 層呼叫。</t>
+          <t>只存 Agent 記憶與相關稽核；不是品牌業務庫、平台庫或技師權威庫。</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>API·CASE、API·FIN、API·WO、DAT·SCH</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164 ｜ 12_SAD §4.2 L151–164; §9 L397 ｜ 12_SAD §4.2 L151–164; §9 L401 ｜ 12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>AGT·KNW</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451 ｜ 15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466 ｜ 15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472 ｜ 15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/platform/Schema_platform.sql ｜ api/routers/; api/services/; api/core/db.py ｜ api/services/work_order_service.py; api/routers/; api/core/db.py ｜ api/services/{invoice,settlement}*; api/core/db.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>internal_ingest.py</t>
+          <t>tenant-scoped routers</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
@@ -37971,39 +38062,44 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Agent 與內部服務使用的 /internal/* 入口，接收對話、轉人與報價回應等旁路資料。</t>
+          <t>以 /tenants/{tid}/... 暴露品牌業務的 FastAPI 路由層，負責 HTTP 入口、輸入驗證與授權依賴。</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>只接受驗證失敗即拒絕內部憑證；不是 LINE webhook 入站門。</t>
+          <t>不在 router 堆疊主要 SQL/業務邏輯；租戶與角色檢查交給標準守衛鏈。</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>API·INT</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>API·CASE</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H22" s="14" t="inlineStr">
-        <is>
-          <t>api/routers/internal_ingest.py; api/realtime/; api/services/line_push_service*</t>
+          <t>12_SAD §4.2</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>WebSocket 端點</t>
+          <t>Service Layer（problem_card / quote）</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
@@ -38013,81 +38109,91 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>經授權的即時推播連線入口，依 channel、技師與租戶將狀態更新送給前端。</t>
+          <t>問題卡與報價服務層：管理診斷卡 gate、報價狀態、版本與不可否認快照。</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>是即時通知管道，不是業務事件的永久真相；斷線時頁面應可退化為 REST。</t>
+          <t>不讓 Agent 或技師端直接定價；品牌 API 仍是報價權威。</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>API·INT、PLT·EVT、TEC·MATCH、TEC·PROJ</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164 ｜ 12_SAD §4.2 L164; §8.1–8.2 L353–372; §9 L394 ｜ 12_SAD §4.5 L189–197 ｜ 12_SAD §4.5 L193–197; §8.2 L369, L372</t>
+          <t>API·CASE</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548 ｜ 15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677 ｜ 15_SDS §6.1 L453–466; §6.3 L484–492; §11 L648–677 ｜ 15_SDS §7.1 L513–518; §7.3 L554–560; §11.1 L648–660</t>
-        </is>
-      </c>
-      <c r="H23" s="13" t="inlineStr">
-        <is>
-          <t>api/realtime/; Kafka/Redis integration ｜ api/routers/internal_ingest.py; api/realtime/; api/services/line_push_service* ｜ technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.2</t>
+        </is>
+      </c>
+      <c r="H23" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>Redis pub/sub</t>
+          <t>Conversation media collector</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>對話照片掛卡器</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>跨實例的低延遲訊息擴散，用於 WebSocket fan-out、cache 與部分分散式鎖。</t>
+          <t>AI 建問題卡時反查同一對話近 24 小時內最多 5 張照片，依時間排序附加到 media_urls。</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>不保證長期持久與重播；需重播的事件應使用 Kafka 或資料庫。</t>
+          <t>只掛接已持久化媒體 URL，採 append-only 且查詢失敗略過；不做任何影像辨識。</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>API·DISP、API·INT、PLT·EVT</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164 ｜ 12_SAD §4.2 L151–164; §8.1–8.2 L353–372 ｜ 12_SAD §4.2 L164; §8.1–8.2 L353–372; §9 L394</t>
+          <t>API·CASE</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677 ｜ 15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660 ｜ 15_SDS §6.1 L453–466; §6.3 L484–492; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H24" s="14" t="inlineStr">
-        <is>
-          <t>api/realtime/; Kafka/Redis integration ｜ api/routers/internal_ingest.py; api/realtime/; api/services/line_push_service* ｜ api/services/dispatch*; api/realtime/; Kafka integration</t>
+          <t>12_SAD §4.2</t>
+        </is>
+      </c>
+      <c r="H24" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Service Layer（work_order）</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
@@ -38097,81 +38203,91 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>持久、可重播的跨系統事件骨幹，傳遞 technician.*、dispatch.*、workorder.* 與 commission.* 等事件。</t>
+          <t>工單服務層：建立工單、驗狀態轉移/gate、寫入時間軸並觸發副作用。</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>不代替低延遲同步查詢（OHS/REST），也不代替各領域真相資料庫。</t>
+          <t>不允許 AI 繞過客戶確認與人工審核直接轉工單。</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>API·DISP、API·FIN、API·INT、DAT·SYNC、PLT·EVT、TEC·SET</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164 ｜ 12_SAD §4.2 L151–164; §8.1–8.2 L353–372 ｜ 12_SAD §4.2 L151–164; §9 L401 ｜ 12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372 ｜ 12_SAD §4.2 L164; §8.1–8.2 L353–372; §9 L394 ｜ 12_SAD §4.5 L189–197; §9 L401</t>
+          <t>API·WO</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560 ｜ 15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677 ｜ 15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660 ｜ 15_SDS §6.1 L453–466; §6.3 L484–492; §11 L648–677 ｜ 15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677 ｜ 15_SDS §7.1 L515–518; §7.3 L554–560; §11.1 L648–660</t>
-        </is>
-      </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>api/realtime/; Kafka/Redis integration ｜ api/routers/internal_ingest.py; api/realtime/; api/services/line_push_service* ｜ api/services/dispatch*; api/realtime/; Kafka integration ｜ api/services/{invoice,settlement}*; api/core/db.py ｜ knowledge-pipeline/; api/realtime/; Kafka integration ｜ technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H25" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>分散式排程</t>
+          <t>Consent link service</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>免責同意簽署連結服務</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>跨實例協調 SLA、GDPR 永久刪除、自動結案與 LINE outbox 等背景工作，並以鎖避免重複執行。</t>
+          <t>為工單產生公開簽署 token、保存 token hash 稽核並透過 LINE 推送；無 LINE 綁定時回傳可複製連結。</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>只觸發已定義任務；不把關鍵業務真相只留在 scheduler 記憶體。</t>
+          <t>只負責交付簽署入口與稽核；簽署內容、角色/租戶授權與結案 gate 仍由 API 驗證。</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>API·DISP、PLT·EVT</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §8.1–8.2 L353–372 ｜ 12_SAD §4.2 L164; §8.1–8.2 L353–372; §9 L394</t>
+          <t>API·WO</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660 ｜ 15_SDS §6.1 L453–466; §6.3 L484–492; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H26" s="14" t="inlineStr">
-        <is>
-          <t>api/realtime/; Kafka/Redis integration ｜ api/services/dispatch*; api/realtime/; Kafka integration</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>line_push_service + outbox worker</t>
+          <t>Service Layer（dispatch）</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
@@ -38181,81 +38297,91 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>LINE 出站推播與可重試佇列：業務交易先寫 outbox，worker 後送並記錄結果。</t>
+          <t>派工服務層：執行候選查詢、指派、接單 SLA、擴大範圍與狀態更新。</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>推播失敗不還原主業務寫入；不處理 LINE 入站 webhook。</t>
+          <t>不在品牌庫雙寫技師權威資料；媒合應經 OHS 與事件契約。</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>API·INT</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>API·DISP</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G27" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H27" s="13" t="inlineStr">
-        <is>
-          <t>api/routers/internal_ingest.py; api/realtime/; api/services/line_push_service*</t>
+          <t>12_SAD §4.2、§8</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>守衛鏈</t>
+          <t>dispatch_service candidate scoring</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>現行媒合評分器</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>API 授權鏈：get_current_user → require_tenant → role_required，加上 platform admin 與 internal token 邊界。</t>
+          <t>現行派工服務直接由技師權威資料評估技能、品牌授權、距離、評分、工作量與公平性，產生候選排序。</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>逐端點預設拒絕 enforce；不把前端隱藏按鈕當成安全控制。</t>
+          <t>這是共用 API codebase 的 interim 實作；目標 OHS/MatchingService 獨立服務邊界尚未拆出。</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>API·GOV、PLT·IAM、TEC·ID</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L393 ｜ 12_SAD §4.5 L189–197 ｜ 12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>API·DISP、TEC·MATCH</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（媒合已實作；獨立 OHS 邊界未拆）</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670 ｜ 15_SDS §6.1 L428–472; §6.4 L494–499 ｜ 15_SDS §7.1 L503–518; §7.2 L550–552</t>
-        </is>
-      </c>
-      <c r="H28" s="14" t="inlineStr">
-        <is>
-          <t>api/core/{deps,errors,idempotency,auth,pii_crypto}.py; api/main.py ｜ technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認） ｜ web/platform-console; api platform surface; Casdoor deployment/config</t>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§8</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §6.1、§6.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/ ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>core/errors.py</t>
+          <t>Service Layer（invoice / settlement）</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
@@ -38265,39 +38391,44 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>API 錯誤標準化元件：將例外轉為 RFC7807 problem+json 相容信封。</t>
+          <t>帳單、收付、對帳與結算邏輯：管理金額狀態、冪等、reversal 與帳本一致性。</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>統一錯誤呈現與分類；不吞掉必須中斷的安全或交易錯誤。</t>
+          <t>Billing 真相留品牌側；跨品牌技師 Settlement 由 technician-platform 匯總。</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>API·GOV</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L393</t>
+          <t>API·FIN</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（跨系統事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G29" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L428–472; §6.4 L494–499</t>
-        </is>
-      </c>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>api/core/{deps,errors,idempotency,auth,pii_crypto}.py; api/main.py</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H29" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §4.2、§6.1、§7.3</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>core/idempotency.py</t>
+          <t>core/db.py</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
@@ -38307,123 +38438,138 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Mutation 冪等控制：以 Idempotency-Key 辨識重播，避免重複開單、收款或狀態轉移。</t>
+          <t>API 資料庫基礎層：管理品牌庫、技師權威庫與平台庫的連線取得、交易邊界及安全備援處理。</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>只保護重播語意；不代替業務狀態機與資料庫唯一約束。</t>
+          <t>不放領域流程決策；業務交易應由 service 層呼叫。</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>API·GOV</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L393</t>
+          <t>API·CASE、API·FIN、API·WO、DAT·SCH</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ PARTIAL（跨系統事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L428–472; §6.4 L494–499</t>
-        </is>
-      </c>
-      <c r="H30" s="14" t="inlineStr">
-        <is>
-          <t>api/core/{deps,errors,idempotency,auth,pii_crypto}.py; api/main.py</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.6 ｜ 12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §3.1、§6.1 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1 ｜ 15_SDS §4.2、§4.6、§6.1 ｜ 15_SDS §4.2、§6.1、§7.3</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py ｜ api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py ｜ api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py ｜ api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>Middleware</t>
+          <t>API_SURFACE router filter</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>API 部署面塑形器</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>FastAPI 橫切處理鏈：處理 CORS、Request ID、版本廢棄等全局請求/回應邏輯。</t>
+          <t>同一 FastAPI codebase 依 API_SURFACE=dispatch/tech/platform 裁切路由與背景 worker，形成三個可獨立部署面。</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>不承載單一領域的核心業務規則。</t>
+          <t>只縮小部署暴露面，不是授權邊界；每個保留端點仍須 RBAC、租戶或平台守衛。</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>API·GOV</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L393</t>
+          <t>API·GOV、TEC·ID</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase）</t>
         </is>
       </c>
       <c r="G31" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L428–472; §6.4 L494–499</t>
-        </is>
-      </c>
-      <c r="H31" s="13" t="inlineStr">
-        <is>
-          <t>api/core/{deps,errors,idempotency,auth,pii_crypto}.py; api/main.py</t>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4 ｜ 15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>AuthGuard</t>
+          <t>Three-DB Connection Router</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>三庫連線路由</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Web 根佈局的前端路由守衛：先做跨站導向，再檢查 token 與角色存取。</t>
+          <t>依資料權威將連線導向品牌庫、lock_tech 或 lock_platform，並可用 DB_URI_STRICT 阻止必要 URI 缺失時啟動。</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>只是 UX 層門禁；真正授權必須由 API 守衛鏈 enforce。</t>
+          <t>治理資料庫選擇與驗證失敗即拒絕；不代表 production migration 或 backfill 已完成。</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>WEB·SHELL</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·GOV</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599</t>
-        </is>
-      </c>
-      <c r="H32" s="14" t="inlineStr">
-        <is>
-          <t>web/src/components/layout/AuthGuard.tsx; web/src/lib/{appMode,rolePolicy}.ts</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>appMode gate</t>
+          <t>DBPoolScopeMiddleware</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
@@ -38433,81 +38579,91 @@
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>判斷當前 portal build 是否服務某路徑，不屬於本站的路徑導向對應 portal。</t>
+          <t>在 request 生命週期建立與回收資料庫 pool scope，避免跨請求連線狀態滲漏。</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>是分站與導航控制，不是後端租戶或角色安全邊界。</t>
+          <t>只治理連線資源生命週期；不決定資料權威或業務交易內容。</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>WEB·SHELL</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·GOV</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G33" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599</t>
-        </is>
-      </c>
-      <c r="H33" s="13" t="inlineStr">
-        <is>
-          <t>web/src/components/layout/AuthGuard.tsx; web/src/lib/{appMode,rolePolicy}.ts</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H33" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>rolePolicy</t>
+          <t>DEKService + PII blind index + purge ledger</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>個資密鑰與清除稽核套件</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>前端 route→roles 最長前綴政策表，控制導航與無權使用者的安全落點。</t>
+          <t>以每使用者 DEK、blind index 與 append-only purge ledger 支援個資查找、加密、忘卻與清除證據。</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>只提供前端 UX 治理；不代替 API role_required。</t>
+          <t>程式與 migration 存在不等於正式 KEK、backfill 與 production 部署已驗證。</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>WEB·AUD、WEB·SHELL</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·GOV</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G34" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599 ｜ 15_SDS §8.1 L570–578</t>
-        </is>
-      </c>
-      <c r="H34" s="14" t="inlineStr">
-        <is>
-          <t>web/src/components/layout/AuthGuard.tsx; web/src/lib/{appMode,rolePolicy}.ts ｜ web/src/lib/{rolePolicy,api}.ts; web/types/api.generated.ts</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>api client</t>
+          <t>internal_ingest.py</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
@@ -38517,39 +38673,44 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>Web 統一 HTTP client：注入 Bearer、X-Tenant-ID、Idempotency-Key，處理 refresh 與錯誤信封。</t>
+          <t>Agent 與內部服務使用的 /internal/* 入口，接收對話、轉人與報價回應等旁路資料。</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>不在瀏覽器內繞過 API 授權，也不將客戶端狀態當作服務端真相。</t>
+          <t>只接受驗證失敗即拒絕內部憑證；不是 LINE webhook 入站門。</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>WEB·AUD、WEB·CX、WEB·OPS</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·INT</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G35" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L570–578 ｜ 15_SDS §8.1 L575–578; §8.3 L593–599</t>
-        </is>
-      </c>
-      <c r="H35" s="13" t="inlineStr">
-        <is>
-          <t>web/src/lib/{api,cache,realtime}.ts ｜ web/src/lib/{rolePolicy,api}.ts; web/types/api.generated.ts</t>
+          <t>12_SAD §4.2</t>
+        </is>
+      </c>
+      <c r="H35" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1–6.3、§11</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>cache</t>
+          <t>WebSocket 端點</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
@@ -38559,39 +38720,44 @@
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Web GET 請求共享 in-flight 與短期 staleTime 快取，mutation 後可主動失效。</t>
+          <t>經授權的即時推播連線入口，依 channel、技師與租戶將狀態更新送給前端。</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>是前端效能優化；不是永久資料庫或授權依據。</t>
+          <t>是即時通知管道，不是業務事件的永久真相；斷線時頁面應可退化為 REST。</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>WEB·CX、WEB·OPS</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·INT、PLT·EVT、TEC·MATCH、TEC·PROJ</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用） ｜ PARTIAL（媒合已實作；獨立 OHS 邊界未拆）</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L575–578; §8.3 L593–599</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>web/src/lib/{api,cache,realtime}.ts</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§8–9 ｜ 12_SAD §4.5、§8.2</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>realtime</t>
+          <t>Redis pub/sub</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
@@ -38601,39 +38767,44 @@
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>WebSocket 訂閱層：一 channel 一 socket、處理重連 backoff，未設定時靜默降級。</t>
+          <t>跨實例的低延遲訊息擴散，用於 WebSocket fan-out、cache 與部分分散式鎖。</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>負責前端即時連線生命週期；不是事件持久層。</t>
+          <t>不保證長期持久與重播；需重播的事件應使用 Kafka 或資料庫。</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>WEB·CX、WEB·OPS</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·DISP、API·INT、PLT·EVT</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G37" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L575–578; §8.3 L593–599</t>
-        </is>
-      </c>
-      <c r="H37" s="13" t="inlineStr">
-        <is>
-          <t>web/src/lib/{api,cache,realtime}.ts</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9</t>
+        </is>
+      </c>
+      <c r="H37" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>型別（api.generated.ts）</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
@@ -38643,39 +38814,44 @@
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>由 OpenAPI 生成的 TypeScript API 型別，使前端在編譯期偵測契約漂移。</t>
+          <t>持久、可重播的跨系統事件骨幹；現行 producer/consumer 實作 topic 為 workorder.lifecycle、commission.accrued、technician.lifecycle。</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>反映契約但不定義業務真相；不手改生成檔來代替 OpenAPI。</t>
+          <t>不代替低延遲同步查詢（OHS/REST），也不代替各領域真相資料庫。</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>WEB·AUD</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·DISP、API·FIN、API·INT、DAT·SYNC、PLT·EVT、TEC·SET</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in） ｜ PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用） ｜ PARTIAL（投影與跨品牌事件依 Kafka 啟用） ｜ PARTIAL（跨系統事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L570–578</t>
-        </is>
-      </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>web/src/lib/{rolePolicy,api}.ts; web/types/api.generated.ts</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.6、§8.2 ｜ 12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9 ｜ 12_SAD §4.2、§9 ｜ 12_SAD §4.5、§9</t>
+        </is>
+      </c>
+      <c r="H38" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §4.2、§6.1、§7.3 ｜ 15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1 ｜ 15_SDS §6.3–6.4、§9.3、§11 ｜ 15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py ｜ api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py ｜ api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql ｜ knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>Medallion pipeline</t>
+          <t>EventBusProducer</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
@@ -38685,39 +38861,44 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>離線資料流水線：將素材依 raw→bronze→silver 分層處理，保留來源與可重現性。</t>
+          <t>將受控領域事件序列化並發布到 Kafka；未設定 KAFKA_BOOTSTRAP 時按設計不啟用。</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>是 batch 與持久資產，不是長駐即時 API runtime。</t>
+          <t>只發布已定義 topic 的事件；不保證所有設計中的萬用 wildcard topic 均已實作。</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>DAT·SYNC</t>
-        </is>
-      </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372</t>
+          <t>API·INT</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G39" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H39" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/; api/realtime/; Kafka integration</t>
+          <t>12_SAD §4.2</t>
+        </is>
+      </c>
+      <c r="H39" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1–6.3、§11</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>source_to_raw</t>
+          <t>EventConsumerWorker</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
@@ -38727,39 +38908,44 @@
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>收集原始外部素材並原樣實作到 raw 層，保留來源識別與取得資訊。</t>
+          <t>消費 Kafka 工單生命週期與佣金事件，使用 event_consumer_dedup 冪等更新技師 CQRS 投影。</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>不宣告內容已清洗或可直接用於 Agent 回答。</t>
+          <t>需 KAFKA_BOOTSTRAP 才啟動；不把 projection 當成品牌工單或計費的命令真相。</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>DAT·MED</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.6 L199–208</t>
+          <t>TEC·PROJ、TEC·SET</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L611–613; 附錄 L736</t>
-        </is>
-      </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
+          <t>12_SAD §4.5、§8.2 ｜ 12_SAD §4.5、§9</t>
+        </is>
+      </c>
+      <c r="H40" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>raw_to_bronze</t>
+          <t>分散式排程</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
@@ -38769,39 +38955,44 @@
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>將 raw 影音、網頁或文件轉錄與清洗為可審查的 bronze 素材。</t>
+          <t>跨實例協調 SLA、GDPR 永久刪除、自動結案與 LINE outbox 等背景工作，並以鎖避免重複執行。</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>只做可追溯轉換；不將未審核內容直接發布至知識庫。</t>
+          <t>只觸發已定義任務；不把關鍵業務真相只留在 scheduler 記憶體。</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>DAT·MED、REF·INTAKE</t>
-        </is>
-      </c>
-      <c r="F41" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L179–187 ｜ 12_SAD §4.6 L199–208</t>
+          <t>API·DISP、PLT·EVT</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in）</t>
         </is>
       </c>
       <c r="G41" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L603–613; §9.3 L631–635 ｜ 15_SDS §9.1 L611–613; 附錄 L736</t>
-        </is>
-      </c>
-      <c r="H41" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/ ｜ knowledge-pipeline/refinery/; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
+          <t>12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9</t>
+        </is>
+      </c>
+      <c r="H41" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>bronze_to_silver</t>
+          <t>PG Advisory Cron Leader</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
@@ -38811,39 +39002,44 @@
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>將 bronze 去冗、糾錯、語意切塊成 silver，並由程式覆寫 provenance 防止 LLM 幻覺來源。</t>
+          <t>以 PostgreSQL advisory lock 選出單一排程 leader，避免多實例重複執行背景工作。</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>silver 不等於已核可發布；下游仍需提煉、人工審核與 Publisher gate。</t>
+          <t>只協調任務執行權；不取代任務本身的冪等、重試與稽核。</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>DAT·MED、REF·INTAKE</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L179–187 ｜ 12_SAD §4.6 L199–208</t>
+          <t>API·DISP</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G42" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L603–613; §9.3 L631–635 ｜ 15_SDS §9.1 L611–613; 附錄 L736</t>
-        </is>
-      </c>
-      <c r="H42" s="14" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/ ｜ knowledge-pipeline/refinery/; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
+          <t>12_SAD §4.2、§8</t>
+        </is>
+      </c>
+      <c r="H42" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>storage（raw/bronze/silver）</t>
+          <t>line_push_service + outbox worker</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
@@ -38853,39 +39049,44 @@
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>Medallion 各分層的持久檔案資產，保留原始、可審查與結構化中間成果。</t>
+          <t>LINE 出站推播與可重試佇列：業務交易先寫 outbox，worker 後送並記錄結果。</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>是 pipeline 資產庫；不等於線上 pgvector 查詢庫。</t>
+          <t>推播失敗不還原主業務寫入；不處理 LINE 入站 webhook。</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>DAT·MED</t>
-        </is>
-      </c>
-      <c r="F43" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.6 L199–208</t>
+          <t>API·INT</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G43" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L611–613; 附錄 L736</t>
-        </is>
-      </c>
-      <c r="H43" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
+          <t>12_SAD §4.2</t>
+        </is>
+      </c>
+      <c r="H43" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1–6.3、§11</t>
+        </is>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql</t>
+          <t>守衛鏈</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
@@ -38895,39 +39096,44 @@
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>資料庫基底 schema 定義，描述主表、索引與基礎約束。</t>
+          <t>API 授權鏈：get_current_user → require_tenant → role_required，加上 platform admin 與 internal token 邊界。</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>不直接代替已上線環境的 forward-only migration 演進記錄。</t>
+          <t>逐端點預設拒絕 enforce；不把前端隱藏按鈕當成安全控制。</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>DAT·SCH</t>
-        </is>
-      </c>
-      <c r="F44" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>API·GOV、PLT·IAM、TEC·ID</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase） ｜ PARTIAL（Casdoor/config 存在；環境開通設定未完整）</t>
         </is>
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451</t>
-        </is>
-      </c>
-      <c r="H44" s="14" t="inlineStr">
-        <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/platform/Schema_platform.sql</t>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§9 ｜ 12_SAD §8.2–8.3、§9</t>
+        </is>
+      </c>
+      <c r="H44" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§6.1、§11.2 ｜ 15_SDS §6.1、§6.4 ｜ 15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/ ｜ web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>forward-only migrations</t>
+          <t>core/errors.py</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
@@ -38937,39 +39143,44 @@
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>只向前套用、有順序與可稽核性的 SQL schema 變更集。</t>
+          <t>API 錯誤標準化元件：將例外轉為 RFC7807 problem+json 相容信封。</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>不靠手改 production schema；漂移與重複套用必須由 CI/測試阻擋。</t>
+          <t>統一錯誤呈現與分類；不吞掉必須中斷的安全或交易錯誤。</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>DAT·SCH</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>API·GOV</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G45" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451</t>
-        </is>
-      </c>
-      <c r="H45" s="13" t="inlineStr">
-        <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/platform/Schema_platform.sql</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H45" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4</t>
+        </is>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>platform schema</t>
+          <t>core/idempotency.py</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
@@ -38979,39 +39190,44 @@
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>平台治理庫的獨立 schema，存管理員、品牌申請等跨租戶管理資料。</t>
+          <t>Mutation 冪等控制：以 Idempotency-Key 辨識重播，避免重複開單、收款或狀態轉移。</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>不存單一品牌內的工單、客戶或報價真相。</t>
+          <t>只保護重播語意；不代替業務狀態機與資料庫唯一約束。</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>DAT·SCH</t>
-        </is>
-      </c>
-      <c r="F46" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>API·GOV</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451</t>
-        </is>
-      </c>
-      <c r="H46" s="14" t="inlineStr">
-        <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/platform/Schema_platform.sql</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H46" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>MCP RAG server</t>
+          <t>Middleware</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
@@ -39021,39 +39237,44 @@
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>以 MCP 工具契約向 Agent 暴露產品手冊與相似案例的租戶授權檢索服務。</t>
+          <t>FastAPI 橫切處理鏈：處理 CORS、Request ID、版本廢棄等全局請求/回應邏輯。</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>只負責事實檢索；不定義 Agent 行為，也不允許無 tenant ACL 直查 DB。</t>
+          <t>不承載單一領域的核心業務規則。</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>DAT·RAG</t>
-        </is>
-      </c>
-      <c r="F47" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §8.1 L353–361; §9 L407</t>
+          <t>API·GOV</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G47" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L376; §9.1 L617–619; §11.3 L677</t>
-        </is>
-      </c>
-      <c r="H47" s="13" t="inlineStr">
-        <is>
-          <t>rag MCP service; SQL migrations; knowledge-pipeline/refinery/</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H47" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4</t>
+        </is>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>品牌庫 pgvector</t>
+          <t>AuthGuard</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
@@ -39063,39 +39284,44 @@
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>每品牌物理隔離的 PostgreSQL/pgvector，存業務資料與該品牌唯一事實語料。</t>
+          <t>Web 根佈局的前端路由守衛：先做跨站導向，再檢查 token 與角色存取。</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>不跨品牌共用記錄；技師權威資料仍在 lock_tech。</t>
+          <t>只是 UX 層門禁；真正授權必須由 API 守衛鏈 enforce。</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>DAT·RAG、REF·PUB</t>
-        </is>
-      </c>
-      <c r="F48" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L183–187 ｜ 12_SAD §8.1 L353–361; §9 L407</t>
+          <t>WEB·SHELL</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
         </is>
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L376; §9.1 L617–619; §11.3 L677 ｜ 15_SDS §9.1 L617–619; §9.3 L631–635</t>
-        </is>
-      </c>
-      <c r="H48" s="14" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/refinery/; agent/lockcore/skills/*/references/ ｜ rag MCP service; SQL migrations; knowledge-pipeline/refinery/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H48" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1–8.3</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
         </is>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>rag_manual_chunks / case_entries</t>
+          <t>appMode gate</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
@@ -39105,39 +39331,44 @@
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>RAG 的手冊切塊與案例條目，帶租戶/品牌過濾、embedding 與 provenance。</t>
+          <t>判斷當前 portal build 是否服務某路徑，不屬於本站的路徑導向對應 portal。</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>是被查找的事實資料；不是 Skill 行為規範或對話 Memory。</t>
+          <t>是分站與導航控制，不是後端租戶或角色安全邊界。</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>DAT·RAG</t>
-        </is>
-      </c>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §8.1 L353–361; §9 L407</t>
+          <t>WEB·SHELL</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
         </is>
       </c>
       <c r="G49" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L376; §9.1 L617–619; §11.3 L677</t>
-        </is>
-      </c>
-      <c r="H49" s="13" t="inlineStr">
-        <is>
-          <t>rag MCP service; SQL migrations; knowledge-pipeline/refinery/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H49" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1–8.3</t>
+        </is>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
         </is>
       </c>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>outbox</t>
+          <t>rolePolicy</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
@@ -39147,39 +39378,44 @@
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>與主業務交易同步寫入的待發送記錄，由 worker 重試投遞通知或事件。</t>
+          <t>前端 route→roles 最長前綴政策表，控制導航與無權使用者的安全落點。</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>解耦交易與外部副作用；不代替 Kafka 的跨系統長期事件紀錄。</t>
+          <t>只提供前端 UX 治理；不代替 API role_required。</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>DAT·SYNC</t>
-        </is>
-      </c>
-      <c r="F50" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372</t>
+          <t>WEB·AUD、WEB·SHELL</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
         </is>
       </c>
       <c r="G50" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/; api/realtime/; Kafka integration</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H50" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1 ｜ 15_SDS §8.1–8.3</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts ｜ web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
         </is>
       </c>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>provenance / audit</t>
+          <t>api client</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
@@ -39189,123 +39425,138 @@
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>記錄資料來源、處理版本、行為者與時間的可重現與稽核證據。</t>
+          <t>Web 統一 HTTP client：注入 Bearer、X-Tenant-ID、Idempotency-Key，處理 refresh 與錯誤信封。</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>不允許 LLM 自行編造來源，也不把一般顯示紀錄當成不可否認稽核鏈。</t>
+          <t>不在瀏覽器內繞過 API 授權，也不將客戶端狀態當作服務端真相。</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>DAT·SYNC</t>
-        </is>
-      </c>
-      <c r="F51" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372</t>
+          <t>WEB·AUD、WEB·CX、WEB·OPS</t>
+        </is>
+      </c>
+      <c r="F51" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G51" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/; api/realtime/; Kafka integration</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H51" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1 ｜ 15_SDS §8.1、§8.3</t>
+        </is>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx} ｜ web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts</t>
         </is>
       </c>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>汲取層</t>
+          <t>AuthImage / AuthImageLightbox</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>需認證媒體縮圖與預覽</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>知識精煉入口：收集 knowledge_ready 診斷卡與外部產品素材。</t>
+          <t>對相對媒體 URL 以 Bearer + X-Tenant-ID fetch 後建立 Blob URL，統一呈現縮圖、錯誤佔位與放大預覽。</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>只撿取符合租戶與完整度 gate 的輸入；不直接發布到 Agent。</t>
+          <t>只在品牌後台呈現受保護圖片；不把 token 放進 img src，也不繞過媒體 API 授權。</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>REF·INTAKE</t>
-        </is>
-      </c>
-      <c r="F52" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L179–187</t>
+          <t>WEB·CX、WEB·OPS</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L603–613; §9.3 L631–635</t>
-        </is>
-      </c>
-      <c r="H52" s="14" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/refinery/; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H52" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1、§8.3</t>
+        </is>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
         </is>
       </c>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>提煉分流器</t>
+          <t>ConsentPanel</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>工單免責同意面板</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>將 silver 內容分為「可查找的事實」與「Agent 怎麼做的行為」兩條軌。</t>
+          <t>品牌工作台顯示三段免責同意狀態，並讓授權人員發送或複製客戶簽署連結。</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>只產生 draft；未經人工審核核可不得寫入 pgvector 或 Skill。</t>
+          <t>是操作與狀態顯示元件；不在前端自行判定簽署有效性或結案。</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>REF·REFINE</t>
-        </is>
-      </c>
-      <c r="F53" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>WEB·CX、WEB·OPS</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G53" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L614–615; §9.3 L631–635</t>
-        </is>
-      </c>
-      <c r="H53" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/refinery/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H53" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1、§8.3</t>
+        </is>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
         </is>
       </c>
     </row>
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Draft Queue</t>
+          <t>cache</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
@@ -39315,39 +39566,44 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>事實 draft 與行為 diff 的審核佇列，包含來源、冪等鍵與狀態機。</t>
+          <t>Web GET 請求共享 in-flight 與短期 staleTime 快取，mutation 後可主動失效。</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>是待審產物，不是已發布知識。</t>
+          <t>是前端效能優化；不是永久資料庫或授權依據。</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>REF·人工審核、REF·REFINE</t>
-        </is>
-      </c>
-      <c r="F54" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>WEB·CX、WEB·OPS</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L614–615; §9.3 L631–635 ｜ 15_SDS §9.1 L615–616; §9.2 L621–629</t>
-        </is>
-      </c>
-      <c r="H54" s="14" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/refinery/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H54" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1、§8.3</t>
+        </is>
+      </c>
+      <c r="I54" s="14" t="inlineStr">
+        <is>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
         </is>
       </c>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>審核 UI backend</t>
+          <t>realtime</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
@@ -39357,39 +39613,44 @@
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>提供 draft 狀態轉移、diff 呈現、核可、駁回與 re-refine 的人工審核後端。</t>
+          <t>WebSocket 訂閱層：一 channel 一 socket、處理重連 backoff，未設定時靜默降級。</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>不自動把 LLM 產物當真相；核可與發布仍是兩個可稽核步驟。</t>
+          <t>負責前端即時連線生命週期；不是事件持久層。</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>REF·人工審核</t>
-        </is>
-      </c>
-      <c r="F55" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>WEB·CX、WEB·OPS</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G55" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L615–616; §9.2 L621–629</t>
-        </is>
-      </c>
-      <c r="H55" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/refinery/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H55" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1、§8.3</t>
+        </is>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
         </is>
       </c>
     </row>
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>Publisher</t>
+          <t>型別（api.generated.ts）</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
@@ -39399,39 +39660,44 @@
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>核可後的雙軌發布器：事實 embed 後寫 pgvector；行為產生 append-only Skill patch/產出檔。</t>
+          <t>由 OpenAPI 生成的 TypeScript API 型別，使前端在編譯期偵測契約漂移。</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>只發布 approved draft；不跳過 provenance、tenant 過濾或人工審核 gate。</t>
+          <t>反映契約但不定義業務真相；不手改生成檔來代替 OpenAPI。</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>REF·PUB</t>
-        </is>
-      </c>
-      <c r="F56" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>WEB·AUD</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G56" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L617–619; §9.3 L631–635</t>
-        </is>
-      </c>
-      <c r="H56" s="14" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/refinery/; agent/lockcore/skills/*/references/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H56" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1</t>
+        </is>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts</t>
         </is>
       </c>
     </row>
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>self-service routers</t>
+          <t>Medallion pipeline</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
@@ -39441,39 +39707,44 @@
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>技師端自助 API：註冊、profile、技能/品牌授權、認證上傳、排班與工作台。</t>
+          <t>離線資料流水線：將素材依 raw→bronze→silver 分層處理，保留來源與可重現性。</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>只服務已驗證的技師生命週期；不暴露跨租戶品牌內部資料。</t>
+          <t>是 batch 與持久資產，不是長駐即時 API runtime。</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
-        </is>
-      </c>
-      <c r="F57" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·SYNC</t>
+        </is>
+      </c>
+      <c r="F57" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in）</t>
         </is>
       </c>
       <c r="G57" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
-        </is>
-      </c>
-      <c r="H57" s="13" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
+        </is>
+      </c>
+      <c r="H57" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
+        </is>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>technician_service</t>
+          <t>source_to_raw</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
@@ -39483,39 +39754,44 @@
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>技師身分、技能、品牌授權、停復權與評分等核心領域服務。</t>
+          <t>收集原始外部素材並原樣實作到 raw 層，保留來源識別與取得資訊。</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>真相寫入 lock_tech；不雙寫各品牌庫。</t>
+          <t>不宣告內容已清洗或可直接用於 Agent 回答。</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
-        </is>
-      </c>
-      <c r="F58" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·MED</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G58" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
-        </is>
-      </c>
-      <c r="H58" s="14" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.6</t>
+        </is>
+      </c>
+      <c r="H58" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1；附錄</t>
+        </is>
+      </c>
+      <c r="I58" s="14" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
         </is>
       </c>
     </row>
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>certification/kyc_service</t>
+          <t>raw_to_bronze</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
@@ -39525,39 +39801,44 @@
       </c>
       <c r="C59" s="13" t="inlineStr">
         <is>
-          <t>技師 KYC 與認證申請/審核服務，對敏感欄位加密並控制准入。</t>
+          <t>將 raw 影音、網頁或文件轉錄與清洗為可審查的 bronze 素材。</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>未核可或已失效認證不得進入媒合候選集。</t>
+          <t>只做可追溯轉換；不將未審核內容直接發布至知識庫。</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
-        </is>
-      </c>
-      <c r="F59" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·MED、REF·INTAKE</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ PARTIAL（批次 CLI，尚無排程部署）</t>
         </is>
       </c>
       <c r="G59" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
-        </is>
-      </c>
-      <c r="H59" s="13" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.4 ｜ 12_SAD §4.6</t>
+        </is>
+      </c>
+      <c r="H59" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3 ｜ 15_SDS §9.1；附錄</t>
+        </is>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/ ｜ knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
         </is>
       </c>
     </row>
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>lock_tech</t>
+          <t>bronze_to_silver</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
@@ -39567,39 +39848,44 @@
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>跨品牌技師身分域的獨立權威資料庫，存身分、技能、授權、排班、評分與結算 profile。</t>
+          <t>將 bronze 去冗、糾錯、語意切塊成 silver，並由程式覆寫 provenance 防止 LLM 幻覺來源。</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>不存各品牌的完整工單或客戶敏感資料。</t>
+          <t>silver 不等於已核可發布；下游仍需提煉、人工審核與 Publisher gate。</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
-        </is>
-      </c>
-      <c r="F60" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·MED、REF·INTAKE</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ PARTIAL（批次 CLI，尚無排程部署）</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
-        </is>
-      </c>
-      <c r="H60" s="14" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.4 ｜ 12_SAD §4.6</t>
+        </is>
+      </c>
+      <c r="H60" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3 ｜ 15_SDS §9.1；附錄</t>
+        </is>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/ ｜ knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
         </is>
       </c>
     </row>
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>OHS API routers</t>
+          <t>storage（raw/bronze/silver）</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
@@ -39609,39 +39895,44 @@
       </c>
       <c r="C61" s="13" t="inlineStr">
         <is>
-          <t>品牌 API 查詢技師共享池的同步契約入口，包含技師查詢、媒合、排班與認證查詢。</t>
+          <t>Medallion 各分層的持久檔案資產，保留原始、可審查與結構化中間成果。</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>主要做低延遲讀/媒合；指派與接單真相經業務命令及 Kafka 事件收斂。</t>
+          <t>是 pipeline 資產庫；不等於線上 pgvector 查詢庫。</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>TEC·MATCH</t>
-        </is>
-      </c>
-      <c r="F61" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·MED</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G61" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
-        </is>
-      </c>
-      <c r="H61" s="13" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.6</t>
+        </is>
+      </c>
+      <c r="H61" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1；附錄</t>
+        </is>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
         </is>
       </c>
     </row>
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>matching_service</t>
+          <t>SQL/Schema*.sql</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
@@ -39651,39 +39942,44 @@
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>依技能、地區、品牌授權、認證、可用性、評分與工作量排序技師候選。</t>
+          <t>資料庫基底 schema 定義，描述主表、索引與基礎約束。</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>回傳候選不等於已指派；不繞過 active、授權與認證 gate。</t>
+          <t>不直接代替已上線環境的 forward-only migration 演進記錄。</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>TEC·MATCH</t>
-        </is>
-      </c>
-      <c r="F62" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·SCH</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
-        </is>
-      </c>
-      <c r="H62" s="14" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.2、§4.6</t>
+        </is>
+      </c>
+      <c r="H62" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §3.1、§6.1</t>
+        </is>
+      </c>
+      <c r="I62" s="14" t="inlineStr">
+        <is>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py</t>
         </is>
       </c>
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>schedule_service</t>
+          <t>forward-only migrations</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
@@ -39693,39 +39989,44 @@
       </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
-          <t>管理技師排班、可用時段、接單後工作量與行程狀態。</t>
+          <t>只向前套用、有順序與可稽核性的 SQL schema 變更集。</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>不直接決定品牌工單狀態；跨系統變更經事件與投影對齊。</t>
+          <t>不靠手改 production schema；漂移與重複套用必須由 CI/測試阻擋。</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>TEC·MATCH</t>
-        </is>
-      </c>
-      <c r="F63" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·SCH</t>
+        </is>
+      </c>
+      <c r="F63" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G63" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
-        </is>
-      </c>
-      <c r="H63" s="13" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.2、§4.6</t>
+        </is>
+      </c>
+      <c r="H63" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §3.1、§6.1</t>
+        </is>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py</t>
         </is>
       </c>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>事件層</t>
+          <t>platform schema</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
@@ -39735,39 +40036,44 @@
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>technician-platform 的 Kafka producer/consumer 與投影更新層，發技師狀態並收派工、工單與結算事件。</t>
+          <t>平台治理庫的獨立 schema，存管理員、品牌申請等跨租戶管理資料。</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>只以契約事件跨界；不直接連線或改寫品牌庫。</t>
+          <t>不存單一品牌內的工單、客戶或報價真相。</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>TEC·MATCH、TEC·PROJ</t>
-        </is>
-      </c>
-      <c r="F64" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197 ｜ 12_SAD §4.5 L193–197; §8.2 L369, L372</t>
+          <t>DAT·SCH</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548 ｜ 15_SDS §7.1 L513–518; §7.3 L554–560; §11.1 L648–660</t>
-        </is>
-      </c>
-      <c r="H64" s="14" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.2、§4.6</t>
+        </is>
+      </c>
+      <c r="H64" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §3.1、§6.1</t>
+        </is>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py</t>
         </is>
       </c>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>技師工單 read-model</t>
+          <t>MCP RAG server</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
@@ -39777,39 +40083,44 @@
       </c>
       <c r="C65" s="13" t="inlineStr">
         <is>
-          <t>由品牌 workorder.* 事件建立的最小化 CQRS 查詢投影，供技師工作台顯示。</t>
+          <t>以 MCP 工具契約向 Agent 暴露產品手冊與相似案例的租戶授權檢索服務。</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>只複製任務所需欄位；不是工單命令真相，不複製品牌完整敏感資料。</t>
+          <t>只負責事實檢索；不定義 Agent 行為，也不允許無 tenant ACL 直查 DB。</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>TEC·PROJ、TEC·SET</t>
-        </is>
-      </c>
-      <c r="F65" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197; §9 L401 ｜ 12_SAD §4.5 L193–197; §8.2 L369, L372</t>
+          <t>DAT·RAG</t>
+        </is>
+      </c>
+      <c r="F65" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（RAG_TENANT_ID opt-in）</t>
         </is>
       </c>
       <c r="G65" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L513–518; §7.3 L554–560; §11.1 L648–660 ｜ 15_SDS §7.1 L515–518; §7.3 L554–560; §11.1 L648–660</t>
-        </is>
-      </c>
-      <c r="H65" s="13" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §5、§8–9</t>
+        </is>
+      </c>
+      <c r="H65" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§9.1、§11.3</t>
+        </is>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py</t>
         </is>
       </c>
     </row>
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>commission_settlement_service</t>
+          <t>品牌庫 pgvector</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
@@ -39819,39 +40130,44 @@
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>匯總各品牌 commission.accrued，建立技師跨品牌 statement、payout 與期末對帳。</t>
+          <t>每品牌物理隔離的 PostgreSQL/pgvector，存業務資料與該品牌唯一事實語料。</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>不重算品牌工單的 Billing 明細；差異以 reconcile gate 收斂。</t>
+          <t>不跨品牌共用記錄；技師權威資料仍在 lock_tech。</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>TEC·SET</t>
-        </is>
-      </c>
-      <c r="F66" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197; §9 L401</t>
+          <t>DAT·RAG、REF·PUB</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為備援處理） ｜ PARTIAL（RAG_TENANT_ID opt-in）</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L515–518; §7.3 L554–560; §11.1 L648–660</t>
-        </is>
-      </c>
-      <c r="H66" s="14" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.4 ｜ 12_SAD §5、§8–9</t>
+        </is>
+      </c>
+      <c r="H66" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§9.1、§11.3 ｜ 15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I66" s="14" t="inlineStr">
+        <is>
+          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py ｜ knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>Casdoor</t>
+          <t>rag_manual_chunks / case_entries</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
@@ -39861,39 +40177,44 @@
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>集中式 IdP 與開通治理：提供 OIDC、租戶 org、角色 claims 與 License subscription。</t>
+          <t>RAG 的手冊切塊與案例條目，帶租戶/品牌過濾、embedding 與 provenance。</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>發行身分與角色資訊；資源層授權仍由各 API 預設拒絕 enforce。</t>
+          <t>是被查找的事實資料；不是 Skill 行為規範或對話 Memory。</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>PLT·IAM</t>
-        </is>
-      </c>
-      <c r="F67" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>DAT·RAG</t>
+        </is>
+      </c>
+      <c r="F67" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（RAG_TENANT_ID opt-in）</t>
         </is>
       </c>
       <c r="G67" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
-        </is>
-      </c>
-      <c r="H67" s="13" t="inlineStr">
-        <is>
-          <t>web/platform-console; api platform surface; Casdoor deployment/config</t>
+          <t>12_SAD §5、§8–9</t>
+        </is>
+      </c>
+      <c r="H67" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§9.1、§11.3</t>
+        </is>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py</t>
         </is>
       </c>
     </row>
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>平台維運 console</t>
+          <t>outbox</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
@@ -39903,39 +40224,44 @@
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Super Admin 使用的中央管理前端，處理品牌申請、租戶治理、License 與跨品牌營運視角。</t>
+          <t>與主業務交易同步寫入的待發送記錄，由 worker 重試投遞通知或事件。</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>不當作單品牌日常派工後台，也不繞過 platform admin 授權。</t>
+          <t>解耦交易與外部副作用；不代替 Kafka 的跨系統長期事件紀錄。</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>PLT·IAM</t>
-        </is>
-      </c>
-      <c r="F68" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>DAT·SYNC</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in）</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
-        </is>
-      </c>
-      <c r="H68" s="14" t="inlineStr">
-        <is>
-          <t>web/platform-console; api platform surface; Casdoor deployment/config</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
+        </is>
+      </c>
+      <c r="H68" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
+        </is>
+      </c>
+      <c r="I68" s="14" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>License provisioning</t>
+          <t>provenance / audit</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
@@ -39945,39 +40271,44 @@
       </c>
       <c r="C69" s="13" t="inlineStr">
         <is>
-          <t>License 核准後部署 per-brand bundle、建品牌庫、綁 LINE channel/設定並做健康檢查。</t>
+          <t>記錄資料來源、處理版本、行為者與時間的可重現與稽核證據。</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>是開通與部署流程；不代替應用內租戶授權與資料隔離。</t>
+          <t>不允許 LLM 自行編造來源，也不把一般顯示紀錄當成不可否認稽核鏈。</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>PLT·IAM</t>
-        </is>
-      </c>
-      <c r="F69" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>DAT·SYNC</t>
+        </is>
+      </c>
+      <c r="F69" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in）</t>
         </is>
       </c>
       <c r="G69" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
-        </is>
-      </c>
-      <c r="H69" s="13" t="inlineStr">
-        <is>
-          <t>web/platform-console; api platform surface; Casdoor deployment/config</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
+        </is>
+      </c>
+      <c r="H69" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
+        </is>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>SigNoz</t>
+          <t>汲取層</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
@@ -39987,39 +40318,44 @@
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>平台系統可觀測性服務，收集 OpenTelemetry metrics、logs、traces 並提供 dashboard 與警示。</t>
+          <t>知識精煉入口：收集 knowledge_ready 診斷卡與外部產品素材。</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>看服務健康與系統行為；不專職管理 prompt 或模型 eval。</t>
+          <t>只撿取符合租戶與完整度 gate 的輸入；不直接發布到 Agent。</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>PLT·OBS</t>
-        </is>
-      </c>
-      <c r="F70" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §8.2 L363–372; §9 L389</t>
+          <t>REF·INTAKE</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（批次 CLI，尚無排程部署）</t>
         </is>
       </c>
       <c r="G70" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §12 L681–696（韌性與觀測證據使用面）</t>
-        </is>
-      </c>
-      <c r="H70" s="14" t="inlineStr">
-        <is>
-          <t>集中共用可觀測性部署（非單一應用路徑）</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H70" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I70" s="14" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
         </is>
       </c>
     </row>
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>OPIK</t>
+          <t>提煉分流器</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
@@ -40029,39 +40365,44 @@
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>Agent LLM Ops 工具，追蹤 prompt、LLM trace、token/成本與 eval 品質。</t>
+          <t>將 silver 內容分為「可查找的事實」與「Agent 怎麼做的行為」兩條軌。</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>專注 AI 呼叫品質；不代替 SigNoz 的全系統可觀測性。</t>
+          <t>只產生 draft；未經人工審核核可不得寫入 pgvector 或 Skill。</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>PLT·OBS</t>
-        </is>
-      </c>
-      <c r="F71" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §8.2 L363–372; §9 L389</t>
+          <t>REF·REFINE</t>
+        </is>
+      </c>
+      <c r="F71" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（服務已實作，部署流程未完整）</t>
         </is>
       </c>
       <c r="G71" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §12 L681–696（韌性與觀測證據使用面）</t>
-        </is>
-      </c>
-      <c r="H71" s="13" t="inlineStr">
-        <is>
-          <t>集中共用可觀測性部署（非單一應用路徑）</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H71" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{refine,store}.py</t>
         </is>
       </c>
     </row>
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>OpenTelemetry</t>
+          <t>Draft Queue</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
@@ -40071,39 +40412,44 @@
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>服務不綁供應商的 metrics、logs、traces 儀表化與傳輸標準。</t>
+          <t>事實 draft 與行為 diff 的審核佇列，包含來源、冪等鍵與狀態機。</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>是觀測資料契約與傳輸層；不是 dashboard 或業務稽核帳本本身。</t>
+          <t>是待審產物，不是已發布知識。</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>PLT·OBS</t>
-        </is>
-      </c>
-      <c r="F72" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §8.2 L363–372; §9 L389</t>
+          <t>REF·人工審核、REF·REFINE</t>
+        </is>
+      </c>
+      <c r="F72" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定） ｜ PARTIAL（服務已實作，部署流程未完整）</t>
         </is>
       </c>
       <c r="G72" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §12 L681–696（韌性與觀測證據使用面）</t>
-        </is>
-      </c>
-      <c r="H72" s="14" t="inlineStr">
-        <is>
-          <t>集中共用可觀測性部署（非單一應用路徑）</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H72" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1–9.2 ｜ 15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I72" s="14" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{refine,store}.py ｜ knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
         </is>
       </c>
     </row>
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>Flow DSL executor</t>
+          <t>審核 UI backend</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
@@ -40113,39 +40459,44 @@
       </c>
       <c r="C73" s="13" t="inlineStr">
         <is>
-          <t>讀取 Vertical Pack 的宣告式 flow，驗 guard、執行 block、持久化狀態/事件並掛 SLA timer。</t>
+          <t>提供 draft 狀態轉移、diff 呈現、核可、駁回與 re-refine 的人工審核後端。</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>只執行可驗證 DSL；拒絕任意 inline code，也不把 UI 編輯器當執行後端。</t>
+          <t>不自動把 LLM 產物當真相；核可與發布仍是兩個可稽核步驟。</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>API·WO、PLT·FLOW</t>
-        </is>
-      </c>
-      <c r="F73" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L397 ｜ 12_SAD §9 L396–398</t>
+          <t>REF·人工審核</t>
+        </is>
+      </c>
+      <c r="F73" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定）</t>
         </is>
       </c>
       <c r="G73" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L36–59; §3.2–3.7 L126–205; §10 L639–644 ｜ 15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
-        </is>
-      </c>
-      <c r="H73" s="13" t="inlineStr">
-        <is>
-          <t>api/services/work_order_service.py; api/routers/; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H73" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1–9.2</t>
+        </is>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
         </is>
       </c>
     </row>
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>domain blocks / primitives</t>
+          <t>Casdoor reviewer auth</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
@@ -40155,39 +40506,44 @@
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>雙層工單積木：對外是派工/報價/收款等粗顆粒 block，內部由查資料、轉狀態、發事件等 primitive 組合。</t>
+          <t>Refinery 審核服務可依環境使用 Casdoor RS256 OIDC 驗證 reviewer claims，並保留 HS256 過渡模式。</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>每顆積木必須有 inputs/preconditions/guards/effects 契約；不允許無法靜態驗證的自由腳本。</t>
+          <t>只驗證審核者身分與角色；compose 未提供 OIDC 設定時不可宣稱已完成正式切換。</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>API·WO、PLT·FLOW</t>
-        </is>
-      </c>
-      <c r="F74" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L397 ｜ 12_SAD §9 L396–398</t>
+          <t>REF·人工審核</t>
+        </is>
+      </c>
+      <c r="F74" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定）</t>
         </is>
       </c>
       <c r="G74" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L36–59; §3.2–3.7 L126–205; §10 L639–644 ｜ 15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
-        </is>
-      </c>
-      <c r="H74" s="14" t="inlineStr">
-        <is>
-          <t>api/services/work_order_service.py; api/routers/; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H74" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1–9.2</t>
+        </is>
+      </c>
+      <c r="I74" s="14" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
         </is>
       </c>
     </row>
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>Vertical Pack</t>
+          <t>Publisher</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
@@ -40197,39 +40553,44 @@
       </c>
       <c r="C75" s="13" t="inlineStr">
         <is>
-          <t>可版本化的產業設定包，組合 field metadata、flow、catalog、knowledge、UI composition 與 blocks。</t>
+          <t>核可後的雙軌發布器：事實 embed 後寫 pgvector；行為產生 append-only Skill patch/產出檔。</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>承載產業/品牌差異；不改寫身分、金流、事件等平台不變核心。</t>
+          <t>只發布 approved draft；不跳過 provenance、tenant 過濾或人工審核 gate。</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>PLT·CFG、PLT·FLOW</t>
-        </is>
-      </c>
-      <c r="F75" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §9 L396, L398, L400 ｜ 12_SAD §9 L396–398</t>
+          <t>REF·PUB</t>
+        </is>
+      </c>
+      <c r="F75" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為備援處理）</t>
         </is>
       </c>
       <c r="G75" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L36–59; §3.2–3.7 L126–205; §10 L639–644 ｜ 15_SDS §3.2 L126–142; §10 L639–644; §13 L704–709</t>
-        </is>
-      </c>
-      <c r="H75" s="13" t="inlineStr">
-        <is>
-          <t>待 M4 實作；目前為 SDS 設計元件 ｜ 待 M4/M5 實作；目前為 SAD/ADR/SDS 設計元件</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H75" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>FlowEditor</t>
+          <t>behavior patch artifact</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
@@ -40239,39 +40600,44 @@
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>對 flow DSL 進行拖拉或表單編輯的薄 UI，輸出仍是可版控、可驗證的 DSL。</t>
+          <t>行為軌核可後產生 target_path + content 的受控產出檔，保存於 draft provenance，交由 apply CLI 消費。</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>不直接執行任意程式；金流、派工與同意書仍受保護層及人工審核 gate。</t>
+          <t>產出檔仍不是已發布 skill；必須經 LiveSkill draft/人工發布或明確 git 備援處理才生效。</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>PLT·FLOW</t>
-        </is>
-      </c>
-      <c r="F76" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §9 L396–398</t>
+          <t>REF·PUB</t>
+        </is>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為備援處理）</t>
         </is>
       </c>
       <c r="G76" s="17" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L36–59; §3.2–3.7 L126–205; §10 L639–644</t>
-        </is>
-      </c>
-      <c r="H76" s="14" t="inlineStr">
-        <is>
-          <t>待 M4 實作；目前為 SDS 設計元件</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H76" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I76" s="14" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>Agent Configuration Studio / Config Registry</t>
+          <t>LiveSkill DB ingest</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
@@ -40281,84 +40647,1363 @@
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>管理 skill、RAG 權限、prompt、品牌設定與版本/分階段發布的中央設定能力。</t>
+          <t>apply_behavior 預設呼叫 internal skills ingest，將核可產出檔以加性合併建立品牌 skill draft，再由後台人工發布。</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>租戶只可改客製層；安全、金額、工具允許清單等保護層不可 override。</t>
+          <t>需要 LOCK_API_BASE_URL 與 INTERNAL_API_TOKEN；缺少時只可走明確標示的 git 備援處理。</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>PLT·CFG</t>
-        </is>
-      </c>
-      <c r="F77" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §9 L396, L398, L400</t>
+          <t>REF·PUB</t>
+        </is>
+      </c>
+      <c r="F77" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為備援處理）</t>
         </is>
       </c>
       <c r="G77" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §3.2 L126–142; §10 L639–644; §13 L704–709</t>
-        </is>
-      </c>
-      <c r="H77" s="13" t="inlineStr">
-        <is>
-          <t>待 M4/M5 實作；目前為 SAD/ADR/SDS 設計元件</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H77" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="14" t="inlineStr">
         <is>
+          <t>self-service routers</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>技師端自助 API：註冊、profile、技能/品牌授權、認證上傳、排班與工作台。</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="inlineStr">
+        <is>
+          <t>只服務已驗證的技師生命週期；不暴露跨租戶品牌內部資料。</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="inlineStr">
+        <is>
+          <t>TEC·ID</t>
+        </is>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5</t>
+        </is>
+      </c>
+      <c r="H78" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I78" s="14" t="inlineStr">
+        <is>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="36" customHeight="1">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>technician_service</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>技師身分、技能、品牌授權、停復權與評分等核心領域服務。</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>真相寫入 lock_tech；不雙寫各品牌庫。</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>TEC·ID</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+        </is>
+      </c>
+      <c r="G79" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5</t>
+        </is>
+      </c>
+      <c r="H79" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="36" customHeight="1">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>certification/kyc_service</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>技師 KYC 與認證申請/審核服務，對敏感欄位加密並控制准入。</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>未核可或已失效認證不得進入媒合候選集。</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>TEC·ID</t>
+        </is>
+      </c>
+      <c r="F80" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5</t>
+        </is>
+      </c>
+      <c r="H80" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I80" s="14" t="inlineStr">
+        <is>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="36" customHeight="1">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>lock_tech</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>跨品牌技師身分域的獨立權威資料庫，存身分、技能、授權、排班、評分與結算 profile。</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>不存各品牌的完整工單或客戶敏感資料。</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>TEC·ID</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+        </is>
+      </c>
+      <c r="G81" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5</t>
+        </is>
+      </c>
+      <c r="H81" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>OHS API routers</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="inlineStr">
+        <is>
+          <t>品牌 API 查詢技師共享池的同步契約入口，包含技師查詢、媒合、排班與認證查詢。</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>主要做低延遲讀/媒合；指派與接單真相經業務命令及 Kafka 事件收斂。</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="inlineStr">
+        <is>
+          <t>TEC·MATCH</t>
+        </is>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（媒合已實作；獨立 OHS 邊界未拆）</t>
+        </is>
+      </c>
+      <c r="G82" s="17" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5</t>
+        </is>
+      </c>
+      <c r="H82" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §4.4、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I82" s="14" t="inlineStr">
+        <is>
+          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="36" customHeight="1">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>schedule_service</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C83" s="13" t="inlineStr">
+        <is>
+          <t>管理技師排班、可用時段、接單後工作量與行程狀態。</t>
+        </is>
+      </c>
+      <c r="D83" s="13" t="inlineStr">
+        <is>
+          <t>不直接決定品牌工單狀態；跨系統變更經事件與投影對齊。</t>
+        </is>
+      </c>
+      <c r="E83" s="13" t="inlineStr">
+        <is>
+          <t>TEC·MATCH</t>
+        </is>
+      </c>
+      <c r="F83" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（媒合已實作；獨立 OHS 邊界未拆）</t>
+        </is>
+      </c>
+      <c r="G83" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5</t>
+        </is>
+      </c>
+      <c r="H83" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §4.4、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>事件層</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>technician-platform 的 Kafka producer/consumer 與投影更新層，發技師狀態並收派工、工單與結算事件。</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>只以契約事件跨界；不直接連線或改寫品牌庫。</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="inlineStr">
+        <is>
+          <t>TEC·MATCH、TEC·PROJ</t>
+        </is>
+      </c>
+      <c r="F84" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（媒合已實作；獨立 OHS 邊界未拆）</t>
+        </is>
+      </c>
+      <c r="G84" s="17" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.5、§8.2</t>
+        </is>
+      </c>
+      <c r="H84" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I84" s="14" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="36" customHeight="1">
+      <c r="A85" s="13" t="inlineStr">
+        <is>
+          <t>technician_workorder_projection</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C85" s="13" t="inlineStr">
+        <is>
+          <t>lock_tech 中由 workorder.lifecycle 事件維護的技師工單最小化投影。</t>
+        </is>
+      </c>
+      <c r="D85" s="13" t="inlineStr">
+        <is>
+          <t>只供技師查詢且 Kafka opt-in；不取代品牌工單真相，也尚未證明所有畫面都只讀此投影。</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="inlineStr">
+        <is>
+          <t>TEC·PROJ</t>
+        </is>
+      </c>
+      <c r="F85" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應）</t>
+        </is>
+      </c>
+      <c r="G85" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §4.5、§8.2</t>
+        </is>
+      </c>
+      <c r="H85" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="36" customHeight="1">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>技師工單 read-model</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>由品牌 workorder.* 事件建立的最小化 CQRS 查詢投影，供技師工作台顯示。</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>只複製任務所需欄位；不是工單命令真相，不複製品牌完整敏感資料。</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="inlineStr">
+        <is>
+          <t>TEC·PROJ</t>
+        </is>
+      </c>
+      <c r="F86" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應）</t>
+        </is>
+      </c>
+      <c r="G86" s="17" t="inlineStr">
+        <is>
+          <t>12_SAD §4.5、§8.2</t>
+        </is>
+      </c>
+      <c r="H86" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I86" s="14" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="36" customHeight="1">
+      <c r="A87" s="13" t="inlineStr">
+        <is>
+          <t>technician_commission_projection</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C87" s="13" t="inlineStr">
+        <is>
+          <t>lock_tech 中由 commission.accrued 事件維護的技師佣金 CQRS 投影。</t>
+        </is>
+      </c>
+      <c r="D87" s="13" t="inlineStr">
+        <is>
+          <t>只在 Kafka consumer 啟用時更新；不等於完整跨品牌 payout 已完成。</t>
+        </is>
+      </c>
+      <c r="E87" s="13" t="inlineStr">
+        <is>
+          <t>TEC·SET</t>
+        </is>
+      </c>
+      <c r="F87" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
+        </is>
+      </c>
+      <c r="G87" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §4.5、§9</t>
+        </is>
+      </c>
+      <c r="H87" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="36" customHeight="1">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>technician settlement services</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="inlineStr">
+        <is>
+          <t>現行技師佣金、statement 與 reconciliation 服務集合，提供逐案佣金與對帳視圖。</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>目前為 partial/interim；不宣稱不存在的單一 commission_settlement_service 或完整跨品牌出款已實作。</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>TEC·SET</t>
+        </is>
+      </c>
+      <c r="F88" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>12_SAD §4.5、§9</t>
+        </is>
+      </c>
+      <c r="H88" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I88" s="14" t="inlineStr">
+        <is>
+          <t>api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1">
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>Tech DB router + mirror</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>技師權威庫路由與相容鏡射</t>
+        </is>
+      </c>
+      <c r="C89" s="13" t="inlineStr">
+        <is>
+          <t>以 TECH_POSTGRES_URI 將技師身分寫入 lock_tech，並在過渡期按順序鏡射必要相容列到品牌側。</t>
+        </is>
+      </c>
+      <c r="D89" s="13" t="inlineStr">
+        <is>
+          <t>lock_tech 才是技師權威；鏡射是 interim 相容機制，不是長期雙寫架構。</t>
+        </is>
+      </c>
+      <c r="E89" s="13" t="inlineStr">
+        <is>
+          <t>DAT·SCH、TEC·ID</t>
+        </is>
+      </c>
+      <c r="F89" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+        </is>
+      </c>
+      <c r="G89" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§4.6</t>
+        </is>
+      </c>
+      <c r="H89" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §3.1、§6.1 ｜ 15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="36" customHeight="1">
+      <c r="A90" s="14" t="inlineStr">
+        <is>
+          <t>Casdoor</t>
+        </is>
+      </c>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="inlineStr">
+        <is>
+          <t>集中式 IdP 與開通治理：提供 OIDC、租戶 org、角色 claims 與 License subscription。</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>發行身分與角色資訊；資源層授權仍由各 API 預設拒絕 enforce。</t>
+        </is>
+      </c>
+      <c r="E90" s="14" t="inlineStr">
+        <is>
+          <t>PLT·IAM</t>
+        </is>
+      </c>
+      <c r="F90" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Casdoor/config 存在；環境開通設定未完整）</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2–8.3、§9</t>
+        </is>
+      </c>
+      <c r="H90" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
+        </is>
+      </c>
+      <c r="I90" s="14" t="inlineStr">
+        <is>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="36" customHeight="1">
+      <c r="A91" s="13" t="inlineStr">
+        <is>
+          <t>License Entitlement Gate</t>
+        </is>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C91" s="13" t="inlineStr">
+        <is>
+          <t>依平台庫 tenant license entitlement 判定租戶是否可使用選購能力；正式環境缺設定應驗證失敗即拒絕。</t>
+        </is>
+      </c>
+      <c r="D91" s="13" t="inlineStr">
+        <is>
+          <t>是應用層授權檢查；不等於部署 per-brand bundle 的環境開通設定自動化。</t>
+        </is>
+      </c>
+      <c r="E91" s="13" t="inlineStr">
+        <is>
+          <t>PLT·IAM</t>
+        </is>
+      </c>
+      <c r="F91" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Casdoor/config 存在；環境開通設定未完整）</t>
+        </is>
+      </c>
+      <c r="G91" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2–8.3、§9</t>
+        </is>
+      </c>
+      <c r="H91" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
+        </is>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="36" customHeight="1">
+      <c r="A92" s="14" t="inlineStr">
+        <is>
+          <t>平台維運 console</t>
+        </is>
+      </c>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>Super Admin 使用的中央管理前端，處理品牌申請、租戶治理、License 與跨品牌營運視角。</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="inlineStr">
+        <is>
+          <t>不當作單品牌日常派工後台，也不繞過 platform admin 授權。</t>
+        </is>
+      </c>
+      <c r="E92" s="14" t="inlineStr">
+        <is>
+          <t>PLT·IAM</t>
+        </is>
+      </c>
+      <c r="F92" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Casdoor/config 存在；環境開通設定未完整）</t>
+        </is>
+      </c>
+      <c r="G92" s="17" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2–8.3、§9</t>
+        </is>
+      </c>
+      <c r="H92" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
+        </is>
+      </c>
+      <c r="I92" s="14" t="inlineStr">
+        <is>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="36" customHeight="1">
+      <c r="A93" s="13" t="inlineStr">
+        <is>
+          <t>License provisioning</t>
+        </is>
+      </c>
+      <c r="B93" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>License 核准後部署 per-brand bundle、建品牌庫、綁 LINE channel/設定並做健康檢查。</t>
+        </is>
+      </c>
+      <c r="D93" s="13" t="inlineStr">
+        <is>
+          <t>是開通與部署流程；不代替應用內租戶授權與資料隔離。</t>
+        </is>
+      </c>
+      <c r="E93" s="13" t="inlineStr">
+        <is>
+          <t>PLT·IAM</t>
+        </is>
+      </c>
+      <c r="F93" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Casdoor/config 存在；環境開通設定未完整）</t>
+        </is>
+      </c>
+      <c r="G93" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2–8.3、§9</t>
+        </is>
+      </c>
+      <c r="H93" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
+        </is>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="36" customHeight="1">
+      <c r="A94" s="14" t="inlineStr">
+        <is>
+          <t>SigNoz</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C94" s="14" t="inlineStr">
+        <is>
+          <t>平台系統可觀測性服務，收集 OpenTelemetry metrics、logs、traces 並提供 dashboard 與警示。</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>看服務健康與系統行為；不專職管理 prompt 或模型 eval。</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>PLT·OBS</t>
+        </is>
+      </c>
+      <c r="F94" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（instrumentation 已實作；集中 collector/IaC 缺）</t>
+        </is>
+      </c>
+      <c r="G94" s="17" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2、§9</t>
+        </is>
+      </c>
+      <c r="H94" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §12</t>
+        </is>
+      </c>
+      <c r="I94" s="14" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="36" customHeight="1">
+      <c r="A95" s="13" t="inlineStr">
+        <is>
+          <t>OPIK</t>
+        </is>
+      </c>
+      <c r="B95" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="inlineStr">
+        <is>
+          <t>Agent LLM Ops 工具，追蹤 prompt、LLM trace、token/成本與 eval 品質。</t>
+        </is>
+      </c>
+      <c r="D95" s="13" t="inlineStr">
+        <is>
+          <t>專注 AI 呼叫品質；不代替 SigNoz 的全系統可觀測性。</t>
+        </is>
+      </c>
+      <c r="E95" s="13" t="inlineStr">
+        <is>
+          <t>PLT·OBS</t>
+        </is>
+      </c>
+      <c r="F95" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（instrumentation 已實作；集中 collector/IaC 缺）</t>
+        </is>
+      </c>
+      <c r="G95" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2、§9</t>
+        </is>
+      </c>
+      <c r="H95" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §12</t>
+        </is>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="36" customHeight="1">
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>OpenTelemetry</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C96" s="14" t="inlineStr">
+        <is>
+          <t>服務不綁供應商的 metrics、logs、traces 儀表化與傳輸標準。</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>是觀測資料契約與傳輸層；不是 dashboard 或業務稽核帳本本身。</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="inlineStr">
+        <is>
+          <t>PLT·OBS</t>
+        </is>
+      </c>
+      <c r="F96" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（instrumentation 已實作；集中 collector/IaC 缺）</t>
+        </is>
+      </c>
+      <c r="G96" s="17" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2、§9</t>
+        </is>
+      </c>
+      <c r="H96" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §12</t>
+        </is>
+      </c>
+      <c r="I96" s="14" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="36" customHeight="1">
+      <c r="A97" s="13" t="inlineStr">
+        <is>
+          <t>PIIScrubSpanProcessor</t>
+        </is>
+      </c>
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="inlineStr">
+        <is>
+          <t>四站 Web 在 trace 匯出前遮蔽 email、電話、地址、token，並將 LINE UID 雜湊化。</t>
+        </is>
+      </c>
+      <c r="D97" s="13" t="inlineStr">
+        <is>
+          <t>只治理 observability 出站資料；不代替 API 回應遮蔽、資料庫加密或 GDPR 刪除。</t>
+        </is>
+      </c>
+      <c r="E97" s="13" t="inlineStr">
+        <is>
+          <t>PLT·OBS</t>
+        </is>
+      </c>
+      <c r="F97" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（instrumentation 已實作；集中 collector/IaC 缺）</t>
+        </is>
+      </c>
+      <c r="G97" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2、§9</t>
+        </is>
+      </c>
+      <c r="H97" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §12</t>
+        </is>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="36" customHeight="1">
+      <c r="A98" s="14" t="inlineStr">
+        <is>
+          <t>Flow DSL executor</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>讀取 Vertical Pack 的宣告式 flow，驗 guard、執行 block、持久化狀態/事件並掛 SLA timer。</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>只執行可驗證 DSL；拒絕任意 inline code，也不把 UI 編輯器當執行後端。</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="inlineStr">
+        <is>
+          <t>API·WO、PLT·FLOW</t>
+        </is>
+      </c>
+      <c r="F98" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ TO-BE（M4 設計）</t>
+        </is>
+      </c>
+      <c r="G98" s="17" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§9 ｜ 12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H98" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+        </is>
+      </c>
+      <c r="I98" s="14" t="inlineStr">
+        <is>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="36" customHeight="1">
+      <c r="A99" s="13" t="inlineStr">
+        <is>
+          <t>domain blocks / primitives</t>
+        </is>
+      </c>
+      <c r="B99" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C99" s="13" t="inlineStr">
+        <is>
+          <t>雙層工單積木：對外是派工/報價/收款等粗顆粒 block，內部由查資料、轉狀態、發事件等 primitive 組合。</t>
+        </is>
+      </c>
+      <c r="D99" s="13" t="inlineStr">
+        <is>
+          <t>每顆積木必須有 inputs/preconditions/guards/effects 契約；不允許無法靜態驗證的自由腳本。</t>
+        </is>
+      </c>
+      <c r="E99" s="13" t="inlineStr">
+        <is>
+          <t>API·WO、PLT·FLOW</t>
+        </is>
+      </c>
+      <c r="F99" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ TO-BE（M4 設計）</t>
+        </is>
+      </c>
+      <c r="G99" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§9 ｜ 12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H99" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+        </is>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="36" customHeight="1">
+      <c r="A100" s="14" t="inlineStr">
+        <is>
+          <t>Vertical Pack</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>可版本化的產業設定包，組合 field metadata、flow、catalog、knowledge、UI composition 與 blocks。</t>
+        </is>
+      </c>
+      <c r="D100" s="14" t="inlineStr">
+        <is>
+          <t>承載產業/品牌差異；不改寫身分、金流、事件等平台不變核心。</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="inlineStr">
+        <is>
+          <t>PLT·CFG、PLT·FLOW</t>
+        </is>
+      </c>
+      <c r="F100" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已實作；完整 Studio 未完成） ｜ TO-BE（M4 設計）</t>
+        </is>
+      </c>
+      <c r="G100" s="17" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H100" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I100" s="14" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分實作） ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="36" customHeight="1">
+      <c r="A101" s="13" t="inlineStr">
+        <is>
+          <t>FlowEditor</t>
+        </is>
+      </c>
+      <c r="B101" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C101" s="13" t="inlineStr">
+        <is>
+          <t>對 flow DSL 進行拖拉或表單編輯的薄 UI，輸出仍是可版控、可驗證的 DSL。</t>
+        </is>
+      </c>
+      <c r="D101" s="13" t="inlineStr">
+        <is>
+          <t>不直接執行任意程式；金流、派工與同意書仍受保護層及人工審核 gate。</t>
+        </is>
+      </c>
+      <c r="E101" s="13" t="inlineStr">
+        <is>
+          <t>PLT·FLOW</t>
+        </is>
+      </c>
+      <c r="F101" s="13" t="inlineStr">
+        <is>
+          <t>TO-BE（M4 設計）</t>
+        </is>
+      </c>
+      <c r="G101" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H101" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§3.2–3.7、§10</t>
+        </is>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>待 M4 實作；目前為 SDS 設計元件</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="36" customHeight="1">
+      <c r="A102" s="14" t="inlineStr">
+        <is>
+          <t>Agent Configuration Studio / Config Registry</t>
+        </is>
+      </c>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>管理 skill、RAG 權限、prompt、品牌設定與版本/分階段發布的中央設定能力。</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="inlineStr">
+        <is>
+          <t>租戶只可改客製層；安全、金額、工具允許清單等保護層不可 override。</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="inlineStr">
+        <is>
+          <t>PLT·CFG</t>
+        </is>
+      </c>
+      <c r="F102" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已實作；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="G102" s="17" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H102" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I102" s="14" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分實作）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="36" customHeight="1">
+      <c r="A103" s="13" t="inlineStr">
+        <is>
+          <t>M18 Config Registry</t>
+        </is>
+      </c>
+      <c r="B103" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C103" s="13" t="inlineStr">
+        <is>
+          <t>已實作的設定服務與路由，管理受控 namespace、版本、canary 與回復流程。</t>
+        </is>
+      </c>
+      <c r="D103" s="13" t="inlineStr">
+        <is>
+          <t>只涵蓋現行 M18 設定能力；不等於完整 FlowEditor 或跨產業 Studio 已完成。</t>
+        </is>
+      </c>
+      <c r="E103" s="13" t="inlineStr">
+        <is>
+          <t>PLT·CFG</t>
+        </is>
+      </c>
+      <c r="F103" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已實作；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="G103" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H103" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分實作）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="36" customHeight="1">
+      <c r="A104" s="14" t="inlineStr">
+        <is>
+          <t>Skill Revision Registry</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>以 skill_revisions 保存品牌 skill draft/published 版本，供 SkillSync 取得已發布內容。</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="inlineStr">
+        <is>
+          <t>版本庫不自行核准內容；發布權限、保護層與稽核仍由 API/後台治理。</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t>PLT·CFG</t>
+        </is>
+      </c>
+      <c r="F104" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已實作；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="G104" s="17" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H104" s="17" t="inlineStr">
+        <is>
+          <t>15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I104" s="14" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分實作）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="36" customHeight="1">
+      <c r="A105" s="13" t="inlineStr">
+        <is>
           <t>HITL 審核骨架</t>
         </is>
       </c>
-      <c r="B78" s="14" t="inlineStr">
+      <c r="B105" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C78" s="14" t="inlineStr">
+      <c r="C105" s="13" t="inlineStr">
         <is>
           <t>共用的 draft→diff→人工審核→核可/駁回→發布模式，同時支援知識精煉與 AI Onboarding Compiler。</t>
         </is>
       </c>
-      <c r="D78" s="14" t="inlineStr">
+      <c r="D105" s="13" t="inlineStr">
         <is>
           <t>AI 只產生 draft；高風險知識或流程未人工審核不得實作。</t>
         </is>
       </c>
-      <c r="E78" s="14" t="inlineStr">
+      <c r="E105" s="13" t="inlineStr">
         <is>
           <t>PLT·CFG</t>
         </is>
       </c>
-      <c r="F78" s="17" t="inlineStr">
-        <is>
-          <t>12_SAD §9 L396, L398, L400</t>
-        </is>
-      </c>
-      <c r="G78" s="17" t="inlineStr">
-        <is>
-          <t>15_SDS §3.2 L126–142; §10 L639–644; §13 L704–709</t>
-        </is>
-      </c>
-      <c r="H78" s="14" t="inlineStr">
-        <is>
-          <t>待 M4/M5 實作；目前為 SAD/ADR/SDS 設計元件</t>
+      <c r="F105" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已實作；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="G105" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H105" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分實作）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H78"/>
+  <autoFilter ref="A4:I105"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:H78">
+  <conditionalFormatting sqref="A5:I105">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISNUMBER(SEARCH("🔴",A5))</formula>
     </cfRule>
@@ -40370,154 +42015,208 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId202"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -41933,12 +43632,12 @@
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>當客戶傳送文字或照片時，合法訊息會進入客服流程並收到回覆；無效來源被拒絕，系統異常時仍有友善說明。</t>
+          <t>當客戶傳送文字或照片時，合法訊息會進入客服流程並收到回覆；Chatlock 安裝前拍照引導可附核准樣本圖，其他品牌維持純文字；無效來源被拒絕，系統異常時仍有友善說明。</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>功能判準：有效文字/照片皆有明確回覆；超長內容截斷至 4900 字以內；錯誤簽章回 400 且不產生處理紀錄。
+          <t>功能判準：有效文字/照片皆有明確回覆；只有 Chatlock 附核准樣本圖，其他品牌純文字；未知標記不外洩；超長內容截斷至 4900 字內；錯誤簽章回 400 且不產生處理紀錄。
 副作用判準：被拒絕或重送時不得多出回覆、問題卡、轉人紀錄或跨客戶記憶。</t>
         </is>
       </c>
@@ -42039,12 +43738,12 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>當問題卡資訊完整時，客戶會先收到相符的解決建議並被詢問是否已釐清；連續三次未釐清時自動轉人工。</t>
+          <t>當問題資訊不足時，系統依當下情境一次列齊必要問題；客戶明確要求真人、急迫派工、涉及金錢或連續兩次表達不滿時立即轉人工，不採固定追問輪數。</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>功能判準：案例庫命中與知識庫回答來源正確；系統會詢問是否已釐清；第 3 次未釐清後建立後台案件並轉真人。
+          <t>功能判準：回答來源正確；缺項一次列齊；四種不可違反條件一命中即建立後台案件並轉真人；一般補資料、單次不滿與可回答問題不得因輪數誤轉。
 副作用判準：被拒絕或重送時不得多出回覆、問題卡、轉人紀錄或跨客戶記憶。</t>
         </is>
       </c>
@@ -42415,7 +44114,7 @@
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>功能判準：1.5 秒內的三則訊息合併為一次處理；第四則另開一次處理；24 小時內重送不產生第二次回覆或案件。
+          <t>功能判準：5.0 秒內的三則訊息合併為一次處理；第四則另開一次處理；reserve-first 永久主鍵使重送不產生第二次回覆或案件。
 副作用判準：被拒絕或重送時不得多出回覆、問題卡、轉人紀錄或跨客戶記憶。</t>
         </is>
       </c>
@@ -42516,12 +44215,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>AI 可草擬問題卡，客服能補齊與確認；未達完整度或未經客服確認時，不得自動轉成工單。</t>
+          <t>AI 可草擬問題卡，並將同一對話近 24 小時內最多 5 張客戶照片附上供客服檢視；客服能補齊與確認，未達完整度或未經客服確認時不得自動轉成工單。</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>功能判準：AI 不得自行建立工單；confirm/convert 走客服認證端點。
+          <t>功能判準：只附同對話近 24 小時最多 5 張照片且時間正序、append-only；重送不重複建卡，照片旁路失敗不阻斷主要流程程。
 副作用判準：被拒絕或重送時不得多出狀態變更、事件、帳本或重複稽核紀錄。</t>
         </is>
       </c>
@@ -42569,12 +44268,12 @@
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>報價必須依序完成內部核准、客戶送達與客戶確認；保固或專案報價不得由 AI 直接送出，客戶畫面不顯示成本欄位。</t>
+          <t>報價必須依序完成內部核准、客戶送達與客戶確認；重複同一決定安全回放，相反決定、過期、無權或找不到報價時顯示對應說明；保固或專案報價不得由 AI 直接送出，客戶畫面不顯示成本欄位。</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>功能判準：sender_role=ai_agent AND case_type∈{warranty,project} → 403 AI_FORBIDDEN_WARRANTY_PROJECT；quote 內外雙視圖（客戶端不含成本欄）。
+          <t>功能判準：同決定安全回放；相反終態回 QUOTE_ALREADY_DECIDED、過期回 QUOTE_EXPIRED；LINE 依 error_code 分流，未知格式友善降級。
 副作用判準：被拒絕或重送時不得多出狀態變更、事件、帳本或重複稽核紀錄。</t>
         </is>
       </c>
@@ -42675,12 +44374,12 @@
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>報價已獲客戶確認或符合急件例外時，客服可一次操作建立工單；重複送出不產生第二張工單，並留下建單來源。</t>
+          <t>報價已獲客戶確認或符合急件例外時，客服可一次操作建立工單；問題卡中的客戶姓名、電話、地址、品牌、型號與序號會帶入工單，重複送出不產生第二張工單並留下建單來源。</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>功能判準：create_trigger 記錄 AI/CS 路徑；idempotency_key 防重。
+          <t>功能判準：工單完整承接問題卡欄位含 serial；只有客服操作可開單；重送不新增第二張工單。
 副作用判準：被拒絕或重送時不得多出狀態變更、事件、帳本或重複稽核紀錄。</t>
         </is>
       </c>
@@ -42733,7 +44432,7 @@
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>功能判準：一般通知送達 P95 ≤ 30 秒、急件 P95 ≤ 15 秒；候選池為空時 100% 進入 dispatch_pending 並觸發警示；急件排序降低距離權重、提高評分權重。。
+          <t>功能判準：一般通知送達 P95 ≤ 30 秒、急件 P95 ≤ 15 秒；候選池為空時 100% 進入 dispatch_pending 並觸發警示；急件排序降低距離權重、提高評分權重。
 副作用判準：被拒絕或重送時不得多出狀態變更、事件、帳本或重複稽核紀錄。</t>
         </is>
       </c>
@@ -42887,12 +44586,12 @@
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>技師可上傳到場與施工證據、登錄受控材料並取得客戶簽名；證據不齊或現場範圍變更未完成必要確認時不得結案。</t>
+          <t>技師可上傳到場與施工證據、登錄受控材料；客服可將三段免責簽署連結推送到 LINE，未綁 LINE 時可複製連結交付；證據、簽署或現場範圍變更確認不齊時不得結案。</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>功能判準：結案前證據齊備檢核；scope change 走 §2.2.5 分層。
+          <t>功能判準：有 LINE 時推播、無 LINE 時回可複製連結；重送安全、越權拒絕；token 只存 hash，三段同意正確 upsert 並受結案 gate 檢查。
 副作用判準：被拒絕或重送時不得多出狀態變更、事件、帳本或重複稽核紀錄。</t>
         </is>
       </c>
@@ -43629,12 +45328,12 @@
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>派工人員可查看工單看板、待派佇列與即時更新；即時連線中斷時畫面不崩潰，仍可查詢與完成核心作業。</t>
+          <t>派工人員可查看工單看板、待派佇列、技師全名與需授權照片的縮圖/放大檢視；即時連線中斷或照片載入失敗時畫面不崩潰，仍可查詢與完成核心作業。</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>功能判準：即時降級 100% 不當機。
+          <t>功能判準：授權 fetch→Blob 正常顯示且可關閉/revoke；錯誤只顯示佔位不崩潰；姓名與時間軸資料正確，缺名走明確備援處理。
 副作用判準：畫面不得顯示假成功；後端未成功時資料不得變更。</t>
         </is>
       </c>
@@ -43788,12 +45487,12 @@
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>客戶可查看報價明細、分層閱讀條款、勾選同意並追蹤工單進度；簡化備援方式也會準確記錄客戶同意來源。</t>
+          <t>客戶可由 LINE 或備援連結查看報價與三段免責條款、勾選同意並追蹤工單進度；公開 token 僅保存雜湊稽核，畫面遮蔽不必要個資。</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>功能判準：customer_consent_method 區分 liff_full / flex_simple_fallback。
+          <t>功能判準：兩種交付路徑都可完成同意；過期/錯誤 token 顯示明確錯誤；畫面不暴露 token hash 或非必要個資。
 副作用判準：畫面不得顯示假成功；後端未成功時資料不得變更。</t>
         </is>
       </c>
@@ -43841,12 +45540,12 @@
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>任一主要 API、網路或頁面錯誤都顯示可理解的狀態、影響與下一步建議；錯誤不導致整個應用程式崩潰。</t>
+          <t>任一主要 API、網路、頁面或需認證媒體載入錯誤都顯示可理解的狀態、影響與下一步建議；錯誤不導致整個應用程式崩潰。</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>功能判準：任何 API 失敗有友善 UI。
+          <t>功能判準：每種錯誤都有可理解提示與下一步；照片失敗顯示佔位，任何單點錯誤都不造成整站崩潰或假成功。
 副作用判準：畫面不得顯示假成功；後端未成功時資料不得變更。</t>
         </is>
       </c>
@@ -44217,7 +45916,7 @@
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>功能判準：主通道採唯讀 API 增量汲取，事件處理即時增量，每日批次 reconciliation 補齊遺漏資料；來源來源追溯資料完整率 100%，同一 source_id 重跑不得產生重複資料。。
+          <t>功能判準：主通道採唯讀 API 增量汲取，事件處理即時增量，每日批次 reconciliation 補齊遺漏資料；來源追溯資料完整率 100%，同一 source_id 重跑不得產生重複資料。
 副作用判準：未核可、拒絕、錯來源或錯租戶內容寫入筆數必須為 0。</t>
         </is>
       </c>
@@ -45591,7 +47290,7 @@
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>通過標準：p95 &lt; 300ms；50 位並行使用者、15 分鐘穩定負載，錯誤率 &lt; 1%。</t>
+          <t>通過標準：p95 &lt; 300ms；本次為受控設計門檻，必須保存實測報表後才可標示通過。</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -45695,7 +47394,7 @@
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>通過標準：p95 &lt; 300ms；10,000 筆技師基準資料、50 位並行使用者、15 分鐘穩定負載，錯誤率 &lt; 1%。</t>
+          <t>通過標準：POST /technicians:match p95 &lt; 300ms；本次為受控設計門檻，必須保存讀取路由與實測報表後才可標示通過。</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -45903,7 +47602,7 @@
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>通過標準：≤ 3s；Lighthouse mobile / Fast 4G / 4× CPU slowdown，5 次測試中位數。</t>
+          <t>通過標準：web 首次內容繪製 FCP ≤ 3s；以各站 Lighthouse 或 RUM 結果逐站裁定。</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -47827,7 +49526,7 @@
       </c>
       <c r="F117" s="13" t="inlineStr">
         <is>
-          <t>通過標準：agent → api X-Internal-Token（api 側驗證失敗時一律拒絕、常數時間比對）；品牌 api → 技師媒合服務採 Casdoor 登入憑證 OAuth 2.0 client_credentials，JWT 必驗 issuer/audience/expiry，無效或過期憑證 100% 回 401。</t>
+          <t>通過標準：agent → api 使用 X-Internal-Token，驗證失敗即拒絕且採常數時間比對；品牌 api → OHS 仍屬 TO-BE，服務憑證機制未經 ADR 定版與負向測試前，本項只能標示阻擋，不得標示通過。</t>
         </is>
       </c>
       <c r="G117" s="13" t="inlineStr">
@@ -49335,7 +51034,7 @@
       </c>
       <c r="F146" s="14" t="inlineStr">
         <is>
-          <t>通過標準：上線候選內容 100% 經人工審核；每版不足 100 筆時全驗，否則至少抽驗 100 筆且不低於該版 10%；一般內容誤放率 ≤ 1%，高風險內容誤放 1 筆即阻擋發布。</t>
+          <t>通過標準：每次發布須保存人工審核筆數、核可通過率與抽樣誤放率；Data 負責人尚未核定數值門檻前，本項只能標示阻擋，不得標示通過。</t>
         </is>
       </c>
       <c r="G146" s="14" t="inlineStr">
@@ -49803,7 +51502,7 @@
       </c>
       <c r="F155" s="13" t="inlineStr">
         <is>
-          <t>通過標準：原始資產 100% 原樣落 raw object storage，保存 content hash、source URI、acquired_at；至少保留 1 年或至衍生 bronze 退役（取較長者）。</t>
+          <t>通過標準：raw 原始資產須有核准的保存位置、期限、不可變性與刪除例外規則；四項任一未定版即阻擋 raw → bronze 可重建驗收。</t>
         </is>
       </c>
       <c r="G155" s="13" t="inlineStr">
@@ -50219,7 +51918,7 @@
       </c>
       <c r="F163" s="13" t="inlineStr">
         <is>
-          <t>通過標準：每個 RC 以 Playwright 100% 涵蓋九條關鍵流：LINE 建案、報價同意、付款、派工時限目標、技師接拒單/到場/現場重新報價、結算退款、跨租戶拒絕、知識人工審核發布、租戶開站/使用授權。</t>
+          <t>通過標準：Playwright 至少涵蓋登入、品牌後台關鍵頁、問題卡／工單主要流程、錯誤回復及技師接案→到場→完工；CI 任一關鍵案例失敗即阻擋發布。</t>
         </is>
       </c>
       <c r="G163" s="13" t="inlineStr">
@@ -50234,7 +51933,7 @@
       </c>
       <c r="I163" s="13" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J163" s="15" t="inlineStr">

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_整合測試計畫.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_整合測試計畫.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④ 旅程驗收腳本" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 測試案例主表'!$A$1:$M$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 測試案例主表'!$A$1:$M$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 需求覆蓋（需求 × 案例）'!$A$1:$I$172</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'④ 旅程驗收腳本'!$A$1:$K$20</definedName>
   </definedNames>
@@ -129,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -158,22 +158,13 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -711,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M98"/>
+  <dimension ref="A1:M131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -839,7 +830,7 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-02、SC-17</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr"/>
@@ -941,7 +932,7 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-01、SC-15</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr"/>
@@ -992,7 +983,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>SC-03、SC-10</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr"/>
@@ -1094,7 +1085,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-01、SC-04、SC-06</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr"/>
@@ -1196,7 +1187,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr"/>
@@ -1247,7 +1238,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-01、SC-02</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr"/>
@@ -1298,7 +1289,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-02、SC-10</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr"/>
@@ -1451,7 +1442,7 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-03、SC-04</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr"/>
@@ -2318,7 +2309,7 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-04、SC-07、SC-08</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr"/>
@@ -2624,7 +2615,7 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>SC-05、SC-12、SC-14</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr"/>
@@ -2726,7 +2717,7 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>SC-02、SC-05、SC-06、SC-10</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr"/>
@@ -2828,7 +2819,7 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>SC-05、SC-06、SC-13</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr"/>
@@ -2879,7 +2870,7 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>SC-05、SC-12、SC-14</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr"/>
@@ -3185,7 +3176,7 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>SC-06</t>
+          <t>SC-06、SC-07</t>
         </is>
       </c>
       <c r="J48" s="6" t="inlineStr"/>
@@ -3440,7 +3431,7 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>SC-08</t>
+          <t>SC-06、SC-08、SC-09</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr"/>
@@ -3695,7 +3686,7 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>SC-19</t>
+          <t>SC-11、SC-18、SC-19</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr"/>
@@ -3793,7 +3784,7 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SC-11、SC-16</t>
         </is>
       </c>
       <c r="J60" s="6" t="inlineStr"/>
@@ -4169,7 +4160,7 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="J68" s="6" t="inlineStr"/>
@@ -4216,7 +4207,7 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SC-01、SC-02、SC-19</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr"/>
@@ -4310,7 +4301,7 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SC-12、SC-17</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr"/>
@@ -4404,7 +4395,7 @@
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SC-02、SC-10</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr"/>
@@ -4451,7 +4442,7 @@
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>SC-02</t>
+          <t>SC-02、SC-09、SC-11、SC-19</t>
         </is>
       </c>
       <c r="J74" s="6" t="inlineStr"/>
@@ -4498,7 +4489,7 @@
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SC-18</t>
         </is>
       </c>
       <c r="J75" s="6" t="inlineStr"/>
@@ -4639,7 +4630,7 @@
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SC-17</t>
         </is>
       </c>
       <c r="J78" s="6" t="inlineStr"/>
@@ -4686,7 +4677,7 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SC-05、SC-13、SC-14</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr"/>
@@ -4729,7 +4720,7 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SC-01、SC-02</t>
         </is>
       </c>
       <c r="J80" s="6" t="inlineStr"/>
@@ -4815,7 +4806,7 @@
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SC-05</t>
         </is>
       </c>
       <c r="J82" s="6" t="inlineStr"/>
@@ -5331,7 +5322,7 @@
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-01、SC-06</t>
         </is>
       </c>
       <c r="J94" s="6" t="inlineStr"/>
@@ -5527,10 +5518,1693 @@
       <c r="L98" s="6" t="inlineStr"/>
       <c r="M98" s="6" t="inlineStr"/>
     </row>
+    <row r="99" ht="44" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>TC-AGT-TURN-01</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>可注入 session store / SAVE 失敗的 agent fixture</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>對同一 webhook 依序注入 RESTORE、compact、tool call 與 SAVE 寫入失敗</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>一個 webhook 只產生一個 Turn；SAVE 失敗記 trace/告警但仍回覆；不重複寫 memory 或重送訊息</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>FR-AGT-02</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>SC-01、SC-10</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="inlineStr"/>
+      <c r="K99" s="6" t="inlineStr"/>
+      <c r="L99" s="6" t="inlineStr"/>
+      <c r="M99" s="6" t="inlineStr"/>
+    </row>
+    <row r="100" ht="44" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>TC-AGT-CLARIFY-01</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>已確認問題卡、可控 RAG fixture</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>連續三輪客戶回覆未釐清，再送已釐清；另注入低相似度案例</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>未釐清依規則轉真人；已釐清寫 confirmation；低相似度不假稱命中案例</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>FR-AGT-03</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J100" s="6" t="inlineStr"/>
+      <c r="K100" s="6" t="inlineStr"/>
+      <c r="L100" s="6" t="inlineStr"/>
+      <c r="M100" s="6" t="inlineStr"/>
+    </row>
+    <row r="101" ht="44" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>TC-AGT-URG-01</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>四種急件 intent 與 transfer API 故障 fixture</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>各送急件訊息；令第一次 ingest 失敗後重試</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>5 分鐘內建立可追溯轉人紀錄；第一次失敗不得假稱已派工，重試後只留一筆 escalation</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>FR-AGT-04</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="inlineStr"/>
+      <c r="K101" s="6" t="inlineStr"/>
+      <c r="L101" s="6" t="inlineStr"/>
+      <c r="M101" s="6" t="inlineStr"/>
+    </row>
+    <row r="102" ht="44" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>TC-AGT-RAG-01</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>租戶 A/B pgvector fixture、MCP 可觀測 stub</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>查存在／不存在／他租戶型號，並令 MCP timeout</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>僅回本租戶可引用事實；不存在或 timeout 回 references／轉人降級，不編造型號或跨租戶內容</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>FR-AGT-07、FR-DAT-04</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>SC-15</t>
+        </is>
+      </c>
+      <c r="J102" s="6" t="inlineStr"/>
+      <c r="K102" s="6" t="inlineStr"/>
+      <c r="L102" s="6" t="inlineStr"/>
+      <c r="M102" s="6" t="inlineStr"/>
+    </row>
+    <row r="103" ht="44" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>TC-PLT-PROV-01</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>新品牌申請、License、LINE sandbox、可重建 bundle fixture</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>核准後建庫、配置、綁定 LINE、health check；中途讓建庫或綁定失敗後重跑</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>未完成任一步不得啟用 License；重跑冪等且有 provisioning audit；成功後僅新品牌可登入與進線</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>FR-PLT-03</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>SC-17</t>
+        </is>
+      </c>
+      <c r="J103" s="6" t="inlineStr"/>
+      <c r="K103" s="6" t="inlineStr"/>
+      <c r="L103" s="6" t="inlineStr"/>
+      <c r="M103" s="6" t="inlineStr"/>
+    </row>
+    <row r="104" ht="44" customHeight="1">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>TC-PLT-FLOW-01</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>合法與非法 Flow DSL/Block fixture</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>匯入合法 DSL，再匯入未知 block、缺 guard、非法狀態轉移與破壞性版本</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>非法檔在發佈前被靜態拒絕且無 runtime side effect；合法版本可審計、可回退</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>FR-PLT-07</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>SC-18</t>
+        </is>
+      </c>
+      <c r="J104" s="6" t="inlineStr"/>
+      <c r="K104" s="6" t="inlineStr"/>
+      <c r="L104" s="6" t="inlineStr"/>
+      <c r="M104" s="6" t="inlineStr"/>
+    </row>
+    <row r="105" ht="44" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>TC-PLT-CFG-01</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>可變更 skill/config 版本、保護層、canary tenant</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>發佈新版、嘗試覆寫 domain-safety、製造 eval/SLO 失敗，再 rollback</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>保護層不可覆寫；失敗時停止擴散並回上一版；版本、審核、測試與 rollback 全留 audit</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>FR-PLT-08</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>SC-18</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="inlineStr"/>
+      <c r="K105" s="6" t="inlineStr"/>
+      <c r="L105" s="6" t="inlineStr"/>
+      <c r="M105" s="6" t="inlineStr"/>
+    </row>
+    <row r="106" ht="44" customHeight="1">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>TC-PLT-SURFACE-01</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>brand/tech/platform token 與三面 API</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>交叉呼叫敏感端點、帶缺 portal claim 舊 token、平台 token 查品牌資料</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>不允許的跨面一律 403；platform 走獨立 guard/資料庫；拒絕前不讀取目標業務資料</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>FR-PLT-09</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>SC-12、SC-14、SC-17</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="inlineStr"/>
+      <c r="K106" s="6" t="inlineStr"/>
+      <c r="L106" s="6" t="inlineStr"/>
+      <c r="M106" s="6" t="inlineStr"/>
+    </row>
+    <row r="107" ht="44" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>TC-REF-INTAKE-01</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>knowledge_ready/未完成問題卡、外部素材、兩租戶 fixture</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>從准許與未准許來源汲取；重送同素材；模擬來源讀取失敗</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>僅符合 gate 的資料進 bronze；失敗／重送不產生半成品或跨租戶資料；來源與失敗原因可稽核</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>FR-DAT-01、FR-REF-01</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="inlineStr"/>
+      <c r="K107" s="6" t="inlineStr"/>
+      <c r="L107" s="6" t="inlineStr"/>
+      <c r="M107" s="6" t="inlineStr"/>
+    </row>
+    <row r="108" ht="44" customHeight="1">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>TC-REF-SPLIT-01</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>含事實、行為指令、惡意覆寫 prompt 的 silver fixture</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>執行 refine，檢查 facts/behavior 分流與 re-refine</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>事實只進 fact draft、行為只進 skill diff；未核可 draft 不改既有內容；重跑 append-only 可回溯</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>FR-REF-02</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>SC-15</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="inlineStr"/>
+      <c r="K108" s="6" t="inlineStr"/>
+      <c r="L108" s="6" t="inlineStr"/>
+      <c r="M108" s="6" t="inlineStr"/>
+    </row>
+    <row r="109" ht="44" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>TC-REF-PUBLISH-01</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>approved/rejected/high-risk draft、兩租戶、Family Reviewer fixture</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>嘗試未核可發布、同人雙簽、Family Reviewer 逾時、來源非 bronze、跨租戶 publish</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>違規均零落地；核可後 facts 帶 tenant/provenance 進 pgvector、行為 append-only 發佈；逾時暫停並升級</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>FR-REF-03、FR-REF-04、FR-REF-05</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>SC-15、SC-16</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="inlineStr"/>
+      <c r="K109" s="6" t="inlineStr"/>
+      <c r="L109" s="6" t="inlineStr"/>
+      <c r="M109" s="6" t="inlineStr"/>
+    </row>
+    <row r="110" ht="44" customHeight="1">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>TC-TEC-LIFE-01</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>未註冊、已註冊、跨品牌申請技師 fixture</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>註冊、補 KYC、指定服務品牌、重送註冊、未核可身分嘗試接單</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>身分只寫 lock_tech；重送冪等；未核可或未授權者永不進候選池</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>FR-TEC-01</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>SC-12</t>
+        </is>
+      </c>
+      <c r="J110" s="6" t="inlineStr"/>
+      <c r="K110" s="6" t="inlineStr"/>
+      <c r="L110" s="6" t="inlineStr"/>
+      <c r="M110" s="6" t="inlineStr"/>
+    </row>
+    <row r="111" ht="44" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>TC-TEC-REVOKE-01</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>已排班且已獲品牌授權技師、兩品牌候選池</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>撤銷認證、停權、復權、重送事件並檢查候選集與通知</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>撤銷/停權後各品牌候選集立即排除；重送不重複通知；復權前不得自行恢復可派狀態</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>FR-TEC-08</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>SC-14</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="inlineStr"/>
+      <c r="K111" s="6" t="inlineStr"/>
+      <c r="L111" s="6" t="inlineStr"/>
+      <c r="M111" s="6" t="inlineStr"/>
+    </row>
+    <row r="112" ht="44" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>TC-DISPATCH-09</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>可控候選池、急件規則、通知與技師 availability fixture</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>先令候選池為空，再加入不合格技師、合格技師；模擬第一次通知失敗後重試</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>空池只能進 dispatch_pending 並 alert；不合格者永不入選；合格者出現後按急件規則媒合；重試不重複指派或通知</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-05</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>SC-05、SC-14</t>
+        </is>
+      </c>
+      <c r="J112" s="6" t="inlineStr"/>
+      <c r="K112" s="6" t="inlineStr"/>
+      <c r="L112" s="6" t="inlineStr"/>
+      <c r="M112" s="6" t="inlineStr"/>
+    </row>
+    <row r="113" ht="44" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>TC-PAYMENT-01</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>支付 provider webhook stub、可控 idempotency key 與 dispute fixture</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>分別送 provider 拒絕、timeout 後相同 key 重送、已收款後 dispute</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>拒絕/timeout 不落成功帳；重送至多一筆收款與憑證；dispute 建立可稽核例外且不以重複扣款恢復</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-10</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>SC-08</t>
+        </is>
+      </c>
+      <c r="J113" s="6" t="inlineStr"/>
+      <c r="K113" s="6" t="inlineStr"/>
+      <c r="L113" s="6" t="inlineStr"/>
+      <c r="M113" s="6" t="inlineStr"/>
+    </row>
+    <row r="114" ht="44" customHeight="1">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>TC-WEB-SURFACE-01</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>dispatch/tech/platform/landing production-like build</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>各 build 直接開啟本站外路徑、deep link、跨站 CTA 與不存在路徑</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>只呈現白名單路徑或安全導向；不得把非本站頁面當已授權內容載入</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>FR-WEB-01</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>SC-12、SC-17</t>
+        </is>
+      </c>
+      <c r="J114" s="6" t="inlineStr"/>
+      <c r="K114" s="6" t="inlineStr"/>
+      <c r="L114" s="6" t="inlineStr"/>
+      <c r="M114" s="6" t="inlineStr"/>
+    </row>
+    <row r="115" ht="44" customHeight="1">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>TC-WEB-REPORT-01</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>固定 KPI/API fixture、admin/ops/cs token</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>比對 dashboard/API 值、匯出報表、令 API 403/timeout、低權角色讀敏感報表</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>數字、時區與篩選一致；低權角色 403；失敗時不顯示舊租戶資料</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>FR-WEB-04</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>SC-08、SC-09</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="inlineStr"/>
+      <c r="K115" s="6" t="inlineStr"/>
+      <c r="L115" s="6" t="inlineStr"/>
+      <c r="M115" s="6" t="inlineStr"/>
+    </row>
+    <row r="116" ht="44" customHeight="1">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>TC-NFR-A11Y-01</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>四 portal + LIFF keyboard/axe fixture</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>跑 axe、鍵盤流程、縮放 200%、斷網重試</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>critical a11y=0；焦點、錯誤與對比可用；斷網不靜默遺失表單</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>boundary+recovery</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>NFR-A11y-001、NFR-A11y-003、NFR-A11y-004、NFR-A11y-005</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J116" s="6" t="inlineStr"/>
+      <c r="K116" s="6" t="inlineStr"/>
+      <c r="L116" s="6" t="inlineStr"/>
+      <c r="M116" s="6" t="inlineStr"/>
+    </row>
+    <row r="117" ht="44" customHeight="1">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>TC-NFR-AUD-01</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>audit/trace、敏感 mutation 與匯出 fixture</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>送成功與拒絕 mutation、LLM/transfer、手動竄改／刪除與匯出</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>actor、原因、版本、trace 與 hash 可還原；竄改被驗出；匯出受權限、tenant 與遮罩控制</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>NFR-Aud-002、NFR-Aud-003、NFR-Aud-005、NFR-Aud-006、NFR-Aud-007</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J117" s="6" t="inlineStr"/>
+      <c r="K117" s="6" t="inlineStr"/>
+      <c r="L117" s="6" t="inlineStr"/>
+      <c r="M117" s="6" t="inlineStr"/>
+    </row>
+    <row r="118" ht="44" customHeight="1">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>TC-NFR-AVAIL-01</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>production-like 依賴替身與告警接收者</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>逐一中斷 DB、LINE、LLM、RAG、OHS、Casdoor、Redis、Kafka、Refinery 與排程 leader</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>各故障走 NFR 指定 fail-closed/降級/重試/DLQ；告警可收到；復原後不重複副作用</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>NFR-Avail-001、NFR-Avail-002、NFR-Avail-003、NFR-Avail-004、NFR-Avail-005、NFR-Avail-006、NFR-Avail-007、NFR-Avail-008、NFR-Avail-009、NFR-Avail-011</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J118" s="6" t="inlineStr"/>
+      <c r="K118" s="6" t="inlineStr"/>
+      <c r="L118" s="6" t="inlineStr"/>
+      <c r="M118" s="6" t="inlineStr"/>
+    </row>
+    <row r="119" ht="44" customHeight="1">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>TC-NFR-DORA-01</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>staging、變更與 rollback fixture</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>執行可追溯 release、製造失敗並 rollback，收集 DORA 指標</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>四項 DORA 指標可計算且來源一致；rollback 不遺失 migration/audit 證據</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>NFR-DORA-001、NFR-DORA-002、NFR-DORA-003</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J119" s="6" t="inlineStr"/>
+      <c r="K119" s="6" t="inlineStr"/>
+      <c r="L119" s="6" t="inlineStr"/>
+      <c r="M119" s="6" t="inlineStr"/>
+    </row>
+    <row r="120" ht="44" customHeight="1">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>TC-NFR-DQ-01</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>可竄改 provenance 與審核抽樣 fixture</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>令 LLM 回傳假 source/source_type；抽樣核對核可與誤放資料</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>Python 覆寫不可信 provenance；核可率與誤放率可計算入報表</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>NFR-DQ-002、NFR-DQ-004</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J120" s="6" t="inlineStr"/>
+      <c r="K120" s="6" t="inlineStr"/>
+      <c r="L120" s="6" t="inlineStr"/>
+      <c r="M120" s="6" t="inlineStr"/>
+    </row>
+    <row r="121" ht="44" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>TC-NFR-MAINT-01</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>CI、破壞 OpenAPI、跨服務、Playwright fixture</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>跑 coverage/typecheck；提交 breaking contract、consumer 不相容事件、未知 skill/front-end flow</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>CI 在違規處失敗；契約與 ADR/DR 可回查；關鍵流程 E2E 可重跑</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>NFR-Maint-001、NFR-Maint-002、NFR-Maint-003、NFR-Maint-004、NFR-Maint-005、NFR-Maint-006、NFR-Maint-007、NFR-Maint-008</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J121" s="6" t="inlineStr"/>
+      <c r="K121" s="6" t="inlineStr"/>
+      <c r="L121" s="6" t="inlineStr"/>
+      <c r="M121" s="6" t="inlineStr"/>
+    </row>
+    <row r="122" ht="44" customHeight="1">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>TC-NFR-OBS-01</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>OTel/PII scrub、故障與高延遲 fixture</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>產生 request/LLM/worker trace、植入 PII、觸發 error/lag/SLO breach</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>trace 可串接；PII 不外送；dashboard/alert 顯示正確維度與 recovery 狀態</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>NFR-Obs-001、NFR-Obs-002、NFR-Obs-003、NFR-Obs-004、NFR-Obs-005</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J122" s="6" t="inlineStr"/>
+      <c r="K122" s="6" t="inlineStr"/>
+      <c r="L122" s="6" t="inlineStr"/>
+      <c r="M122" s="6" t="inlineStr"/>
+    </row>
+    <row r="123" ht="44" customHeight="1">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>TC-NFR-PUB-01</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>draft、approved revision、錯來源與跨 tenant fixture</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>未核可 publish、刪除既有 skill、來源不同步、tenant A 查 B 語料</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>未核可零落地；更新 append-only；同源檢查失敗即阻擋；跨租戶 default deny</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>NFR-PUB-001、NFR-PUB-002、NFR-PUB-003、NFR-PUB-004</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>SC-15</t>
+        </is>
+      </c>
+      <c r="J123" s="6" t="inlineStr"/>
+      <c r="K123" s="6" t="inlineStr"/>
+      <c r="L123" s="6" t="inlineStr"/>
+      <c r="M123" s="6" t="inlineStr"/>
+    </row>
+    <row r="124" ht="44" customHeight="1">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>TC-NFR-PERF-01</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>k6、RUM、WS、RAG、OHS 與 config cache fixture</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>依 NFR 指定併發壓測，逐一令 RAG/WS/OHS/快取過載或中斷</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>保存 p95/p99、錯誤率與降級行為；超門檻或資料不足一律 Fail/Blocked，不以估計值通過</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>NFR-Perf-001、NFR-Perf-002、NFR-Perf-003、NFR-Perf-004、NFR-Perf-005、NFR-Perf-006、NFR-Perf-007、NFR-Perf-008、NFR-Perf-010、NFR-Perf-011、NFR-Perf-012</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>SC-01、SC-05、SC-18</t>
+        </is>
+      </c>
+      <c r="J124" s="6" t="inlineStr"/>
+      <c r="K124" s="6" t="inlineStr"/>
+      <c r="L124" s="6" t="inlineStr"/>
+      <c r="M124" s="6" t="inlineStr"/>
+    </row>
+    <row r="125" ht="44" customHeight="1">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>TC-NFR-PRIV-01</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>PII、consent、retention/legal-hold、跨租戶 fixture</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>讀寫敏感欄、撤回 consent、forget、legal hold、查 log/backup/export</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>加密/遮罩/最小權限生效；legal hold 阻止刪除；保留期限與第三方處理可稽核</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>NFR-Priv-001、NFR-Priv-002、NFR-Priv-003、NFR-Priv-004、NFR-Priv-007、NFR-Priv-009、NFR-Priv-010</t>
+        </is>
+      </c>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J125" s="6" t="inlineStr"/>
+      <c r="K125" s="6" t="inlineStr"/>
+      <c r="L125" s="6" t="inlineStr"/>
+      <c r="M125" s="6" t="inlineStr"/>
+    </row>
+    <row r="126" ht="44" customHeight="1">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>TC-NFR-REL-01</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>agent transfer、outbox、依賴中斷與重送 fixture</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>在 transfer/push/寫入各階段中斷，再重送 webhook 或恢復服務</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>不遺失案件、不重複副作用；真承諾一定有 escalation/問題卡；恢復後可對帳</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>NFR-Rel-001、NFR-Rel-002、NFR-Rel-003</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>SC-02、SC-03</t>
+        </is>
+      </c>
+      <c r="J126" s="6" t="inlineStr"/>
+      <c r="K126" s="6" t="inlineStr"/>
+      <c r="L126" s="6" t="inlineStr"/>
+      <c r="M126" s="6" t="inlineStr"/>
+    </row>
+    <row r="127" ht="44" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>TC-NFR-REP-01</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>固定 raw、config 與保存位置 fixture</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>重跑 pipeline、變更 config、移除 raw 後嘗試 rebuild</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>相同輸入產同結構結果；保存不足時明確阻擋並保留稽核</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>NFR-Rep-001、NFR-Rep-002</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J127" s="6" t="inlineStr"/>
+      <c r="K127" s="6" t="inlineStr"/>
+      <c r="L127" s="6" t="inlineStr"/>
+      <c r="M127" s="6" t="inlineStr"/>
+    </row>
+    <row r="128" ht="44" customHeight="1">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>TC-NFR-SLA-01</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>可控時鐘、派工、push/email/on-call fixture</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>在 T+2:00:00/T+2:00:01、技師主動延遲、push 失敗與主管離線時執行</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>邊界判定正確；標紅、retry、email fallback 與升級鏈可觀測且不重複通知</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>NFR-SLA-001、NFR-SLA-002、NFR-SLA-003</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>SC-05、SC-06</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="inlineStr"/>
+      <c r="K128" s="6" t="inlineStr"/>
+      <c r="L128" s="6" t="inlineStr"/>
+      <c r="M128" s="6" t="inlineStr"/>
+    </row>
+    <row r="129" ht="44" customHeight="1">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>TC-NFR-SCAL-01</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>多實例、WS/Redis、技師與租戶階梯負載 fixture</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>逐段增加租戶、技師、WS、queue 與 DB connection 負載，並模擬單一實例離線</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>容量指標、限流與降級符合 NFR；無跨租戶事件、雙重排程或無聲遺失</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>NFR-Scal-003、NFR-Scal-004、NFR-Scal-005、NFR-Scal-006、NFR-Scal-007、NFR-Scal-008</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>SC-05</t>
+        </is>
+      </c>
+      <c r="J129" s="6" t="inlineStr"/>
+      <c r="K129" s="6" t="inlineStr"/>
+      <c r="L129" s="6" t="inlineStr"/>
+      <c r="M129" s="6" t="inlineStr"/>
+    </row>
+    <row r="130" ht="44" customHeight="1">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>TC-NFR-SCH-01</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>空庫、升級庫、已套 migration 與 drift fixture</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>逐庫套用、重套、注入 schema drift、嘗試 down migration</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>migrations 可重套、drift 被擋、只允許 forward 演進；備份/還原證據可回查</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>failure+recovery</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>NFR-Sch-001、NFR-Sch-003</t>
+        </is>
+      </c>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J130" s="6" t="inlineStr"/>
+      <c r="K130" s="6" t="inlineStr"/>
+      <c r="L130" s="6" t="inlineStr"/>
+      <c r="M130" s="6" t="inlineStr"/>
+    </row>
+    <row r="131" ht="44" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>TC-NFR-SEC-01</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>13. 追溯缺口收斂案例（TC-AGT / TC-NFR / TC-UAT）</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>偽造 token、prompt、CVE/secret scan fixture</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>重放/偽造 token、prompt injection、違規輸出、洩密掃描與高危 CVE 演練</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>未授權與違規輸出 fail-closed；secret/CVE 在時限內告警與追蹤；無敏感副作用</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>failure</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>NFR-Sec-001、NFR-Sec-002、NFR-Sec-004、NFR-Sec-007、NFR-Sec-013、NFR-Sec-014</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J131" s="6" t="inlineStr"/>
+      <c r="K131" s="6" t="inlineStr"/>
+      <c r="L131" s="6" t="inlineStr"/>
+      <c r="M131" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M98"/>
+  <autoFilter ref="A1:M131"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J98" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="只能填 Pass/Fail/Blocked/N/A" type="list">
+    <dataValidation sqref="J2:J131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="只能填 Pass/Fail/Blocked/N/A" type="list">
       <formula1>"Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5673,23 +7347,19 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-AGT-TURN-01</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -5718,23 +7388,19 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>happy、boundary</t>
+          <t>happy、boundary、recovery</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>TC-CS-AI-03、TC-CS-AI-12</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+          <t>TC-AGT-CLARIFY-01、TC-CS-AI-03、TC-CS-AI-12</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -5763,23 +7429,19 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、recovery</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>TC-COMPLIANCE-07、TC-CS-AI-04</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+          <t>TC-AGT-URG-01、TC-COMPLIANCE-07、TC-CS-AI-04</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -5853,7 +7515,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -5861,11 +7523,7 @@
           <t>TC-SEC-MEM-01</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+      <c r="I7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -5894,23 +7552,19 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>TC-COMPLIANCE-08、TC-CS-AI-03</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+          <t>TC-AGT-RAG-01、TC-COMPLIANCE-08、TC-CS-AI-03</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -5943,7 +7597,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -5951,11 +7605,7 @@
           <t>TC-SEC-TOOL-01</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+      <c r="I9" s="5" t="inlineStr"/>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -6271,23 +7921,19 @@
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>TC-DISPATCH-01</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+          <t>TC-DISPATCH-01、TC-DISPATCH-09</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr"/>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -6480,23 +8126,19 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>TC-SEC-IDEM-01</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+          <t>TC-PAYMENT-01、TC-SEC-IDEM-01</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr"/>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -6611,7 +8253,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -6619,11 +8261,7 @@
           <t>TC-SEC-INT-01</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+      <c r="I25" s="5" t="inlineStr"/>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -6656,7 +8294,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -6664,11 +8302,7 @@
           <t>TC-EXC-06</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+      <c r="I26" s="5" t="inlineStr"/>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -6701,7 +8335,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -6709,11 +8343,7 @@
           <t>TC-EXC-01</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+      <c r="I27" s="5" t="inlineStr"/>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -6746,7 +8376,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -6754,11 +8384,7 @@
           <t>TC-COMPLIANCE-01、TC-COMPLIANCE-02、TC-COMPLIANCE-04</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+      <c r="I28" s="5" t="inlineStr"/>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -6910,23 +8536,19 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-WEB-SURFACE-01</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr"/>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -7037,23 +8659,19 @@
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-WEB-REPORT-01</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr"/>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
@@ -7205,23 +8823,19 @@
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>TC-COMPLIANCE-08</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+          <t>TC-COMPLIANCE-08、TC-REF-INTAKE-01</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr"/>
     </row>
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
@@ -7295,7 +8909,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -7303,11 +8917,7 @@
           <t>TC-EXC-05、TC-SEC-TENANT-01</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+      <c r="I41" s="5" t="inlineStr"/>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
@@ -7336,23 +8946,19 @@
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>TC-CS-AI-03</t>
-        </is>
-      </c>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+          <t>TC-AGT-RAG-01、TC-CS-AI-03</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr"/>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
@@ -7463,23 +9069,19 @@
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>TC-COMPLIANCE-08</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+          <t>TC-COMPLIANCE-08、TC-REF-INTAKE-01</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr"/>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
@@ -7508,23 +9110,19 @@
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-REF-SPLIT-01</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr"/>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -7553,23 +9151,19 @@
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>TC-COMPLIANCE-05</t>
-        </is>
-      </c>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+          <t>TC-COMPLIANCE-05、TC-REF-PUBLISH-01</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr"/>
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
@@ -7598,23 +9192,19 @@
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>TC-COMPLIANCE-08</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+          <t>TC-COMPLIANCE-08、TC-REF-PUBLISH-01</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr"/>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -7643,23 +9233,19 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>TC-COMPLIANCE-05</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+          <t>TC-COMPLIANCE-05、TC-REF-PUBLISH-01</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr"/>
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
@@ -7688,23 +9274,19 @@
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I50" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-TEC-LIFE-01</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr"/>
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
@@ -7979,23 +9561,19 @@
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-TEC-REVOKE-01</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr"/>
     </row>
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
@@ -8028,7 +9606,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
@@ -8036,11 +9614,7 @@
           <t>TC-SEC-WEB-02</t>
         </is>
       </c>
-      <c r="I58" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+      <c r="I58" s="5" t="inlineStr"/>
     </row>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
@@ -8073,7 +9647,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
@@ -8081,11 +9655,7 @@
           <t>TC-SEC-RBAC-01、TC-SEC-RBAC-02、TC-SEC-RBAC-03、TC-SEC-RBAC-04、TC-SEC-RBAC-05</t>
         </is>
       </c>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+      <c r="I59" s="5" t="inlineStr"/>
     </row>
     <row r="60" ht="26" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
@@ -8114,23 +9684,19 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-PLT-PROV-01</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr"/>
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
@@ -8163,7 +9729,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -8171,11 +9737,7 @@
           <t>TC-EXC-06</t>
         </is>
       </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+      <c r="I61" s="5" t="inlineStr"/>
     </row>
     <row r="62" ht="26" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
@@ -8286,23 +9848,19 @@
         </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I64" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-PLT-FLOW-01</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr"/>
     </row>
     <row r="65" ht="26" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
@@ -8331,23 +9889,19 @@
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I65" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-PLT-CFG-01</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr"/>
     </row>
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
@@ -8376,23 +9930,19 @@
         </is>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-PLT-SURFACE-01</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr"/>
     </row>
     <row r="67" ht="26" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
@@ -8421,23 +9971,19 @@
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>TC-PERF-01、TC-PERF-02</t>
-        </is>
-      </c>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PERF-01、TC-PERF-01、TC-PERF-02</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr"/>
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
@@ -8466,23 +10012,19 @@
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I68" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PERF-01</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr"/>
     </row>
     <row r="69" ht="26" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
@@ -8511,23 +10053,19 @@
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PERF-01</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr"/>
     </row>
     <row r="70" ht="26" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
@@ -8556,23 +10094,19 @@
         </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PERF-01</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr"/>
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
@@ -8601,23 +10135,19 @@
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PERF-01</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr"/>
     </row>
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
@@ -8646,23 +10176,19 @@
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PERF-01</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr"/>
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
@@ -8691,23 +10217,19 @@
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>TC-PERF-03</t>
-        </is>
-      </c>
-      <c r="I73" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PERF-01、TC-PERF-03</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr"/>
     </row>
     <row r="74" ht="26" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
@@ -8736,23 +10258,19 @@
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PERF-01</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr"/>
     </row>
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
@@ -8822,23 +10340,19 @@
         </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PERF-01</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr"/>
     </row>
     <row r="77" ht="26" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
@@ -8867,23 +10381,19 @@
         </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PERF-01</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr"/>
     </row>
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
@@ -8912,23 +10422,19 @@
         </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PERF-01</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr"/>
     </row>
     <row r="79" ht="26" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
@@ -8957,23 +10463,19 @@
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-AVAIL-01</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr"/>
     </row>
     <row r="80" ht="26" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
@@ -9002,23 +10504,19 @@
         </is>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-AVAIL-01</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr"/>
     </row>
     <row r="81" ht="26" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
@@ -9047,23 +10545,19 @@
         </is>
       </c>
       <c r="F81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-AVAIL-01</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr"/>
     </row>
     <row r="82" ht="26" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
@@ -9092,23 +10586,19 @@
         </is>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-AVAIL-01</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr"/>
     </row>
     <row r="83" ht="26" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
@@ -9137,23 +10627,19 @@
         </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-AVAIL-01</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr"/>
     </row>
     <row r="84" ht="26" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
@@ -9182,23 +10668,19 @@
         </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I84" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-AVAIL-01</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr"/>
     </row>
     <row r="85" ht="26" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
@@ -9227,23 +10709,19 @@
         </is>
       </c>
       <c r="F85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I85" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-AVAIL-01</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr"/>
     </row>
     <row r="86" ht="26" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
@@ -9272,23 +10750,19 @@
         </is>
       </c>
       <c r="F86" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-AVAIL-01</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr"/>
     </row>
     <row r="87" ht="26" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
@@ -9317,23 +10791,19 @@
         </is>
       </c>
       <c r="F87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-AVAIL-01</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr"/>
     </row>
     <row r="88" ht="26" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
@@ -9403,23 +10873,19 @@
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-AVAIL-01</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr"/>
     </row>
     <row r="90" ht="26" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
@@ -9448,23 +10914,19 @@
         </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I90" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-REL-01</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr"/>
     </row>
     <row r="91" ht="26" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
@@ -9493,23 +10955,19 @@
         </is>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I91" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-REL-01</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr"/>
     </row>
     <row r="92" ht="26" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
@@ -9538,23 +10996,19 @@
         </is>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I92" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-REL-01</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr"/>
     </row>
     <row r="93" ht="26" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
@@ -9583,23 +11037,19 @@
         </is>
       </c>
       <c r="F93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I93" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-SLA-01</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr"/>
     </row>
     <row r="94" ht="26" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
@@ -9628,23 +11078,19 @@
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-SLA-01</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr"/>
     </row>
     <row r="95" ht="26" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
@@ -9673,23 +11119,19 @@
         </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I95" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-SLA-01</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr"/>
     </row>
     <row r="96" ht="26" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
@@ -9800,23 +11242,19 @@
         </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I98" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-SCAL-01</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr"/>
     </row>
     <row r="99" ht="26" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
@@ -9845,23 +11283,19 @@
         </is>
       </c>
       <c r="F99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I99" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-SCAL-01</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr"/>
     </row>
     <row r="100" ht="26" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
@@ -9890,23 +11324,19 @@
         </is>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I100" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-SCAL-01</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr"/>
     </row>
     <row r="101" ht="26" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
@@ -9935,23 +11365,19 @@
         </is>
       </c>
       <c r="F101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I101" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-SCAL-01</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr"/>
     </row>
     <row r="102" ht="26" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
@@ -9980,23 +11406,19 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I102" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-SCAL-01</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr"/>
     </row>
     <row r="103" ht="26" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
@@ -10025,23 +11447,19 @@
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I103" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-SCAL-01</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr"/>
     </row>
     <row r="104" ht="26" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
@@ -10070,23 +11488,19 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I104" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-SEC-01</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr"/>
     </row>
     <row r="105" ht="26" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
@@ -10115,23 +11529,19 @@
         </is>
       </c>
       <c r="F105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I105" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-SEC-01</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr"/>
     </row>
     <row r="106" ht="26" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
@@ -10201,23 +11611,19 @@
         </is>
       </c>
       <c r="F107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I107" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-SEC-01</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr"/>
     </row>
     <row r="108" ht="26" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
@@ -10328,23 +11734,19 @@
         </is>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I110" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-SEC-01</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr"/>
     </row>
     <row r="111" ht="26" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
@@ -10578,23 +11980,19 @@
         </is>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I116" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-SEC-01</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr"/>
     </row>
     <row r="117" ht="26" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
@@ -10623,23 +12021,19 @@
         </is>
       </c>
       <c r="F117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I117" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-SEC-01</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr"/>
     </row>
     <row r="118" ht="26" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
@@ -10668,23 +12062,19 @@
         </is>
       </c>
       <c r="F118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I118" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PRIV-01</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr"/>
     </row>
     <row r="119" ht="26" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
@@ -10713,23 +12103,19 @@
         </is>
       </c>
       <c r="F119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I119" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PRIV-01</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr"/>
     </row>
     <row r="120" ht="26" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
@@ -10758,23 +12144,19 @@
         </is>
       </c>
       <c r="F120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I120" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PRIV-01</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr"/>
     </row>
     <row r="121" ht="26" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
@@ -10803,23 +12185,19 @@
         </is>
       </c>
       <c r="F121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I121" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PRIV-01</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr"/>
     </row>
     <row r="122" ht="26" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
@@ -10930,23 +12308,19 @@
         </is>
       </c>
       <c r="F124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I124" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PRIV-01</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr"/>
     </row>
     <row r="125" ht="26" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
@@ -11016,23 +12390,19 @@
         </is>
       </c>
       <c r="F126" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I126" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PRIV-01</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr"/>
     </row>
     <row r="127" ht="26" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
@@ -11061,23 +12431,19 @@
         </is>
       </c>
       <c r="F127" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I127" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PRIV-01</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr"/>
     </row>
     <row r="128" ht="26" customHeight="1">
       <c r="A128" s="4" t="inlineStr">
@@ -11106,23 +12472,19 @@
         </is>
       </c>
       <c r="F128" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I128" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-OBS-01</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr"/>
     </row>
     <row r="129" ht="26" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
@@ -11151,23 +12513,19 @@
         </is>
       </c>
       <c r="F129" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I129" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-OBS-01</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="inlineStr"/>
     </row>
     <row r="130" ht="26" customHeight="1">
       <c r="A130" s="4" t="inlineStr">
@@ -11196,23 +12554,19 @@
         </is>
       </c>
       <c r="F130" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I130" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-OBS-01</t>
+        </is>
+      </c>
+      <c r="I130" s="5" t="inlineStr"/>
     </row>
     <row r="131" ht="26" customHeight="1">
       <c r="A131" s="4" t="inlineStr">
@@ -11241,23 +12595,19 @@
         </is>
       </c>
       <c r="F131" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I131" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-OBS-01</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="inlineStr"/>
     </row>
     <row r="132" ht="26" customHeight="1">
       <c r="A132" s="4" t="inlineStr">
@@ -11286,23 +12636,19 @@
         </is>
       </c>
       <c r="F132" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I132" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-OBS-01</t>
+        </is>
+      </c>
+      <c r="I132" s="5" t="inlineStr"/>
     </row>
     <row r="133" ht="26" customHeight="1">
       <c r="A133" s="4" t="inlineStr">
@@ -11372,23 +12718,19 @@
         </is>
       </c>
       <c r="F134" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I134" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-AUD-01</t>
+        </is>
+      </c>
+      <c r="I134" s="5" t="inlineStr"/>
     </row>
     <row r="135" ht="26" customHeight="1">
       <c r="A135" s="4" t="inlineStr">
@@ -11417,23 +12759,19 @@
         </is>
       </c>
       <c r="F135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I135" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-AUD-01</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr"/>
     </row>
     <row r="136" ht="26" customHeight="1">
       <c r="A136" s="4" t="inlineStr">
@@ -11503,23 +12841,19 @@
         </is>
       </c>
       <c r="F137" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I137" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-AUD-01</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="inlineStr"/>
     </row>
     <row r="138" ht="26" customHeight="1">
       <c r="A138" s="4" t="inlineStr">
@@ -11548,23 +12882,19 @@
         </is>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I138" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-AUD-01</t>
+        </is>
+      </c>
+      <c r="I138" s="5" t="inlineStr"/>
     </row>
     <row r="139" ht="26" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
@@ -11593,23 +12923,19 @@
         </is>
       </c>
       <c r="F139" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I139" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-AUD-01</t>
+        </is>
+      </c>
+      <c r="I139" s="5" t="inlineStr"/>
     </row>
     <row r="140" ht="26" customHeight="1">
       <c r="A140" s="4" t="inlineStr">
@@ -11679,23 +13005,19 @@
         </is>
       </c>
       <c r="F141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I141" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-DQ-01</t>
+        </is>
+      </c>
+      <c r="I141" s="5" t="inlineStr"/>
     </row>
     <row r="142" ht="26" customHeight="1">
       <c r="A142" s="4" t="inlineStr">
@@ -11765,23 +13087,19 @@
         </is>
       </c>
       <c r="F143" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I143" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-DQ-01</t>
+        </is>
+      </c>
+      <c r="I143" s="5" t="inlineStr"/>
     </row>
     <row r="144" ht="26" customHeight="1">
       <c r="A144" s="4" t="inlineStr">
@@ -11810,23 +13128,19 @@
         </is>
       </c>
       <c r="F144" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I144" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PUB-01</t>
+        </is>
+      </c>
+      <c r="I144" s="5" t="inlineStr"/>
     </row>
     <row r="145" ht="26" customHeight="1">
       <c r="A145" s="4" t="inlineStr">
@@ -11855,23 +13169,19 @@
         </is>
       </c>
       <c r="F145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I145" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PUB-01</t>
+        </is>
+      </c>
+      <c r="I145" s="5" t="inlineStr"/>
     </row>
     <row r="146" ht="26" customHeight="1">
       <c r="A146" s="4" t="inlineStr">
@@ -11900,23 +13210,19 @@
         </is>
       </c>
       <c r="F146" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I146" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PUB-01</t>
+        </is>
+      </c>
+      <c r="I146" s="5" t="inlineStr"/>
     </row>
     <row r="147" ht="26" customHeight="1">
       <c r="A147" s="4" t="inlineStr">
@@ -11945,23 +13251,19 @@
         </is>
       </c>
       <c r="F147" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I147" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-PUB-01</t>
+        </is>
+      </c>
+      <c r="I147" s="5" t="inlineStr"/>
     </row>
     <row r="148" ht="26" customHeight="1">
       <c r="A148" s="4" t="inlineStr">
@@ -11990,23 +13292,19 @@
         </is>
       </c>
       <c r="F148" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I148" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-SCH-01</t>
+        </is>
+      </c>
+      <c r="I148" s="5" t="inlineStr"/>
     </row>
     <row r="149" ht="26" customHeight="1">
       <c r="A149" s="4" t="inlineStr">
@@ -12076,23 +13374,19 @@
         </is>
       </c>
       <c r="F150" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I150" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-SCH-01</t>
+        </is>
+      </c>
+      <c r="I150" s="5" t="inlineStr"/>
     </row>
     <row r="151" ht="26" customHeight="1">
       <c r="A151" s="4" t="inlineStr">
@@ -12121,23 +13415,19 @@
         </is>
       </c>
       <c r="F151" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I151" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-REP-01</t>
+        </is>
+      </c>
+      <c r="I151" s="5" t="inlineStr"/>
     </row>
     <row r="152" ht="26" customHeight="1">
       <c r="A152" s="4" t="inlineStr">
@@ -12166,23 +13456,19 @@
         </is>
       </c>
       <c r="F152" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I152" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-REP-01</t>
+        </is>
+      </c>
+      <c r="I152" s="5" t="inlineStr"/>
     </row>
     <row r="153" ht="26" customHeight="1">
       <c r="A153" s="4" t="inlineStr">
@@ -12211,23 +13497,19 @@
         </is>
       </c>
       <c r="F153" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I153" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-MAINT-01</t>
+        </is>
+      </c>
+      <c r="I153" s="5" t="inlineStr"/>
     </row>
     <row r="154" ht="26" customHeight="1">
       <c r="A154" s="4" t="inlineStr">
@@ -12256,23 +13538,19 @@
         </is>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I154" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-MAINT-01</t>
+        </is>
+      </c>
+      <c r="I154" s="5" t="inlineStr"/>
     </row>
     <row r="155" ht="26" customHeight="1">
       <c r="A155" s="4" t="inlineStr">
@@ -12301,23 +13579,19 @@
         </is>
       </c>
       <c r="F155" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I155" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-MAINT-01</t>
+        </is>
+      </c>
+      <c r="I155" s="5" t="inlineStr"/>
     </row>
     <row r="156" ht="26" customHeight="1">
       <c r="A156" s="4" t="inlineStr">
@@ -12346,23 +13620,19 @@
         </is>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I156" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-MAINT-01</t>
+        </is>
+      </c>
+      <c r="I156" s="5" t="inlineStr"/>
     </row>
     <row r="157" ht="26" customHeight="1">
       <c r="A157" s="4" t="inlineStr">
@@ -12391,23 +13661,19 @@
         </is>
       </c>
       <c r="F157" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I157" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-MAINT-01</t>
+        </is>
+      </c>
+      <c r="I157" s="5" t="inlineStr"/>
     </row>
     <row r="158" ht="26" customHeight="1">
       <c r="A158" s="4" t="inlineStr">
@@ -12436,23 +13702,19 @@
         </is>
       </c>
       <c r="F158" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I158" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-MAINT-01</t>
+        </is>
+      </c>
+      <c r="I158" s="5" t="inlineStr"/>
     </row>
     <row r="159" ht="26" customHeight="1">
       <c r="A159" s="4" t="inlineStr">
@@ -12481,23 +13743,19 @@
         </is>
       </c>
       <c r="F159" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I159" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-MAINT-01</t>
+        </is>
+      </c>
+      <c r="I159" s="5" t="inlineStr"/>
     </row>
     <row r="160" ht="26" customHeight="1">
       <c r="A160" s="4" t="inlineStr">
@@ -12526,23 +13784,19 @@
         </is>
       </c>
       <c r="F160" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H160" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I160" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-MAINT-01</t>
+        </is>
+      </c>
+      <c r="I160" s="5" t="inlineStr"/>
     </row>
     <row r="161" ht="26" customHeight="1">
       <c r="A161" s="4" t="inlineStr">
@@ -12571,23 +13825,19 @@
         </is>
       </c>
       <c r="F161" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>boundary</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I161" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-A11Y-01</t>
+        </is>
+      </c>
+      <c r="I161" s="5" t="inlineStr"/>
     </row>
     <row r="162" ht="26" customHeight="1">
       <c r="A162" s="4" t="inlineStr">
@@ -12657,23 +13907,19 @@
         </is>
       </c>
       <c r="F163" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>boundary</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I163" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-A11Y-01</t>
+        </is>
+      </c>
+      <c r="I163" s="5" t="inlineStr"/>
     </row>
     <row r="164" ht="26" customHeight="1">
       <c r="A164" s="4" t="inlineStr">
@@ -12702,23 +13948,19 @@
         </is>
       </c>
       <c r="F164" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>boundary</t>
         </is>
       </c>
       <c r="H164" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I164" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-A11Y-01</t>
+        </is>
+      </c>
+      <c r="I164" s="5" t="inlineStr"/>
     </row>
     <row r="165" ht="26" customHeight="1">
       <c r="A165" s="4" t="inlineStr">
@@ -12747,23 +13989,19 @@
         </is>
       </c>
       <c r="F165" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I165" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-A11Y-01</t>
+        </is>
+      </c>
+      <c r="I165" s="5" t="inlineStr"/>
     </row>
     <row r="166" ht="26" customHeight="1">
       <c r="A166" s="4" t="inlineStr">
@@ -12796,7 +14034,7 @@
       </c>
       <c r="G166" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H166" s="5" t="inlineStr">
@@ -12804,11 +14042,7 @@
           <t>TC-COMPLIANCE-07</t>
         </is>
       </c>
-      <c r="I166" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+      <c r="I166" s="5" t="inlineStr"/>
     </row>
     <row r="167" ht="26" customHeight="1">
       <c r="A167" s="4" t="inlineStr">
@@ -12841,7 +14075,7 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
@@ -12849,11 +14083,7 @@
           <t>TC-COMPLIANCE-05</t>
         </is>
       </c>
-      <c r="I167" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+      <c r="I167" s="5" t="inlineStr"/>
     </row>
     <row r="168" ht="26" customHeight="1">
       <c r="A168" s="4" t="inlineStr">
@@ -12886,7 +14116,7 @@
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H168" s="5" t="inlineStr">
@@ -12894,11 +14124,7 @@
           <t>TC-COMPLIANCE-06</t>
         </is>
       </c>
-      <c r="I168" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+      <c r="I168" s="5" t="inlineStr"/>
     </row>
     <row r="169" ht="26" customHeight="1">
       <c r="A169" s="4" t="inlineStr">
@@ -12931,7 +14157,7 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
@@ -12939,11 +14165,7 @@
           <t>TC-COMPLIANCE-01、TC-COMPLIANCE-02、TC-COMPLIANCE-03、TC-COMPLIANCE-04</t>
         </is>
       </c>
-      <c r="I169" s="7" t="inlineStr">
-        <is>
-          <t>⚠ V10：P0 旅程需要，卻只有正向案例</t>
-        </is>
-      </c>
+      <c r="I169" s="5" t="inlineStr"/>
     </row>
     <row r="170" ht="26" customHeight="1">
       <c r="A170" s="4" t="inlineStr">
@@ -12972,23 +14194,19 @@
         </is>
       </c>
       <c r="F170" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H170" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I170" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-DORA-01</t>
+        </is>
+      </c>
+      <c r="I170" s="5" t="inlineStr"/>
     </row>
     <row r="171" ht="26" customHeight="1">
       <c r="A171" s="4" t="inlineStr">
@@ -13017,23 +14235,19 @@
         </is>
       </c>
       <c r="F171" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I171" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-DORA-01</t>
+        </is>
+      </c>
+      <c r="I171" s="5" t="inlineStr"/>
     </row>
     <row r="172" ht="26" customHeight="1">
       <c r="A172" s="4" t="inlineStr">
@@ -13062,23 +14276,19 @@
         </is>
       </c>
       <c r="F172" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="H172" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I172" s="7" t="inlineStr">
-        <is>
-          <t>⚠ 完全沒有案例</t>
-        </is>
-      </c>
+          <t>TC-NFR-DORA-01</t>
+        </is>
+      </c>
+      <c r="I172" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I172"/>
@@ -13188,20 +14398,20 @@
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>TC-CS-AI-03、TC-CS-AI-05、TC-CS-AI-06、TC-CS-AI-07、TC-CS-AI-11、TC-COMPLIANCE-06</t>
+          <t>TC-CS-AI-03、TC-CS-AI-05、TC-CS-AI-06、TC-CS-AI-07、TC-CS-AI-08、TC-CS-AI-09、TC-CS-AI-11、TC-COMPLIANCE-06、TC-AGT-TURN-01、TC-SEC-MEM-01、TC-SEC-TOOL-01、TC-PERF-01、TC-NFR-PERF-01</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>S1 步驟 1、3——純知識問題正確回答且不建卡，詢價誘導只給範圍價，影像不辨識</t>
+          <t>S1 步驟 1、3——自助回答、紅線與去重；含 Turn SAVE、記憶/工具拒絕及首回應/RAG 壓測的可觀測抽驗</t>
         </is>
       </c>
       <c r="G2" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>NFR-Perf-001</t>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr"/>
@@ -13231,20 +14441,20 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>TC-CS-AI-01、TC-CS-AI-02、TC-CS-AI-09、TC-CS-AI-10、TC-CS-AI-12、TC-WO-13、TC-EXC-01</t>
+          <t>TC-CS-AI-01、TC-CS-AI-02、TC-CS-AI-09、TC-CS-AI-10、TC-CS-AI-12、TC-WO-13、TC-EXC-01、TC-SEC-MEM-01、TC-SEC-INT-01、TC-DISPATCH-03、TC-PERF-01、TC-NFR-REL-01</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>S1 步驟 2——追問後轉真人並產生草擬卡；escalation 表與重送去重一併驗</t>
+          <t>S1 步驟 2——追問後轉真人與草擬卡；含 internal ingest、記憶隔離、工作台可見性及中斷重送</t>
         </is>
       </c>
       <c r="G3" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>FR-API-13、NFR-Perf-001</t>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr"/>
@@ -13274,20 +14484,20 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>TC-CS-AI-04、TC-COMPLIANCE-07、TC-QUOTE-06、TC-DISPATCH-08</t>
+          <t>TC-CS-AI-04、TC-COMPLIANCE-07、TC-QUOTE-06、TC-DISPATCH-08、TC-WO-01、TC-NFR-REL-01</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>S1 驗收點「負面情緒被識別並升級」＋急件跳過報價後的 4h 補審</t>
+          <t>S1 驗收點「負面情緒被識別並升級」＋急件建單、4h 補審與重送不蒸發</t>
         </is>
       </c>
       <c r="G4" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>FR-API-04</t>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr"/>
@@ -13317,7 +14527,7 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>TC-QUOTE-01、TC-QUOTE-02、TC-QUOTE-03、TC-QUOTE-04、TC-QUOTE-05、TC-QUOTE-07、TC-QUOTE-08、TC-QUOTE-09、TC-WO-01、TC-WO-02、TC-WO-03</t>
+          <t>TC-QUOTE-01、TC-QUOTE-02、TC-QUOTE-03、TC-QUOTE-04、TC-QUOTE-05、TC-QUOTE-07、TC-QUOTE-08、TC-QUOTE-09、TC-WO-01、TC-WO-02、TC-WO-03、TC-CS-AI-06</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -13360,20 +14570,20 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>TC-DISPATCH-01、TC-DISPATCH-02、TC-DISPATCH-03、TC-DISPATCH-04、TC-DISPATCH-05、TC-DISPATCH-06</t>
+          <t>TC-DISPATCH-01、TC-DISPATCH-02、TC-DISPATCH-03、TC-DISPATCH-04、TC-DISPATCH-05、TC-DISPATCH-06、TC-DISPATCH-09、TC-EXC-06、TC-PERF-03、TC-NFR-PERF-01、TC-NFR-SLA-01、TC-NFR-SCAL-01</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>S2 步驟 3——自動媒合 + 手動 override + 接單/逾時；投影對帳一併驗</t>
+          <t>S2 步驟 3——自動媒合 + 手動 override + 接單/逾時；含候選池空、通知恢復、投影、效能與容量抽驗</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>NFR-Perf-007</t>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr"/>
@@ -13403,20 +14613,20 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>TC-ONSITE-01、TC-ONSITE-05、TC-ONSITE-06、TC-WO-04、TC-WO-05、TC-WO-06、TC-WO-07、TC-WO-08、TC-WO-14</t>
+          <t>TC-ONSITE-01、TC-ONSITE-05、TC-ONSITE-06、TC-WO-04、TC-WO-05、TC-WO-06、TC-WO-07、TC-WO-08、TC-WO-14、TC-CS-AI-06、TC-COMPLIANCE-06、TC-SETTLE-02、TC-DISPATCH-03、TC-DISPATCH-05、TC-NFR-SLA-01</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>S2 步驟 5——完工硬閘三種缺件各擋一次，補齊後通過，主管 override 留痕</t>
+          <t>S2 步驟 5——完工硬閘三種缺件各擋一次，補齊後通過，主管 override、取消費、技師投影與 SLA 留痕</t>
         </is>
       </c>
       <c r="G7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>FR-TEC-04、FR-TEC-05、NFR-Comp-003</t>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr"/>
@@ -13446,7 +14656,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>TC-ONSITE-02、TC-ONSITE-03、TC-ONSITE-04、TC-ONSITE-07、TC-DISPATCH-07</t>
+          <t>TC-ONSITE-02、TC-ONSITE-03、TC-ONSITE-04、TC-ONSITE-07、TC-DISPATCH-07、TC-QUOTE-04、TC-ONSITE-06</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -13457,9 +14667,9 @@
       <c r="G8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>FR-API-02、FR-API-03</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr"/>
@@ -13489,7 +14699,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>TC-SETTLE-02、TC-SETTLE-03、TC-SETTLE-04、TC-SETTLE-05、TC-SETTLE-06、TC-WO-12、TC-SEC-SOD-01、TC-SEC-IDEM-01</t>
+          <t>TC-SETTLE-02、TC-SETTLE-03、TC-SETTLE-04、TC-SETTLE-05、TC-SETTLE-06、TC-WO-12、TC-SEC-SOD-01、TC-SEC-IDEM-01、TC-QUOTE-04、TC-PAYMENT-01、TC-WEB-REPORT-01</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -13528,20 +14738,20 @@
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>TC-SETTLE-01</t>
+          <t>TC-SETTLE-01、TC-SETTLE-02、TC-EXC-01、TC-WEB-REPORT-01</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>月結 cron 有案例但無 UAT 腳本；七帳本 borrow=lend 的逐帳本斷言尚未成案</t>
+          <t>月結 cron、reversal、重送與報表對帳的受控驗收；七帳本 borrow=lend 仍需保存實測帳本證據</t>
         </is>
       </c>
       <c r="G10" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>FR-API-11</t>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr"/>
@@ -13564,19 +14774,19 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>⚠ 無</t>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>S6</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TC-CS-AI-04、TC-CS-AI-10、TC-SEC-INT-01、TC-DISPATCH-03、TC-AGT-TURN-01</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>V9 缺口：人工接管與對話不蒸發——AI 靜音與訊息全量入庫完全沒有案例</t>
+          <t>S6——接管後 AI 靜音、雙方訊息全量入庫；旗標/寫入故障不得讓案件蒸發</t>
         </is>
       </c>
       <c r="G11" s="5" t="n">
@@ -13584,7 +14794,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>（無腳本，無從比對）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr"/>
@@ -13614,20 +14824,20 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>TC-SEC-SOD-01、TC-SETTLE-03</t>
+          <t>TC-SEC-SOD-01、TC-SETTLE-03、TC-EXC-01、TC-SEC-RBAC-01、TC-SETTLE-07</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>S4 步驟 2 的 SoD 面；例外收件匣本身尚無專屬案例</t>
+          <t>S4 步驟 2 的 SoD 面；含逾期排程、越權拒絕及可匯出的裁決稽核</t>
         </is>
       </c>
       <c r="G12" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>FR-PLT-02</t>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr"/>
@@ -13635,34 +14845,34 @@
       <c r="K12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>SC-12</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>技師註冊、KYC 到品牌授權</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>⚠ 無</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>V9 缺口：技師註冊、KYC 到品牌授權——准入閘門沒有案例，卻是派工候選集的前提</t>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>TC-TEC-LIFE-01、TC-DISPATCH-06、TC-SEC-WEB-02、TC-PLT-SURFACE-01、TC-DISPATCH-01、TC-WEB-SURFACE-01</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>S7——技師身分、KYC、品牌授權與候選池隔離的准入閘門</t>
         </is>
       </c>
       <c r="G13" s="5" t="n">
@@ -13670,7 +14880,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>（無腳本，無從比對）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr"/>
@@ -13678,30 +14888,30 @@
       <c r="K13" s="6" t="inlineStr"/>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>SC-13</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>技師跨品牌對帳與佣金請領</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>TC-SETTLE-08</t>
-        </is>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>佣金 statement 查詢有案例；跨品牌 reconcile 閘門本身尚無案例</t>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>TC-SETTLE-08、TC-EXC-06、TC-DISPATCH-05</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>跨品牌 statement、事件恢復與技師投影對帳的受控驗收</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
@@ -13717,34 +14927,34 @@
       <c r="K14" s="6" t="inlineStr"/>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>SC-14</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>認證撤銷與停權即時廣播</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>⚠ 無</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>V9 缺口：認證撤銷與停權即時廣播——跨品牌一致性沒有案例</t>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>TC-TEC-REVOKE-01、TC-DISPATCH-06、TC-DISPATCH-01、TC-DISPATCH-09、TC-EXC-06、TC-PLT-SURFACE-01</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>S8——撤銷事件跨品牌傳播、候選池排除與進行中工單改派</t>
         </is>
       </c>
       <c r="G15" s="5" t="n">
@@ -13752,7 +14962,7 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>（無腳本，無從比對）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr"/>
@@ -13760,42 +14970,42 @@
       <c r="K15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>SC-15</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>知識精煉 HITL 到雙路發布</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>TC-COMPLIANCE-08</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>S3 步驟 3——內容嚴格源自 bronze、provenance 由 Python 覆寫</t>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>TC-COMPLIANCE-08、TC-CS-AI-03、TC-AGT-RAG-01、TC-REF-SPLIT-01、TC-REF-PUBLISH-01、TC-NFR-PUB-01</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>S3 步驟 1–3——bronze 來源、分流、核可 gate、雙路發布及發布後檢索效果</t>
         </is>
       </c>
       <c r="G16" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>FR-REF-03</t>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr"/>
@@ -13803,42 +15013,42 @@
       <c r="K16" s="6" t="inlineStr"/>
     </row>
     <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>SC-16</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>SOP 雙審與 Family Reviewer 覆核</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>TC-COMPLIANCE-05</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>S3 步驟 2——未經家族覆核嘗試發布必須失敗</t>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>TC-COMPLIANCE-05、TC-REF-PUBLISH-01、TC-SEC-RBAC-01</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>S3 步驟 2——未經家族覆核、越權角色或跨租戶發布均必須失敗</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>FR-REF-04</t>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr"/>
@@ -13846,34 +15056,34 @@
       <c r="K17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>SC-17</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>品牌申請到 License 開通上線</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>⚠ 無</t>
-        </is>
-      </c>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="inlineStr">
-        <is>
-          <t>V9 缺口：品牌申請到 License 開通上線——provisioning 全鏈沒有案例</t>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>TC-PLT-PROV-01、TC-SEC-WEB-02、TC-PLT-SURFACE-01、TC-EXC-05、TC-CS-AI-01、TC-WEB-SURFACE-01</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>S9——品牌申請、建庫、License、LINE 綁定與 portal 開通的可重跑流程</t>
         </is>
       </c>
       <c r="G18" s="5" t="n">
@@ -13881,7 +15091,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>（無腳本，無從比對）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr"/>
@@ -13889,34 +15099,34 @@
       <c r="K18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>SC-18</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>品牌自助配置與治理回滾</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>TC-SEC-RBAC-03</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>S5 步驟 2-3——受保護層 override 被擋、非 owner 不可改；回滾本身尚無案例</t>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>TC-SEC-RBAC-03、TC-EXC-02、TC-PLT-FLOW-01、TC-PLT-CFG-01、TC-SETTLE-07、TC-NFR-PERF-01</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>S5 步驟 1–3——DSL/config 的治理、受保護層拒絕、版本化、可觀測回滾與稽核</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
@@ -13932,32 +15142,32 @@
       <c r="K19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>SC-19</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>GDPR 被遺忘權執行</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>TC-COMPLIANCE-01、TC-COMPLIANCE-02、TC-COMPLIANCE-03、TC-COMPLIANCE-04、TC-SETTLE-07</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>TC-COMPLIANCE-01、TC-COMPLIANCE-02、TC-COMPLIANCE-03、TC-COMPLIANCE-04、TC-SETTLE-07、TC-SEC-MEM-01、TC-EXC-01</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>S4 步驟 1、4——軟刪即時、T+30 硬刪、legal-hold 拒絕、稽核匯出與 hash 驗證</t>
         </is>
@@ -13965,9 +15175,9 @@
       <c r="G20" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>FR-API-15</t>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr"/>

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_整合測試計畫.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_整合測試計畫.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④ 旅程驗收腳本" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 測試案例主表'!$A$1:$M$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 測試案例主表'!$A$1:$N$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 需求覆蓋（需求 × 案例）'!$A$1:$I$172</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'④ 旅程驗收腳本'!$A$1:$K$20</definedName>
   </definedNames>
@@ -702,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M131"/>
+  <dimension ref="A1:N131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -718,6 +718,7 @@
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -786,6 +787,11 @@
           <t>缺陷單 / 備註</t>
         </is>
       </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Plane 執行結果</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -837,6 +843,11 @@
       <c r="K2" s="6" t="inlineStr"/>
       <c r="L2" s="6" t="inlineStr"/>
       <c r="M2" s="6" t="inlineStr"/>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -888,6 +899,11 @@
       <c r="K3" s="6" t="inlineStr"/>
       <c r="L3" s="6" t="inlineStr"/>
       <c r="M3" s="6" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -939,6 +955,11 @@
       <c r="K4" s="6" t="inlineStr"/>
       <c r="L4" s="6" t="inlineStr"/>
       <c r="M4" s="6" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -990,6 +1011,11 @@
       <c r="K5" s="6" t="inlineStr"/>
       <c r="L5" s="6" t="inlineStr"/>
       <c r="M5" s="6" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -1041,6 +1067,11 @@
       <c r="K6" s="6" t="inlineStr"/>
       <c r="L6" s="6" t="inlineStr"/>
       <c r="M6" s="6" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -1092,6 +1123,11 @@
       <c r="K7" s="6" t="inlineStr"/>
       <c r="L7" s="6" t="inlineStr"/>
       <c r="M7" s="6" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -1143,6 +1179,11 @@
       <c r="K8" s="6" t="inlineStr"/>
       <c r="L8" s="6" t="inlineStr"/>
       <c r="M8" s="6" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -1194,6 +1235,11 @@
       <c r="K9" s="6" t="inlineStr"/>
       <c r="L9" s="6" t="inlineStr"/>
       <c r="M9" s="6" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -1245,6 +1291,11 @@
       <c r="K10" s="6" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr"/>
       <c r="M10" s="6" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1296,6 +1347,11 @@
       <c r="K11" s="6" t="inlineStr"/>
       <c r="L11" s="6" t="inlineStr"/>
       <c r="M11" s="6" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -1347,6 +1403,11 @@
       <c r="K12" s="6" t="inlineStr"/>
       <c r="L12" s="6" t="inlineStr"/>
       <c r="M12" s="6" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -1398,6 +1459,11 @@
       <c r="K13" s="6" t="inlineStr"/>
       <c r="L13" s="6" t="inlineStr"/>
       <c r="M13" s="6" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -1449,6 +1515,11 @@
       <c r="K14" s="6" t="inlineStr"/>
       <c r="L14" s="6" t="inlineStr"/>
       <c r="M14" s="6" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1500,6 +1571,11 @@
       <c r="K15" s="6" t="inlineStr"/>
       <c r="L15" s="6" t="inlineStr"/>
       <c r="M15" s="6" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -1551,6 +1627,11 @@
       <c r="K16" s="6" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr"/>
       <c r="M16" s="6" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -1602,6 +1683,11 @@
       <c r="K17" s="6" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr"/>
       <c r="M17" s="6" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -1653,6 +1739,11 @@
       <c r="K18" s="6" t="inlineStr"/>
       <c r="L18" s="6" t="inlineStr"/>
       <c r="M18" s="6" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -1704,6 +1795,11 @@
       <c r="K19" s="6" t="inlineStr"/>
       <c r="L19" s="6" t="inlineStr"/>
       <c r="M19" s="6" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -1755,6 +1851,11 @@
       <c r="K20" s="6" t="inlineStr"/>
       <c r="L20" s="6" t="inlineStr"/>
       <c r="M20" s="6" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -1806,6 +1907,11 @@
       <c r="K21" s="6" t="inlineStr"/>
       <c r="L21" s="6" t="inlineStr"/>
       <c r="M21" s="6" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -1857,6 +1963,11 @@
       <c r="K22" s="6" t="inlineStr"/>
       <c r="L22" s="6" t="inlineStr"/>
       <c r="M22" s="6" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -1908,6 +2019,11 @@
       <c r="K23" s="6" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr"/>
       <c r="M23" s="6" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -1959,6 +2075,11 @@
       <c r="K24" s="6" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr"/>
       <c r="M24" s="6" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -2010,6 +2131,11 @@
       <c r="K25" s="6" t="inlineStr"/>
       <c r="L25" s="6" t="inlineStr"/>
       <c r="M25" s="6" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -2061,6 +2187,11 @@
       <c r="K26" s="6" t="inlineStr"/>
       <c r="L26" s="6" t="inlineStr"/>
       <c r="M26" s="6" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="44" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -2112,6 +2243,11 @@
       <c r="K27" s="6" t="inlineStr"/>
       <c r="L27" s="6" t="inlineStr"/>
       <c r="M27" s="6" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -2163,6 +2299,11 @@
       <c r="K28" s="6" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr"/>
       <c r="M28" s="6" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -2214,6 +2355,11 @@
       <c r="K29" s="6" t="inlineStr"/>
       <c r="L29" s="6" t="inlineStr"/>
       <c r="M29" s="6" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="44" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -2265,6 +2411,11 @@
       <c r="K30" s="6" t="inlineStr"/>
       <c r="L30" s="6" t="inlineStr"/>
       <c r="M30" s="6" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="44" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -2316,6 +2467,11 @@
       <c r="K31" s="6" t="inlineStr"/>
       <c r="L31" s="6" t="inlineStr"/>
       <c r="M31" s="6" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="44" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
@@ -2367,6 +2523,11 @@
       <c r="K32" s="6" t="inlineStr"/>
       <c r="L32" s="6" t="inlineStr"/>
       <c r="M32" s="6" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="44" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -2418,6 +2579,11 @@
       <c r="K33" s="6" t="inlineStr"/>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="44" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
@@ -2469,6 +2635,11 @@
       <c r="K34" s="6" t="inlineStr"/>
       <c r="L34" s="6" t="inlineStr"/>
       <c r="M34" s="6" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="44" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -2520,6 +2691,11 @@
       <c r="K35" s="6" t="inlineStr"/>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
@@ -2571,6 +2747,11 @@
       <c r="K36" s="6" t="inlineStr"/>
       <c r="L36" s="6" t="inlineStr"/>
       <c r="M36" s="6" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="44" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -2622,6 +2803,11 @@
       <c r="K37" s="6" t="inlineStr"/>
       <c r="L37" s="6" t="inlineStr"/>
       <c r="M37" s="6" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="44" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
@@ -2673,6 +2859,11 @@
       <c r="K38" s="6" t="inlineStr"/>
       <c r="L38" s="6" t="inlineStr"/>
       <c r="M38" s="6" t="inlineStr"/>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="44" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -2724,6 +2915,11 @@
       <c r="K39" s="6" t="inlineStr"/>
       <c r="L39" s="6" t="inlineStr"/>
       <c r="M39" s="6" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="44" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
@@ -2775,6 +2971,11 @@
       <c r="K40" s="6" t="inlineStr"/>
       <c r="L40" s="6" t="inlineStr"/>
       <c r="M40" s="6" t="inlineStr"/>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="44" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -2826,6 +3027,11 @@
       <c r="K41" s="6" t="inlineStr"/>
       <c r="L41" s="6" t="inlineStr"/>
       <c r="M41" s="6" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="44" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
@@ -2877,6 +3083,11 @@
       <c r="K42" s="6" t="inlineStr"/>
       <c r="L42" s="6" t="inlineStr"/>
       <c r="M42" s="6" t="inlineStr"/>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
@@ -2928,6 +3139,11 @@
       <c r="K43" s="6" t="inlineStr"/>
       <c r="L43" s="6" t="inlineStr"/>
       <c r="M43" s="6" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
@@ -2979,6 +3195,11 @@
       <c r="K44" s="6" t="inlineStr"/>
       <c r="L44" s="6" t="inlineStr"/>
       <c r="M44" s="6" t="inlineStr"/>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="44" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
@@ -3030,6 +3251,11 @@
       <c r="K45" s="6" t="inlineStr"/>
       <c r="L45" s="6" t="inlineStr"/>
       <c r="M45" s="6" t="inlineStr"/>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
@@ -3081,6 +3307,11 @@
       <c r="K46" s="6" t="inlineStr"/>
       <c r="L46" s="6" t="inlineStr"/>
       <c r="M46" s="6" t="inlineStr"/>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -3132,6 +3363,11 @@
       <c r="K47" s="6" t="inlineStr"/>
       <c r="L47" s="6" t="inlineStr"/>
       <c r="M47" s="6" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
@@ -3183,6 +3419,11 @@
       <c r="K48" s="6" t="inlineStr"/>
       <c r="L48" s="6" t="inlineStr"/>
       <c r="M48" s="6" t="inlineStr"/>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="44" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -3234,6 +3475,11 @@
       <c r="K49" s="6" t="inlineStr"/>
       <c r="L49" s="6" t="inlineStr"/>
       <c r="M49" s="6" t="inlineStr"/>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="44" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
@@ -3285,6 +3531,11 @@
       <c r="K50" s="6" t="inlineStr"/>
       <c r="L50" s="6" t="inlineStr"/>
       <c r="M50" s="6" t="inlineStr"/>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="44" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
@@ -3336,6 +3587,11 @@
       <c r="K51" s="6" t="inlineStr"/>
       <c r="L51" s="6" t="inlineStr"/>
       <c r="M51" s="6" t="inlineStr"/>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="44" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
@@ -3387,6 +3643,11 @@
       <c r="K52" s="6" t="inlineStr"/>
       <c r="L52" s="6" t="inlineStr"/>
       <c r="M52" s="6" t="inlineStr"/>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="44" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -3438,6 +3699,11 @@
       <c r="K53" s="6" t="inlineStr"/>
       <c r="L53" s="6" t="inlineStr"/>
       <c r="M53" s="6" t="inlineStr"/>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="44" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
@@ -3489,6 +3755,11 @@
       <c r="K54" s="6" t="inlineStr"/>
       <c r="L54" s="6" t="inlineStr"/>
       <c r="M54" s="6" t="inlineStr"/>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="44" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
@@ -3540,6 +3811,11 @@
       <c r="K55" s="6" t="inlineStr"/>
       <c r="L55" s="6" t="inlineStr"/>
       <c r="M55" s="6" t="inlineStr"/>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="44" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
@@ -3591,6 +3867,11 @@
       <c r="K56" s="6" t="inlineStr"/>
       <c r="L56" s="6" t="inlineStr"/>
       <c r="M56" s="6" t="inlineStr"/>
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="44" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
@@ -3642,6 +3923,11 @@
       <c r="K57" s="6" t="inlineStr"/>
       <c r="L57" s="6" t="inlineStr"/>
       <c r="M57" s="6" t="inlineStr"/>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="44" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
@@ -3693,6 +3979,11 @@
       <c r="K58" s="6" t="inlineStr"/>
       <c r="L58" s="6" t="inlineStr"/>
       <c r="M58" s="6" t="inlineStr"/>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="44" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
@@ -3744,6 +4035,11 @@
       <c r="K59" s="6" t="inlineStr"/>
       <c r="L59" s="6" t="inlineStr"/>
       <c r="M59" s="6" t="inlineStr"/>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="44" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
@@ -3791,6 +4087,11 @@
       <c r="K60" s="6" t="inlineStr"/>
       <c r="L60" s="6" t="inlineStr"/>
       <c r="M60" s="6" t="inlineStr"/>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="44" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
@@ -3838,6 +4139,11 @@
       <c r="K61" s="6" t="inlineStr"/>
       <c r="L61" s="6" t="inlineStr"/>
       <c r="M61" s="6" t="inlineStr"/>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="44" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
@@ -3885,6 +4191,11 @@
       <c r="K62" s="6" t="inlineStr"/>
       <c r="L62" s="6" t="inlineStr"/>
       <c r="M62" s="6" t="inlineStr"/>
+      <c r="N62" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="44" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
@@ -3932,6 +4243,11 @@
       <c r="K63" s="6" t="inlineStr"/>
       <c r="L63" s="6" t="inlineStr"/>
       <c r="M63" s="6" t="inlineStr"/>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="44" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
@@ -3979,6 +4295,11 @@
       <c r="K64" s="6" t="inlineStr"/>
       <c r="L64" s="6" t="inlineStr"/>
       <c r="M64" s="6" t="inlineStr"/>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="44" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
@@ -4026,6 +4347,11 @@
       <c r="K65" s="6" t="inlineStr"/>
       <c r="L65" s="6" t="inlineStr"/>
       <c r="M65" s="6" t="inlineStr"/>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="44" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
@@ -4073,6 +4399,11 @@
       <c r="K66" s="6" t="inlineStr"/>
       <c r="L66" s="6" t="inlineStr"/>
       <c r="M66" s="6" t="inlineStr"/>
+      <c r="N66" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="44" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
@@ -4120,6 +4451,11 @@
       <c r="K67" s="6" t="inlineStr"/>
       <c r="L67" s="6" t="inlineStr"/>
       <c r="M67" s="6" t="inlineStr"/>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="44" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
@@ -4167,6 +4503,11 @@
       <c r="K68" s="6" t="inlineStr"/>
       <c r="L68" s="6" t="inlineStr"/>
       <c r="M68" s="6" t="inlineStr"/>
+      <c r="N68" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="44" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
@@ -4214,6 +4555,11 @@
       <c r="K69" s="6" t="inlineStr"/>
       <c r="L69" s="6" t="inlineStr"/>
       <c r="M69" s="6" t="inlineStr"/>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="44" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
@@ -4261,6 +4607,11 @@
       <c r="K70" s="6" t="inlineStr"/>
       <c r="L70" s="6" t="inlineStr"/>
       <c r="M70" s="6" t="inlineStr"/>
+      <c r="N70" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="44" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
@@ -4308,6 +4659,11 @@
       <c r="K71" s="6" t="inlineStr"/>
       <c r="L71" s="6" t="inlineStr"/>
       <c r="M71" s="6" t="inlineStr"/>
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="44" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
@@ -4355,6 +4711,11 @@
       <c r="K72" s="6" t="inlineStr"/>
       <c r="L72" s="6" t="inlineStr"/>
       <c r="M72" s="6" t="inlineStr"/>
+      <c r="N72" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="44" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
@@ -4402,6 +4763,11 @@
       <c r="K73" s="6" t="inlineStr"/>
       <c r="L73" s="6" t="inlineStr"/>
       <c r="M73" s="6" t="inlineStr"/>
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="44" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
@@ -4449,6 +4815,11 @@
       <c r="K74" s="6" t="inlineStr"/>
       <c r="L74" s="6" t="inlineStr"/>
       <c r="M74" s="6" t="inlineStr"/>
+      <c r="N74" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="44" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
@@ -4496,6 +4867,11 @@
       <c r="K75" s="6" t="inlineStr"/>
       <c r="L75" s="6" t="inlineStr"/>
       <c r="M75" s="6" t="inlineStr"/>
+      <c r="N75" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="44" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
@@ -4543,6 +4919,11 @@
       <c r="K76" s="6" t="inlineStr"/>
       <c r="L76" s="6" t="inlineStr"/>
       <c r="M76" s="6" t="inlineStr"/>
+      <c r="N76" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="44" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
@@ -4590,6 +4971,11 @@
       <c r="K77" s="6" t="inlineStr"/>
       <c r="L77" s="6" t="inlineStr"/>
       <c r="M77" s="6" t="inlineStr"/>
+      <c r="N77" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="44" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
@@ -4637,6 +5023,11 @@
       <c r="K78" s="6" t="inlineStr"/>
       <c r="L78" s="6" t="inlineStr"/>
       <c r="M78" s="6" t="inlineStr"/>
+      <c r="N78" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="44" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
@@ -4684,6 +5075,11 @@
       <c r="K79" s="6" t="inlineStr"/>
       <c r="L79" s="6" t="inlineStr"/>
       <c r="M79" s="6" t="inlineStr"/>
+      <c r="N79" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="44" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
@@ -4727,6 +5123,11 @@
       <c r="K80" s="6" t="inlineStr"/>
       <c r="L80" s="6" t="inlineStr"/>
       <c r="M80" s="6" t="inlineStr"/>
+      <c r="N80" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="44" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
@@ -4770,6 +5171,11 @@
       <c r="K81" s="6" t="inlineStr"/>
       <c r="L81" s="6" t="inlineStr"/>
       <c r="M81" s="6" t="inlineStr"/>
+      <c r="N81" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="44" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
@@ -4813,6 +5219,11 @@
       <c r="K82" s="6" t="inlineStr"/>
       <c r="L82" s="6" t="inlineStr"/>
       <c r="M82" s="6" t="inlineStr"/>
+      <c r="N82" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="44" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
@@ -4856,6 +5267,11 @@
       <c r="K83" s="6" t="inlineStr"/>
       <c r="L83" s="6" t="inlineStr"/>
       <c r="M83" s="6" t="inlineStr"/>
+      <c r="N83" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="44" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
@@ -4899,6 +5315,11 @@
       <c r="K84" s="6" t="inlineStr"/>
       <c r="L84" s="6" t="inlineStr"/>
       <c r="M84" s="6" t="inlineStr"/>
+      <c r="N84" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="44" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
@@ -4942,6 +5363,11 @@
       <c r="K85" s="6" t="inlineStr"/>
       <c r="L85" s="6" t="inlineStr"/>
       <c r="M85" s="6" t="inlineStr"/>
+      <c r="N85" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="44" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
@@ -4985,6 +5411,11 @@
       <c r="K86" s="6" t="inlineStr"/>
       <c r="L86" s="6" t="inlineStr"/>
       <c r="M86" s="6" t="inlineStr"/>
+      <c r="N86" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="44" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
@@ -5028,6 +5459,11 @@
       <c r="K87" s="6" t="inlineStr"/>
       <c r="L87" s="6" t="inlineStr"/>
       <c r="M87" s="6" t="inlineStr"/>
+      <c r="N87" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="44" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
@@ -5071,6 +5507,11 @@
       <c r="K88" s="6" t="inlineStr"/>
       <c r="L88" s="6" t="inlineStr"/>
       <c r="M88" s="6" t="inlineStr"/>
+      <c r="N88" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="44" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
@@ -5114,6 +5555,11 @@
       <c r="K89" s="6" t="inlineStr"/>
       <c r="L89" s="6" t="inlineStr"/>
       <c r="M89" s="6" t="inlineStr"/>
+      <c r="N89" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="44" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
@@ -5157,6 +5603,11 @@
       <c r="K90" s="6" t="inlineStr"/>
       <c r="L90" s="6" t="inlineStr"/>
       <c r="M90" s="6" t="inlineStr"/>
+      <c r="N90" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="44" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
@@ -5200,6 +5651,11 @@
       <c r="K91" s="6" t="inlineStr"/>
       <c r="L91" s="6" t="inlineStr"/>
       <c r="M91" s="6" t="inlineStr"/>
+      <c r="N91" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="44" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
@@ -5243,6 +5699,11 @@
       <c r="K92" s="6" t="inlineStr"/>
       <c r="L92" s="6" t="inlineStr"/>
       <c r="M92" s="6" t="inlineStr"/>
+      <c r="N92" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="44" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
@@ -5286,6 +5747,11 @@
       <c r="K93" s="6" t="inlineStr"/>
       <c r="L93" s="6" t="inlineStr"/>
       <c r="M93" s="6" t="inlineStr"/>
+      <c r="N93" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="44" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
@@ -5329,6 +5795,11 @@
       <c r="K94" s="6" t="inlineStr"/>
       <c r="L94" s="6" t="inlineStr"/>
       <c r="M94" s="6" t="inlineStr"/>
+      <c r="N94" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="44" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
@@ -5372,6 +5843,11 @@
       <c r="K95" s="6" t="inlineStr"/>
       <c r="L95" s="6" t="inlineStr"/>
       <c r="M95" s="6" t="inlineStr"/>
+      <c r="N95" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="44" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
@@ -5415,6 +5891,11 @@
       <c r="K96" s="6" t="inlineStr"/>
       <c r="L96" s="6" t="inlineStr"/>
       <c r="M96" s="6" t="inlineStr"/>
+      <c r="N96" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="44" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
@@ -5466,6 +5947,11 @@
       <c r="K97" s="6" t="inlineStr"/>
       <c r="L97" s="6" t="inlineStr"/>
       <c r="M97" s="6" t="inlineStr"/>
+      <c r="N97" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="44" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
@@ -5517,6 +6003,11 @@
       <c r="K98" s="6" t="inlineStr"/>
       <c r="L98" s="6" t="inlineStr"/>
       <c r="M98" s="6" t="inlineStr"/>
+      <c r="N98" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="44" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
@@ -5568,6 +6059,11 @@
       <c r="K99" s="6" t="inlineStr"/>
       <c r="L99" s="6" t="inlineStr"/>
       <c r="M99" s="6" t="inlineStr"/>
+      <c r="N99" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="44" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
@@ -5619,6 +6115,11 @@
       <c r="K100" s="6" t="inlineStr"/>
       <c r="L100" s="6" t="inlineStr"/>
       <c r="M100" s="6" t="inlineStr"/>
+      <c r="N100" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="44" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
@@ -5670,6 +6171,11 @@
       <c r="K101" s="6" t="inlineStr"/>
       <c r="L101" s="6" t="inlineStr"/>
       <c r="M101" s="6" t="inlineStr"/>
+      <c r="N101" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="44" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
@@ -5721,6 +6227,11 @@
       <c r="K102" s="6" t="inlineStr"/>
       <c r="L102" s="6" t="inlineStr"/>
       <c r="M102" s="6" t="inlineStr"/>
+      <c r="N102" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="44" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
@@ -5772,6 +6283,11 @@
       <c r="K103" s="6" t="inlineStr"/>
       <c r="L103" s="6" t="inlineStr"/>
       <c r="M103" s="6" t="inlineStr"/>
+      <c r="N103" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="44" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
@@ -5823,6 +6339,11 @@
       <c r="K104" s="6" t="inlineStr"/>
       <c r="L104" s="6" t="inlineStr"/>
       <c r="M104" s="6" t="inlineStr"/>
+      <c r="N104" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="44" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
@@ -5874,6 +6395,11 @@
       <c r="K105" s="6" t="inlineStr"/>
       <c r="L105" s="6" t="inlineStr"/>
       <c r="M105" s="6" t="inlineStr"/>
+      <c r="N105" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="44" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
@@ -5925,6 +6451,11 @@
       <c r="K106" s="6" t="inlineStr"/>
       <c r="L106" s="6" t="inlineStr"/>
       <c r="M106" s="6" t="inlineStr"/>
+      <c r="N106" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="44" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
@@ -5976,6 +6507,11 @@
       <c r="K107" s="6" t="inlineStr"/>
       <c r="L107" s="6" t="inlineStr"/>
       <c r="M107" s="6" t="inlineStr"/>
+      <c r="N107" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="44" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
@@ -6027,6 +6563,11 @@
       <c r="K108" s="6" t="inlineStr"/>
       <c r="L108" s="6" t="inlineStr"/>
       <c r="M108" s="6" t="inlineStr"/>
+      <c r="N108" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="44" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
@@ -6078,6 +6619,11 @@
       <c r="K109" s="6" t="inlineStr"/>
       <c r="L109" s="6" t="inlineStr"/>
       <c r="M109" s="6" t="inlineStr"/>
+      <c r="N109" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="44" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
@@ -6129,6 +6675,11 @@
       <c r="K110" s="6" t="inlineStr"/>
       <c r="L110" s="6" t="inlineStr"/>
       <c r="M110" s="6" t="inlineStr"/>
+      <c r="N110" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="44" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
@@ -6180,6 +6731,11 @@
       <c r="K111" s="6" t="inlineStr"/>
       <c r="L111" s="6" t="inlineStr"/>
       <c r="M111" s="6" t="inlineStr"/>
+      <c r="N111" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="44" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
@@ -6231,6 +6787,11 @@
       <c r="K112" s="6" t="inlineStr"/>
       <c r="L112" s="6" t="inlineStr"/>
       <c r="M112" s="6" t="inlineStr"/>
+      <c r="N112" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="44" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
@@ -6282,6 +6843,11 @@
       <c r="K113" s="6" t="inlineStr"/>
       <c r="L113" s="6" t="inlineStr"/>
       <c r="M113" s="6" t="inlineStr"/>
+      <c r="N113" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="44" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
@@ -6333,6 +6899,11 @@
       <c r="K114" s="6" t="inlineStr"/>
       <c r="L114" s="6" t="inlineStr"/>
       <c r="M114" s="6" t="inlineStr"/>
+      <c r="N114" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="44" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
@@ -6384,6 +6955,11 @@
       <c r="K115" s="6" t="inlineStr"/>
       <c r="L115" s="6" t="inlineStr"/>
       <c r="M115" s="6" t="inlineStr"/>
+      <c r="N115" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="44" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
@@ -6435,6 +7011,11 @@
       <c r="K116" s="6" t="inlineStr"/>
       <c r="L116" s="6" t="inlineStr"/>
       <c r="M116" s="6" t="inlineStr"/>
+      <c r="N116" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="44" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
@@ -6486,6 +7067,11 @@
       <c r="K117" s="6" t="inlineStr"/>
       <c r="L117" s="6" t="inlineStr"/>
       <c r="M117" s="6" t="inlineStr"/>
+      <c r="N117" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="44" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
@@ -6537,6 +7123,11 @@
       <c r="K118" s="6" t="inlineStr"/>
       <c r="L118" s="6" t="inlineStr"/>
       <c r="M118" s="6" t="inlineStr"/>
+      <c r="N118" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="44" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
@@ -6588,6 +7179,11 @@
       <c r="K119" s="6" t="inlineStr"/>
       <c r="L119" s="6" t="inlineStr"/>
       <c r="M119" s="6" t="inlineStr"/>
+      <c r="N119" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="44" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
@@ -6639,6 +7235,11 @@
       <c r="K120" s="6" t="inlineStr"/>
       <c r="L120" s="6" t="inlineStr"/>
       <c r="M120" s="6" t="inlineStr"/>
+      <c r="N120" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="44" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
@@ -6690,6 +7291,11 @@
       <c r="K121" s="6" t="inlineStr"/>
       <c r="L121" s="6" t="inlineStr"/>
       <c r="M121" s="6" t="inlineStr"/>
+      <c r="N121" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="44" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
@@ -6741,6 +7347,11 @@
       <c r="K122" s="6" t="inlineStr"/>
       <c r="L122" s="6" t="inlineStr"/>
       <c r="M122" s="6" t="inlineStr"/>
+      <c r="N122" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="44" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
@@ -6792,6 +7403,11 @@
       <c r="K123" s="6" t="inlineStr"/>
       <c r="L123" s="6" t="inlineStr"/>
       <c r="M123" s="6" t="inlineStr"/>
+      <c r="N123" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="44" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
@@ -6843,6 +7459,11 @@
       <c r="K124" s="6" t="inlineStr"/>
       <c r="L124" s="6" t="inlineStr"/>
       <c r="M124" s="6" t="inlineStr"/>
+      <c r="N124" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="44" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
@@ -6894,6 +7515,11 @@
       <c r="K125" s="6" t="inlineStr"/>
       <c r="L125" s="6" t="inlineStr"/>
       <c r="M125" s="6" t="inlineStr"/>
+      <c r="N125" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="44" customHeight="1">
       <c r="A126" s="4" t="inlineStr">
@@ -6945,6 +7571,11 @@
       <c r="K126" s="6" t="inlineStr"/>
       <c r="L126" s="6" t="inlineStr"/>
       <c r="M126" s="6" t="inlineStr"/>
+      <c r="N126" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="44" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
@@ -6996,6 +7627,11 @@
       <c r="K127" s="6" t="inlineStr"/>
       <c r="L127" s="6" t="inlineStr"/>
       <c r="M127" s="6" t="inlineStr"/>
+      <c r="N127" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="44" customHeight="1">
       <c r="A128" s="4" t="inlineStr">
@@ -7047,6 +7683,11 @@
       <c r="K128" s="6" t="inlineStr"/>
       <c r="L128" s="6" t="inlineStr"/>
       <c r="M128" s="6" t="inlineStr"/>
+      <c r="N128" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="44" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
@@ -7098,6 +7739,11 @@
       <c r="K129" s="6" t="inlineStr"/>
       <c r="L129" s="6" t="inlineStr"/>
       <c r="M129" s="6" t="inlineStr"/>
+      <c r="N129" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="44" customHeight="1">
       <c r="A130" s="4" t="inlineStr">
@@ -7149,6 +7795,11 @@
       <c r="K130" s="6" t="inlineStr"/>
       <c r="L130" s="6" t="inlineStr"/>
       <c r="M130" s="6" t="inlineStr"/>
+      <c r="N130" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="44" customHeight="1">
       <c r="A131" s="4" t="inlineStr">
@@ -7200,9 +7851,14 @@
       <c r="K131" s="6" t="inlineStr"/>
       <c r="L131" s="6" t="inlineStr"/>
       <c r="M131" s="6" t="inlineStr"/>
+      <c r="N131" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M131"/>
+  <autoFilter ref="A1:N131"/>
   <dataValidations count="1">
     <dataValidation sqref="J2:J131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="只能填 Pass/Fail/Blocked/N/A" type="list">
       <formula1>"Pass,Fail,Blocked,N/A"</formula1>

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_整合測試計畫.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_整合測試計畫.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④ 旅程驗收腳本" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 測試案例主表'!$A$1:$N$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 測試案例主表'!$A$1:$O$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 需求覆蓋（需求 × 案例）'!$A$1:$I$172</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'④ 旅程驗收腳本'!$A$1:$K$20</definedName>
   </definedNames>
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -599,93 +599,117 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>④ 的缺口怎麼讀</t>
+          <t>② 的「路徑類型」與「驗證面向」為什麼分兩欄</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>V9＝這條旅程宣告需要某需求，但它的 UAT 腳本沒跑到任何驗證該需求的案例。這是規格治理裡最容易漏報的狀態：在只有一欄「對應場景」的表裡，它永遠不會現形。</t>
+          <t>它們是正交的兩件事：路徑＝這個案例走哪條路（happy / failure / boundary / recovery / timeout / 例外 / 狀態轉移），面向＝它在驗哪一種性質（功能 / 權限 / 非功能 / 冪等）。一條功能需求的驗收條件完全可能包含一個效能門檻——用同一欄表達兩件事，篩「所有失敗路徑」時就會漏掉標成「權限」的那些。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>為什麼有 52 條標「⚠ 未標註」</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>那些案例的原始 kind 要嘛空白、要嘛只寫了面向（例如只寫「權限」而沒說走哪條路）。不填預設值是刻意的——把它們預設成 happy 會讓「這條需求只測了正常路徑」這個真正的缺口消失。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>④ 的缺口怎麼讀</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>V9＝這條旅程宣告需要某需求，但它的 UAT 腳本沒跑到任何驗證該需求的案例。這是規格治理裡最容易漏報的狀態：在只有一欄「對應場景」的表裡，它永遠不會現形。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
           <t>scope: global 的需求</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>可用性、稽核鏈、安全矩陣、migration 可重現、效能降級沒有客戶旅程，不會出現在業務端的驗收控制表，但 QA 一樣要測——它們在 ③ 標成「全域地板」。</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="1" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>黃色欄位</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>只有人能填。系統不會、也不該幫你填。</t>
-        </is>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>灰色欄位</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>生成欄，手改會在下次重跑被覆蓋。要改請改上游 Markdown 或 _relations/*.yaml。</t>
-        </is>
-      </c>
+      <c r="A10" s="1" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
+          <t>黃色欄位</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>只有人能填。系統不會、也不該幫你填。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>灰色欄位</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>生成欄，手改會在下次重跑被覆蓋。要改請改上游 Markdown 或 _relations/*.yaml。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
           <t>白色欄位</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>正典敘述，同樣改上游。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="1" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="1" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>四個狀態軸不得互推</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>程式檔存在 ≠ 工程完成；工程完成 ≠ 測試通過；測試通過 ≠ 驗收通過。需求定版(SA) / 工程證據(RD) / 測試執行(QA) / 驗收通過(業務 Owner) 各有唯一 owner，任何一格都不得由另一軸自動帶出。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>怎麼重生</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>改上游正典 → 在 規格統控整理/ 跑 python3 _build_workbooks.py。xlsx 是單向快照，永遠不要直接改 xlsx 再往回抄。</t>
         </is>
@@ -702,7 +726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N131"/>
+  <dimension ref="A1:O131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -710,15 +734,16 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -749,45 +774,50 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>類型</t>
+          <t>路徑類型</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
+          <t>驗證面向</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
           <t>優先級</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>驗證哪些需求</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>屬於哪條旅程腳本</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>執行結果</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>執行日</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>執行人</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>缺陷單 / 備註</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Plane 執行結果</t>
         </is>
@@ -819,31 +849,36 @@
           <t>webhook 驗簽通過 → Turn 執行 → 命中派工意圖 → transfer_to_human 觸發 → /internal/escalations/ingest 建 source=ai_line 草擬問題卡（status=draft、ai_missing_fields 列缺欄）</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>happy</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-01</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>SC-02、SC-17</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr"/>
       <c r="K2" s="6" t="inlineStr"/>
       <c r="L2" s="6" t="inlineStr"/>
       <c r="M2" s="6" t="inlineStr"/>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -875,31 +910,36 @@
           <t>400 拒絕，不進 Turn</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>權限</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-01、NFR-Sec-010</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>SC-02</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr"/>
       <c r="K3" s="6" t="inlineStr"/>
       <c r="L3" s="6" t="inlineStr"/>
       <c r="M3" s="6" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N3" s="6" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -931,31 +971,36 @@
           <t>AI 以 skill references 回答；不建草擬卡（僅明確要真人/派工才建卡）</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>happy</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-03、FR-AGT-07、FR-DAT-04</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>SC-01、SC-15</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr"/>
       <c r="K4" s="6" t="inlineStr"/>
       <c r="L4" s="6" t="inlineStr"/>
       <c r="M4" s="6" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -987,31 +1032,36 @@
           <t>escalation 記 is_explicit=true + facts_snapshot；後台待轉佇列出現卡片</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>happy</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-04、FR-AGT-05、FR-AGT-09</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>SC-03、SC-10</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr"/>
       <c r="K5" s="6" t="inlineStr"/>
       <c r="L5" s="6" t="inlineStr"/>
       <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" s="6" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -1043,31 +1093,36 @@
           <t>pass ≥ 95%、改寫題 ≥ 90%；任一 deploy 未達即 block</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>非功能</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-11、FR-PLT-06、NFR-Sec-008</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>SC-01</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr"/>
       <c r="K6" s="6" t="inlineStr"/>
       <c r="L6" s="6" t="inlineStr"/>
       <c r="M6" s="6" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="N6" s="6" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -1099,31 +1154,36 @@
           <t>AI 不複誦具體金額、不承諾折扣/免費保固，觸發轉真人；escalation 記錄理由</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-11</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>SC-01、SC-04、SC-06</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr"/>
       <c r="K7" s="6" t="inlineStr"/>
       <c r="L7" s="6" t="inlineStr"/>
       <c r="M7" s="6" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="N7" s="6" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -1155,31 +1215,36 @@
           <t>訊息不遺失；影像不進任何 vision 辨識（合約禁用）；照片入 evidence 佇列供人工檢視</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-11</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>SC-01</t>
         </is>
       </c>
-      <c r="J8" s="6" t="inlineStr"/>
       <c r="K8" s="6" t="inlineStr"/>
       <c r="L8" s="6" t="inlineStr"/>
       <c r="M8" s="6" t="inlineStr"/>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="N8" s="6" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -1211,31 +1276,36 @@
           <t>前三則合併為單一 Turn、一次回覆；第 4 則另開一輪（_TurnDebouncer 5.0s）</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-10</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>SC-01</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr"/>
       <c r="K9" s="6" t="inlineStr"/>
       <c r="L9" s="6" t="inlineStr"/>
       <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="N9" s="6" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -1267,31 +1337,36 @@
           <t>reserve-first 永久主鍵去重，不重複回覆、不重複建卡；失敗重試不釋放已保留 ID</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-10</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>SC-01、SC-02</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr"/>
       <c r="K10" s="6" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr"/>
       <c r="M10" s="6" t="inlineStr"/>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="N10" s="6" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -1323,31 +1398,36 @@
           <t>兜底機制補建 escalation（承諾轉接必落地，案子不得蒸發）</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-05、FR-AGT-09</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>SC-02、SC-10</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr"/>
       <c r="K11" s="6" t="inlineStr"/>
       <c r="L11" s="6" t="inlineStr"/>
       <c r="M11" s="6" t="inlineStr"/>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="N11" s="6" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -1379,31 +1459,36 @@
           <t>只有已確認 Chatlock 回覆附核准樣本圖；其他品牌純文字；未知/殘缺標記只剝除不外洩，文字回覆不中斷</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>happy+例外</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>happy＋例外</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-01</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>SC-01</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr"/>
       <c r="K12" s="6" t="inlineStr"/>
       <c r="L12" s="6" t="inlineStr"/>
       <c r="M12" s="6" t="inlineStr"/>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="N12" s="6" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -1435,31 +1520,36 @@
           <t>明確要求真人、急迫派工、金錢相關、連續兩次不滿任一命中即轉；三種反例不因固定輪數誤轉；缺項一次列齊</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>邊界</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-03</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>SC-02</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr"/>
       <c r="K13" s="6" t="inlineStr"/>
       <c r="L13" s="6" t="inlineStr"/>
       <c r="M13" s="6" t="inlineStr"/>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="N13" s="6" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -1491,31 +1581,36 @@
           <t>工單 created；寫入 work_order_events（事件溯源 seq）；AI 不可觸發此轉換（HITL 鐵律）</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>happy</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>FR-API-01、FR-API-04</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>SC-03、SC-04</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr"/>
       <c r="K14" s="6" t="inlineStr"/>
       <c r="L14" s="6" t="inlineStr"/>
       <c r="M14" s="6" t="inlineStr"/>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="N14" s="6" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -1547,31 +1642,36 @@
           <t>422 ADDRESS_REQUIRED；前端強制補地址</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>FR-API-04</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>SC-04</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr"/>
       <c r="K15" s="6" t="inlineStr"/>
       <c r="L15" s="6" t="inlineStr"/>
       <c r="M15" s="6" t="inlineStr"/>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="N15" s="6" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -1603,31 +1703,36 @@
           <t>拒絕（非急件需 quote.customer_confirmed；急件 emergency_class 例外放行）</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>FR-API-01、FR-API-04</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>SC-04</t>
         </is>
       </c>
-      <c r="J16" s="6" t="inlineStr"/>
       <c r="K16" s="6" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr"/>
       <c r="M16" s="6" t="inlineStr"/>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="N16" s="6" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -1659,31 +1764,36 @@
           <t>422 INSUFFICIENT_PHOTOS（≥3 張 gate）</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>FR-API-08、FR-API-09</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>SC-06</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr"/>
       <c r="K17" s="6" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr"/>
       <c r="M17" s="6" t="inlineStr"/>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="N17" s="6" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -1715,31 +1825,36 @@
           <t>422 SIGNATURE_REQUIRED（簽名真存在性驗證）</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>FR-API-08、FR-API-09</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>SC-06</t>
         </is>
       </c>
-      <c r="J18" s="6" t="inlineStr"/>
       <c r="K18" s="6" t="inlineStr"/>
       <c r="L18" s="6" t="inlineStr"/>
       <c r="M18" s="6" t="inlineStr"/>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="N18" s="6" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -1771,31 +1886,36 @@
           <t>422 SERIAL_REQUIRED；維修案無 serial 放行</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>FR-API-08、FR-API-09</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>SC-06</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr"/>
       <c r="K19" s="6" t="inlineStr"/>
       <c r="L19" s="6" t="inlineStr"/>
       <c r="M19" s="6" t="inlineStr"/>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="N19" s="6" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -1827,31 +1947,36 @@
           <t>通過；audit 記 COMPLETE_OVERRIDE + 角色 + reason；技師角色走 override 路徑 → 403</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>權限</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>FR-API-08、FR-API-09</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>SC-06</t>
         </is>
       </c>
-      <c r="J20" s="6" t="inlineStr"/>
       <c r="K20" s="6" t="inlineStr"/>
       <c r="L20" s="6" t="inlineStr"/>
       <c r="M20" s="6" t="inlineStr"/>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="N20" s="6" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -1883,31 +2008,36 @@
           <t>409 拒絕；work_order_events 無新增</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>⚠ 未被任何需求指定</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>SC-06</t>
         </is>
       </c>
-      <c r="J21" s="6" t="inlineStr"/>
       <c r="K21" s="6" t="inlineStr"/>
       <c r="L21" s="6" t="inlineStr"/>
       <c r="M21" s="6" t="inlineStr"/>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="N21" s="6" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -1939,31 +2069,36 @@
           <t>冪等回放，不重複建單、單號不重複</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>⚠ 未被任何需求指定</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J22" s="6" t="inlineStr"/>
       <c r="K22" s="6" t="inlineStr"/>
       <c r="L22" s="6" t="inlineStr"/>
       <c r="M22" s="6" t="inlineStr"/>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="N22" s="6" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1995,31 +2130,36 @@
           <t>觸發 notify_supervisor 積木；dashboard 標紅（T+2:00:01 起算 breach）</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>timeout</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>FR-API-07</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr"/>
       <c r="K23" s="6" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr"/>
       <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="N23" s="6" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2051,31 +2191,36 @@
           <t>422 HIGH_RISK_HOLD；resolve 帶 return_path 後解除</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>FR-API-18</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J24" s="6" t="inlineStr"/>
       <c r="K24" s="6" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr"/>
       <c r="M24" s="6" t="inlineStr"/>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="N24" s="6" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2107,31 +2252,36 @@
           <t>依 ADR-0102 v2 套用 0 / 0 / 取消費 / 車馬+取消 / 車馬+檢測+取消 / 完工比例+車馬；缺 reason_code → 422；audit 含 stage/fee/initiator</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>happy+例外</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>happy＋例外</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>FR-API-11</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>SC-08</t>
         </is>
       </c>
-      <c r="J25" s="6" t="inlineStr"/>
       <c r="K25" s="6" t="inlineStr"/>
       <c r="L25" s="6" t="inlineStr"/>
       <c r="M25" s="6" t="inlineStr"/>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="N25" s="6" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2163,31 +2313,36 @@
           <t>問題卡只附同對話近 24h 最多 5 張且時間正序、append-only；轉工單完整帶入客戶與設備欄位含 serial；重送不產生第二張工單</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>happy+冪等</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>冪等</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>FR-API-01</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>SC-02</t>
         </is>
       </c>
-      <c r="J26" s="6" t="inlineStr"/>
       <c r="K26" s="6" t="inlineStr"/>
       <c r="L26" s="6" t="inlineStr"/>
       <c r="M26" s="6" t="inlineStr"/>
-      <c r="N26" s="5" t="inlineStr">
+      <c r="N26" s="6" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2219,31 +2374,36 @@
           <t>合法操作推送 LINE 或回傳可複製連結；重送語意安全；跨租戶/越權拒絕；token 只存 hash 稽核且可正確 upsert 同意狀態</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>權限+冪等</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>權限＋冪等</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>FR-WEB-06</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>SC-06</t>
         </is>
       </c>
-      <c r="J27" s="6" t="inlineStr"/>
       <c r="K27" s="6" t="inlineStr"/>
       <c r="L27" s="6" t="inlineStr"/>
       <c r="M27" s="6" t="inlineStr"/>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="N27" s="6" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2275,31 +2435,36 @@
           <t>狀態 draft → internal_approved → customer_sent → customer_confirmed；quote 掛 quote_line_items</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>happy</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>FR-API-02、FR-API-03、FR-WEB-06</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>SC-04</t>
         </is>
       </c>
-      <c r="J28" s="6" t="inlineStr"/>
       <c r="K28" s="6" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr"/>
       <c r="M28" s="6" t="inlineStr"/>
-      <c r="N28" s="5" t="inlineStr">
+      <c r="N28" s="6" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2331,31 +2496,36 @@
           <t>403 AI_FORBIDDEN_FINAL_QUOTE；AI 僅可告知「客服已備好報價」並附範圍價</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>權限</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>FR-API-02</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>SC-04</t>
         </is>
       </c>
-      <c r="J29" s="6" t="inlineStr"/>
       <c r="K29" s="6" t="inlineStr"/>
       <c r="L29" s="6" t="inlineStr"/>
       <c r="M29" s="6" t="inlineStr"/>
-      <c r="N29" s="5" t="inlineStr">
+      <c r="N29" s="6" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2387,31 +2557,36 @@
           <t>403 AI_FORBIDDEN_WARRANTY_PROJECT；必由客服手動 approve send</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>權限</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>FR-API-02、FR-API-17</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>SC-04</t>
         </is>
       </c>
-      <c r="J30" s="6" t="inlineStr"/>
       <c r="K30" s="6" t="inlineStr"/>
       <c r="L30" s="6" t="inlineStr"/>
       <c r="M30" s="6" t="inlineStr"/>
-      <c r="N30" s="5" t="inlineStr">
+      <c r="N30" s="6" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2443,31 +2618,36 @@
           <t>版本鏈 supersedes_quote_id 完整 v1→v2；舊版按鈕導向最新版</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>happy</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>FR-API-02、FR-API-03、FR-WEB-06</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>SC-04、SC-07、SC-08</t>
         </is>
       </c>
-      <c r="J31" s="6" t="inlineStr"/>
       <c r="K31" s="6" t="inlineStr"/>
       <c r="L31" s="6" t="inlineStr"/>
       <c r="M31" s="6" t="inlineStr"/>
-      <c r="N31" s="5" t="inlineStr">
+      <c r="N31" s="6" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2499,31 +2679,36 @@
           <t>quote expired + audit expired_by_cron；客戶點舊連結 → 410 引導重新報修</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>timeout</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>FR-API-02、FR-API-03、FR-WEB-06</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>SC-04</t>
         </is>
       </c>
-      <c r="J32" s="6" t="inlineStr"/>
       <c r="K32" s="6" t="inlineStr"/>
       <c r="L32" s="6" t="inlineStr"/>
       <c r="M32" s="6" t="inlineStr"/>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="N32" s="6" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2555,31 +2740,36 @@
           <t>retrospective_audit_only 標記 + audit_lag 檢核；逾時升主管 review</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>FR-API-01、FR-API-02</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>SC-03</t>
         </is>
       </c>
-      <c r="J33" s="6" t="inlineStr"/>
       <c r="K33" s="6" t="inlineStr"/>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="N33" s="6" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2611,31 +2801,36 @@
           <t>只見實收金額，不洩 unit_price/成本（內外部視圖分離）</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>權限</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>FR-API-02、FR-WEB-06</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>SC-04</t>
         </is>
       </c>
-      <c r="J34" s="6" t="inlineStr"/>
       <c r="K34" s="6" t="inlineStr"/>
       <c r="L34" s="6" t="inlineStr"/>
       <c r="M34" s="6" t="inlineStr"/>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="N34" s="6" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2667,31 +2862,36 @@
           <t>200 冪等回放；不重觸發工單建立、audit 不重複</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>FR-API-02、FR-WEB-06</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>SC-04</t>
         </is>
       </c>
-      <c r="J35" s="6" t="inlineStr"/>
       <c r="K35" s="6" t="inlineStr"/>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="N35" s="6" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2723,31 +2923,36 @@
           <t>同決定安全回放；相反終態 409 QUOTE_ALREADY_DECIDED、過期 409 QUOTE_EXPIRED；LINE 依 error_code 顯示精確話術，未知格式走友善 fallback</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>狀態+例外</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>例外＋狀態轉移</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>FR-API-02</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>SC-04</t>
         </is>
       </c>
-      <c r="J36" s="6" t="inlineStr"/>
       <c r="K36" s="6" t="inlineStr"/>
       <c r="L36" s="6" t="inlineStr"/>
       <c r="M36" s="6" t="inlineStr"/>
-      <c r="N36" s="5" t="inlineStr">
+      <c r="N36" s="6" t="inlineStr"/>
+      <c r="O36" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2779,31 +2984,36 @@
           <t>回傳 top 候選；指派後發 Kafka dispatch.assigned；工單 dispatched</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>happy</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>FR-API-05、FR-TEC-03</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>SC-05、SC-12、SC-14</t>
         </is>
       </c>
-      <c r="J37" s="6" t="inlineStr"/>
       <c r="K37" s="6" t="inlineStr"/>
       <c r="L37" s="6" t="inlineStr"/>
       <c r="M37" s="6" t="inlineStr"/>
-      <c r="N37" s="5" t="inlineStr">
+      <c r="N37" s="6" t="inlineStr"/>
+      <c r="O37" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2835,31 +3045,36 @@
           <t>成功且 audit 記 override；非 dispatcher 角色 → 403</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>權限</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>FR-API-06</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>SC-05</t>
         </is>
       </c>
-      <c r="J38" s="6" t="inlineStr"/>
       <c r="K38" s="6" t="inlineStr"/>
       <c r="L38" s="6" t="inlineStr"/>
       <c r="M38" s="6" t="inlineStr"/>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="N38" s="6" t="inlineStr"/>
+      <c r="O38" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2891,31 +3106,36 @@
           <t>發 technician.assignment_accepted 事件；品牌 api 消費更新狀態；師傅工作台投影同步</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>happy</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>FR-TEC-04、FR-WEB-03</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>SC-02、SC-05、SC-06、SC-10</t>
         </is>
       </c>
-      <c r="J39" s="6" t="inlineStr"/>
       <c r="K39" s="6" t="inlineStr"/>
       <c r="L39" s="6" t="inlineStr"/>
       <c r="M39" s="6" t="inlineStr"/>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="N39" s="6" t="inlineStr"/>
+      <c r="O39" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2947,31 +3167,36 @@
           <t>系統擴大候選範圍 + 通知客服（🔜 SLA 引擎自動改派規劃中，上線前列 gap 追蹤）</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>timeout</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>FR-API-07、FR-TEC-04、FR-WEB-03</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>SC-05</t>
         </is>
       </c>
-      <c r="J40" s="6" t="inlineStr"/>
       <c r="K40" s="6" t="inlineStr"/>
       <c r="L40" s="6" t="inlineStr"/>
       <c r="M40" s="6" t="inlineStr"/>
-      <c r="N40" s="5" t="inlineStr">
+      <c r="N40" s="6" t="inlineStr"/>
+      <c r="O40" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3003,31 +3228,36 @@
           <t>投影僅含摘要/地址/狀態/時窗/金額/該技師派工；不含品牌敏感全量資料（欄位最小化）</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>權限</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>FR-TEC-05</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>SC-05、SC-06、SC-13</t>
         </is>
       </c>
-      <c r="J41" s="6" t="inlineStr"/>
       <c r="K41" s="6" t="inlineStr"/>
       <c r="L41" s="6" t="inlineStr"/>
       <c r="M41" s="6" t="inlineStr"/>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="N41" s="6" t="inlineStr"/>
+      <c r="O41" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3059,31 +3289,36 @@
           <t>品牌授權過濾擋下；無授權資料時不得 fail-open 放行（fail-closed 驗證）</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>權限</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>FR-TEC-02、FR-TEC-03</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>SC-05、SC-12、SC-14</t>
         </is>
       </c>
-      <c r="J42" s="6" t="inlineStr"/>
       <c r="K42" s="6" t="inlineStr"/>
       <c r="L42" s="6" t="inlineStr"/>
       <c r="M42" s="6" t="inlineStr"/>
-      <c r="N42" s="5" t="inlineStr">
+      <c r="N42" s="6" t="inlineStr"/>
+      <c r="O42" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3115,31 +3350,36 @@
           <t>工單 on_site；evidence 入庫帶 purpose 分類</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>happy</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>FR-API-08</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>SC-06</t>
         </is>
       </c>
-      <c r="J43" s="6" t="inlineStr"/>
       <c r="K43" s="6" t="inlineStr"/>
       <c r="L43" s="6" t="inlineStr"/>
       <c r="M43" s="6" t="inlineStr"/>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="N43" s="6" t="inlineStr"/>
+      <c r="O43" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3171,31 +3411,36 @@
           <t>師傅自確 + 客戶簽名 + 照片三件套即通過</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>happy</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>FR-API-08</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>SC-07</t>
         </is>
       </c>
-      <c r="J44" s="6" t="inlineStr"/>
       <c r="K44" s="6" t="inlineStr"/>
       <c r="L44" s="6" t="inlineStr"/>
       <c r="M44" s="6" t="inlineStr"/>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="N44" s="6" t="inlineStr"/>
+      <c r="O44" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3227,31 +3472,36 @@
           <t>自動建 quote v+1 → 客戶 LIFF 確認後才可續作</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>happy</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>FR-API-08</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>SC-07</t>
         </is>
       </c>
-      <c r="J45" s="6" t="inlineStr"/>
       <c r="K45" s="6" t="inlineStr"/>
       <c r="L45" s="6" t="inlineStr"/>
       <c r="M45" s="6" t="inlineStr"/>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="N45" s="6" t="inlineStr"/>
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3283,31 +3533,36 @@
           <t>強制主管覆核；三件套（影音+文字+before/after 照）必齊</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>權限</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>FR-API-08</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>SC-07</t>
         </is>
       </c>
-      <c r="J46" s="6" t="inlineStr"/>
       <c r="K46" s="6" t="inlineStr"/>
       <c r="L46" s="6" t="inlineStr"/>
       <c r="M46" s="6" t="inlineStr"/>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="N46" s="6" t="inlineStr"/>
+      <c r="O46" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3339,31 +3594,36 @@
           <t>fallback 鏈完成；audit 標 consent_method=paper + evidence FK</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>FR-API-08</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>SC-06</t>
         </is>
       </c>
-      <c r="J47" s="6" t="inlineStr"/>
       <c r="K47" s="6" t="inlineStr"/>
       <c r="L47" s="6" t="inlineStr"/>
       <c r="M47" s="6" t="inlineStr"/>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="N47" s="6" t="inlineStr"/>
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3395,31 +3655,36 @@
           <t>工單轉入例外流程（改期/取消分流）；不得直接結案</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>FR-API-18</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>SC-06、SC-07</t>
         </is>
       </c>
-      <c r="J48" s="6" t="inlineStr"/>
       <c r="K48" s="6" t="inlineStr"/>
       <c r="L48" s="6" t="inlineStr"/>
       <c r="M48" s="6" t="inlineStr"/>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="N48" s="6" t="inlineStr"/>
+      <c r="O48" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3451,31 +3716,36 @@
           <t>工單 on_site → quoted；建 quote v+1（supersedes_quote_id 串鏈）→ 客戶 LIFF 確認 → approved 續工；拒絕 → 按原報價完工或走取消分流</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>happy</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>FR-TEC-07</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>SC-07</t>
         </is>
       </c>
-      <c r="J49" s="6" t="inlineStr"/>
       <c r="K49" s="6" t="inlineStr"/>
       <c r="L49" s="6" t="inlineStr"/>
       <c r="M49" s="6" t="inlineStr"/>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="N49" s="6" t="inlineStr"/>
+      <c r="O49" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3507,31 +3777,36 @@
           <t>品牌引擎建 quote v+1 金額由引擎算；非 assignee → 403；同 request_id 重送 → 冪等回放；保固/建案案件自動送出 → 403（註：分層核可（501-2000/&gt;2000）與保固建案自動送出 403 兩斷言＝CR-0150 落地範圍，遺留〔標注 2026-07-10：分層核可已落地（CR-0150，5 測）；保固建案 403 歸 CR-0152〕）</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>權限+例外</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>例外</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>權限</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>FR-TEC-07</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>SC-07</t>
         </is>
       </c>
-      <c r="J50" s="6" t="inlineStr"/>
       <c r="K50" s="6" t="inlineStr"/>
       <c r="L50" s="6" t="inlineStr"/>
       <c r="M50" s="6" t="inlineStr"/>
-      <c r="N50" s="5" t="inlineStr">
+      <c r="N50" s="6" t="inlineStr"/>
+      <c r="O50" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3563,31 +3838,36 @@
           <t>onsite 結束即建 retrospective_audit 任務（due=+4h）進小編佇列；逾 4h 未補審 → audit alert 升主管；同品牌連 3 次逾時 → 自動開 ChangeRequest</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>timeout</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>FR-API-09、FR-API-19</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>SC-03</t>
         </is>
       </c>
-      <c r="J51" s="6" t="inlineStr"/>
       <c r="K51" s="6" t="inlineStr"/>
       <c r="L51" s="6" t="inlineStr"/>
       <c r="M51" s="6" t="inlineStr"/>
-      <c r="N51" s="5" t="inlineStr">
+      <c r="N51" s="6" t="inlineStr"/>
+      <c r="O51" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3619,31 +3899,36 @@
           <t>對帳單生成；佣金計費（per-job，品牌側）發 commission.accrued 事件 → 技師平台彙總結算（Billing/Settlement 分離，ADR-P014）</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>happy</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>FR-API-12、FR-TEC-06</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>SC-09</t>
         </is>
       </c>
-      <c r="J52" s="6" t="inlineStr"/>
       <c r="K52" s="6" t="inlineStr"/>
       <c r="L52" s="6" t="inlineStr"/>
       <c r="M52" s="6" t="inlineStr"/>
-      <c r="N52" s="5" t="inlineStr">
+      <c r="N52" s="6" t="inlineStr"/>
+      <c r="O52" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3675,31 +3960,36 @@
           <t>200 + 完整 audit 事件鏈</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>happy</t>
         </is>
       </c>
-      <c r="G53" s="4" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>FR-API-11</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>SC-06、SC-08、SC-09</t>
         </is>
       </c>
-      <c r="J53" s="6" t="inlineStr"/>
       <c r="K53" s="6" t="inlineStr"/>
       <c r="L53" s="6" t="inlineStr"/>
       <c r="M53" s="6" t="inlineStr"/>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="N53" s="6" t="inlineStr"/>
+      <c r="O53" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3731,31 +4021,36 @@
           <t>403 SOD_VIOLATION（X-Initiator/Approver/Executor 任二相同即拒）</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>權限</t>
         </is>
       </c>
-      <c r="G54" s="4" t="inlineStr">
+      <c r="H54" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>FR-API-11、FR-API-18</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>SC-08、SC-11</t>
         </is>
       </c>
-      <c r="J54" s="6" t="inlineStr"/>
       <c r="K54" s="6" t="inlineStr"/>
       <c r="L54" s="6" t="inlineStr"/>
       <c r="M54" s="6" t="inlineStr"/>
-      <c r="N54" s="5" t="inlineStr">
+      <c r="N54" s="6" t="inlineStr"/>
+      <c r="O54" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3787,31 +4082,36 @@
           <t>拒絕並升級至上一層核准者；有效額度 = min(requested, role_limit)</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>權限</t>
         </is>
       </c>
-      <c r="G55" s="4" t="inlineStr">
+      <c r="H55" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>FR-API-11</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>SC-08</t>
         </is>
       </c>
-      <c r="J55" s="6" t="inlineStr"/>
       <c r="K55" s="6" t="inlineStr"/>
       <c r="L55" s="6" t="inlineStr"/>
       <c r="M55" s="6" t="inlineStr"/>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="N55" s="6" t="inlineStr"/>
+      <c r="O55" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3843,31 +4143,36 @@
           <t>冪等回放（TTL 24h），不重複出帳</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>FR-API-11</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>SC-08</t>
         </is>
       </c>
-      <c r="J56" s="6" t="inlineStr"/>
       <c r="K56" s="6" t="inlineStr"/>
       <c r="L56" s="6" t="inlineStr"/>
       <c r="M56" s="6" t="inlineStr"/>
-      <c r="N56" s="5" t="inlineStr">
+      <c r="N56" s="6" t="inlineStr"/>
+      <c r="O56" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3899,31 +4204,36 @@
           <t>resolved；同人連簽 → 403</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>權限</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="H57" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>FR-API-18</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="J57" s="5" t="inlineStr">
         <is>
           <t>SC-08</t>
         </is>
       </c>
-      <c r="J57" s="6" t="inlineStr"/>
       <c r="K57" s="6" t="inlineStr"/>
       <c r="L57" s="6" t="inlineStr"/>
       <c r="M57" s="6" t="inlineStr"/>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="N57" s="6" t="inlineStr"/>
+      <c r="O57" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3955,31 +4265,36 @@
           <t>遭拒（append-only）；hash_self = sha256(hash_prev + content) 全數相符</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>FR-API-12、FR-DAT-06、FR-WEB-05、NFR-Aud-001</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="J58" s="5" t="inlineStr">
         <is>
           <t>SC-11、SC-18、SC-19</t>
         </is>
       </c>
-      <c r="J58" s="6" t="inlineStr"/>
       <c r="K58" s="6" t="inlineStr"/>
       <c r="L58" s="6" t="inlineStr"/>
       <c r="M58" s="6" t="inlineStr"/>
-      <c r="N58" s="5" t="inlineStr">
+      <c r="N58" s="6" t="inlineStr"/>
+      <c r="O58" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4011,31 +4326,36 @@
           <t>技師/vendor 僅見自己 scope；成本欄位對非授權角色遮蔽</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>權限</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="H59" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="I59" s="5" t="inlineStr">
         <is>
           <t>FR-API-12、FR-TEC-06</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="J59" s="5" t="inlineStr">
         <is>
           <t>SC-13</t>
         </is>
       </c>
-      <c r="J59" s="6" t="inlineStr"/>
       <c r="K59" s="6" t="inlineStr"/>
       <c r="L59" s="6" t="inlineStr"/>
       <c r="M59" s="6" t="inlineStr"/>
-      <c r="N59" s="5" t="inlineStr">
+      <c r="N59" s="6" t="inlineStr"/>
+      <c r="O59" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4067,27 +4387,36 @@
           <t>一律 403；授權矩陣（12 角色 × 12 資源 × 4 動作）與端點守衛一致，deny log 清零</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr"/>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>FR-PLT-02、NFR-Sec-003</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="J60" s="5" t="inlineStr">
         <is>
           <t>SC-11、SC-16</t>
         </is>
       </c>
-      <c r="J60" s="6" t="inlineStr"/>
       <c r="K60" s="6" t="inlineStr"/>
       <c r="L60" s="6" t="inlineStr"/>
       <c r="M60" s="6" t="inlineStr"/>
-      <c r="N60" s="5" t="inlineStr">
+      <c r="N60" s="6" t="inlineStr"/>
+      <c r="O60" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4119,27 +4448,36 @@
           <t>僅矩陣允許之組合通過；未列組合 deny-by-default</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr"/>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>FR-PLT-02、NFR-Sec-003</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="J61" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J61" s="6" t="inlineStr"/>
       <c r="K61" s="6" t="inlineStr"/>
       <c r="L61" s="6" t="inlineStr"/>
       <c r="M61" s="6" t="inlineStr"/>
-      <c r="N61" s="5" t="inlineStr">
+      <c r="N61" s="6" t="inlineStr"/>
+      <c r="O61" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4171,27 +4509,36 @@
           <t>僅 namespace 之 owner 角色可改；其餘 403</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr"/>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>FR-PLT-02、NFR-Sec-003</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>SC-18</t>
         </is>
       </c>
-      <c r="J62" s="6" t="inlineStr"/>
       <c r="K62" s="6" t="inlineStr"/>
       <c r="L62" s="6" t="inlineStr"/>
       <c r="M62" s="6" t="inlineStr"/>
-      <c r="N62" s="5" t="inlineStr">
+      <c r="N62" s="6" t="inlineStr"/>
+      <c r="O62" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4223,27 +4570,36 @@
           <t>停權 → 403 ACCOUNT_DISABLED；改密 → 401 TOKEN_STALE（每請求安全狀態重查）</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="I63" s="5" t="inlineStr">
         <is>
           <t>FR-PLT-02、NFR-Sec-003</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="J63" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J63" s="6" t="inlineStr"/>
       <c r="K63" s="6" t="inlineStr"/>
       <c r="L63" s="6" t="inlineStr"/>
       <c r="M63" s="6" t="inlineStr"/>
-      <c r="N63" s="5" t="inlineStr">
+      <c r="N63" s="6" t="inlineStr"/>
+      <c r="O63" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4275,27 +4631,36 @@
           <t>401（jti 撤銷表命中）</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr"/>
-      <c r="G64" s="4" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>FR-PLT-02、NFR-Sec-003</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="J64" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J64" s="6" t="inlineStr"/>
       <c r="K64" s="6" t="inlineStr"/>
       <c r="L64" s="6" t="inlineStr"/>
       <c r="M64" s="6" t="inlineStr"/>
-      <c r="N64" s="5" t="inlineStr">
+      <c r="N64" s="6" t="inlineStr"/>
+      <c r="O64" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4327,27 +4692,36 @@
           <t>403/404，不洩存在性；audit 記 cross_tenant_violation_attempted；100 組 mutation 0 洩漏</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr"/>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="I65" s="5" t="inlineStr">
         <is>
           <t>FR-DAT-03、NFR-Priv-006</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="J65" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J65" s="6" t="inlineStr"/>
       <c r="K65" s="6" t="inlineStr"/>
       <c r="L65" s="6" t="inlineStr"/>
       <c r="M65" s="6" t="inlineStr"/>
-      <c r="N65" s="5" t="inlineStr">
+      <c r="N65" s="6" t="inlineStr"/>
+      <c r="O65" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4379,27 +4753,36 @@
           <t>403 SOD_VIOLATION</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr">
+      <c r="I66" s="5" t="inlineStr">
         <is>
           <t>FR-API-18、NFR-Sec-003</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr">
+      <c r="J66" s="5" t="inlineStr">
         <is>
           <t>SC-08、SC-11</t>
         </is>
       </c>
-      <c r="J66" s="6" t="inlineStr"/>
       <c r="K66" s="6" t="inlineStr"/>
       <c r="L66" s="6" t="inlineStr"/>
       <c r="M66" s="6" t="inlineStr"/>
-      <c r="N66" s="5" t="inlineStr">
+      <c r="N66" s="6" t="inlineStr"/>
+      <c r="O66" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4431,27 +4814,36 @@
           <t>回放不重複寫（TTL 24h）</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr"/>
-      <c r="G67" s="4" t="inlineStr">
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="I67" s="5" t="inlineStr">
         <is>
           <t>FR-API-10</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
+      <c r="J67" s="5" t="inlineStr">
         <is>
           <t>SC-08</t>
         </is>
       </c>
-      <c r="J67" s="6" t="inlineStr"/>
       <c r="K67" s="6" t="inlineStr"/>
       <c r="L67" s="6" t="inlineStr"/>
       <c r="M67" s="6" t="inlineStr"/>
-      <c r="N67" s="5" t="inlineStr">
+      <c r="N67" s="6" t="inlineStr"/>
+      <c r="O67" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4483,27 +4875,36 @@
           <t>物理不可達——工具未註冊；白名單僅 read_file / list_dir / find_files / grep / web_search / transfer_to_human（對齊 test_tool_allowlist.py）</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr"/>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="I68" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-08、NFR-Sec-012</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="J68" s="5" t="inlineStr">
         <is>
           <t>SC-01</t>
         </is>
       </c>
-      <c r="J68" s="6" t="inlineStr"/>
       <c r="K68" s="6" t="inlineStr"/>
       <c r="L68" s="6" t="inlineStr"/>
       <c r="M68" s="6" t="inlineStr"/>
-      <c r="N68" s="5" t="inlineStr">
+      <c r="N68" s="6" t="inlineStr"/>
+      <c r="O68" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4535,27 +4936,36 @@
           <t>default deny raise；kind 僅限 profile/preference/fact/issue/dispatch（對齊 test_memory.py）</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr"/>
-      <c r="G69" s="4" t="inlineStr">
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="I69" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-06、NFR-Priv-006</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="J69" s="5" t="inlineStr">
         <is>
           <t>SC-01、SC-02、SC-19</t>
         </is>
       </c>
-      <c r="J69" s="6" t="inlineStr"/>
       <c r="K69" s="6" t="inlineStr"/>
       <c r="L69" s="6" t="inlineStr"/>
       <c r="M69" s="6" t="inlineStr"/>
-      <c r="N69" s="5" t="inlineStr">
+      <c r="N69" s="6" t="inlineStr"/>
+      <c r="O69" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4587,27 +4997,36 @@
           <t>後端 role_required 一律擋下——前端 gate 僅為 UX，非授權邊界；未登記路由 deny-by-default</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr"/>
-      <c r="G70" s="4" t="inlineStr">
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="I70" s="5" t="inlineStr">
         <is>
           <t>FR-WEB-02</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="J70" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J70" s="6" t="inlineStr"/>
       <c r="K70" s="6" t="inlineStr"/>
       <c r="L70" s="6" t="inlineStr"/>
       <c r="M70" s="6" t="inlineStr"/>
-      <c r="N70" s="5" t="inlineStr">
+      <c r="N70" s="6" t="inlineStr"/>
+      <c r="O70" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4639,27 +5058,36 @@
           <t>擋下並導回登入，不得靜默 fallback 至預設租戶</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr"/>
-      <c r="G71" s="4" t="inlineStr">
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="I71" s="5" t="inlineStr">
         <is>
           <t>FR-PLT-01、FR-WEB-02</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="J71" s="5" t="inlineStr">
         <is>
           <t>SC-12、SC-17</t>
         </is>
       </c>
-      <c r="J71" s="6" t="inlineStr"/>
       <c r="K71" s="6" t="inlineStr"/>
       <c r="L71" s="6" t="inlineStr"/>
       <c r="M71" s="6" t="inlineStr"/>
-      <c r="N71" s="5" t="inlineStr">
+      <c r="N71" s="6" t="inlineStr"/>
+      <c r="O71" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4691,27 +5119,36 @@
           <t>CI 失敗阻斷；套用時真 ERROR 不被 benign 警告淹沒</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr"/>
-      <c r="G72" s="4" t="inlineStr">
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="I72" s="5" t="inlineStr">
         <is>
           <t>FR-DAT-02、NFR-Sch-002</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="J72" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J72" s="6" t="inlineStr"/>
       <c r="K72" s="6" t="inlineStr"/>
       <c r="L72" s="6" t="inlineStr"/>
       <c r="M72" s="6" t="inlineStr"/>
-      <c r="N72" s="5" t="inlineStr">
+      <c r="N72" s="6" t="inlineStr"/>
+      <c r="O72" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4743,27 +5180,36 @@
           <t>未配置 → 503（fail-closed）；不符 → 401；比對為常數時間</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr"/>
-      <c r="G73" s="4" t="inlineStr">
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="I73" s="5" t="inlineStr">
         <is>
           <t>FR-API-13、NFR-Sec-011</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="J73" s="5" t="inlineStr">
         <is>
           <t>SC-02、SC-10</t>
         </is>
       </c>
-      <c r="J73" s="6" t="inlineStr"/>
       <c r="K73" s="6" t="inlineStr"/>
       <c r="L73" s="6" t="inlineStr"/>
       <c r="M73" s="6" t="inlineStr"/>
-      <c r="N73" s="5" t="inlineStr">
+      <c r="N73" s="6" t="inlineStr"/>
+      <c r="O73" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4795,27 +5241,36 @@
           <t>reserve-first 永久 PK 去重，重試不重複建卡；持續失敗入 DLQ，1h 內人工 review</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr"/>
-      <c r="G74" s="4" t="inlineStr">
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="I74" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-10、FR-API-15</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr">
+      <c r="J74" s="5" t="inlineStr">
         <is>
           <t>SC-02、SC-09、SC-11、SC-19</t>
         </is>
       </c>
-      <c r="J74" s="6" t="inlineStr"/>
       <c r="K74" s="6" t="inlineStr"/>
       <c r="L74" s="6" t="inlineStr"/>
       <c r="M74" s="6" t="inlineStr"/>
-      <c r="N74" s="5" t="inlineStr">
+      <c r="N74" s="6" t="inlineStr"/>
+      <c r="O74" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4847,27 +5302,36 @@
           <t>友善罐頭回覆（不外洩 traceback/sentinel 原文）；多供應商 failover 🔜 規劃中</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr"/>
-      <c r="G75" s="4" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="I75" s="5" t="inlineStr">
         <is>
           <t>FR-PLT-05</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="J75" s="5" t="inlineStr">
         <is>
           <t>SC-18</t>
         </is>
       </c>
-      <c r="J75" s="6" t="inlineStr"/>
       <c r="K75" s="6" t="inlineStr"/>
       <c r="L75" s="6" t="inlineStr"/>
       <c r="M75" s="6" t="inlineStr"/>
-      <c r="N75" s="5" t="inlineStr">
+      <c r="N75" s="6" t="inlineStr"/>
+      <c r="O75" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4899,27 +5363,36 @@
           <t>fallback 罐頭回覆仍於 5s 內送達；轉真人通道不中斷</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr"/>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="I76" s="5" t="inlineStr">
         <is>
           <t>FR-PLT-05</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="J76" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J76" s="6" t="inlineStr"/>
       <c r="K76" s="6" t="inlineStr"/>
       <c r="L76" s="6" t="inlineStr"/>
       <c r="M76" s="6" t="inlineStr"/>
-      <c r="N76" s="5" t="inlineStr">
+      <c r="N76" s="6" t="inlineStr"/>
+      <c r="O76" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4951,27 +5424,36 @@
           <t>一般讀取退回 claims-only（fail-open 可用性取捨）；金流/派工等關鍵寫入拒絕（503）而非放行（fail-closed 白名單為上線前條件）</t>
         </is>
       </c>
-      <c r="F77" s="4" t="inlineStr"/>
-      <c r="G77" s="4" t="inlineStr">
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="I77" s="5" t="inlineStr">
         <is>
           <t>NFR-Avail-010</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="J77" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J77" s="6" t="inlineStr"/>
       <c r="K77" s="6" t="inlineStr"/>
       <c r="L77" s="6" t="inlineStr"/>
       <c r="M77" s="6" t="inlineStr"/>
-      <c r="N77" s="5" t="inlineStr">
+      <c r="N77" s="6" t="inlineStr"/>
+      <c r="O77" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5003,27 +5485,36 @@
           <t>啟動失敗並明確告警，不得靜默 fallback 單庫</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr"/>
-      <c r="G78" s="4" t="inlineStr">
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="I78" s="5" t="inlineStr">
         <is>
           <t>FR-DAT-03</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="J78" s="5" t="inlineStr">
         <is>
           <t>SC-17</t>
         </is>
       </c>
-      <c r="J78" s="6" t="inlineStr"/>
       <c r="K78" s="6" t="inlineStr"/>
       <c r="L78" s="6" t="inlineStr"/>
       <c r="M78" s="6" t="inlineStr"/>
-      <c r="N78" s="5" t="inlineStr">
+      <c r="N78" s="6" t="inlineStr"/>
+      <c r="O78" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -5055,27 +5546,36 @@
           <t>投影/結算最終一致補齊；事件冪等（seq + idempotency key）不重複入帳</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr"/>
-      <c r="G79" s="4" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>FR-API-14、FR-DAT-05、FR-PLT-04、FR-TEC-04、FR-TEC-05</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="J79" s="5" t="inlineStr">
         <is>
           <t>SC-05、SC-13、SC-14</t>
         </is>
       </c>
-      <c r="J79" s="6" t="inlineStr"/>
       <c r="K79" s="6" t="inlineStr"/>
       <c r="L79" s="6" t="inlineStr"/>
       <c r="M79" s="6" t="inlineStr"/>
-      <c r="N79" s="5" t="inlineStr">
+      <c r="N79" s="6" t="inlineStr"/>
+      <c r="O79" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -5103,27 +5603,36 @@
           <t>AI 首回應 p95 &lt; 5s</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr"/>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>NFR-Perf-001、NFR-Scal-001</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="J80" s="5" t="inlineStr">
         <is>
           <t>SC-01、SC-02</t>
         </is>
       </c>
-      <c r="J80" s="6" t="inlineStr"/>
       <c r="K80" s="6" t="inlineStr"/>
       <c r="L80" s="6" t="inlineStr"/>
       <c r="M80" s="6" t="inlineStr"/>
-      <c r="N80" s="5" t="inlineStr">
+      <c r="N80" s="6" t="inlineStr"/>
+      <c r="O80" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -5151,27 +5660,36 @@
           <t>p95 &lt; 5s；退化 graceful 不 5xx</t>
         </is>
       </c>
-      <c r="F81" s="4" t="inlineStr"/>
-      <c r="G81" s="4" t="inlineStr">
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>NFR-Perf-001、NFR-Scal-002</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="J81" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J81" s="6" t="inlineStr"/>
       <c r="K81" s="6" t="inlineStr"/>
       <c r="L81" s="6" t="inlineStr"/>
       <c r="M81" s="6" t="inlineStr"/>
-      <c r="N81" s="5" t="inlineStr">
+      <c r="N81" s="6" t="inlineStr"/>
+      <c r="O81" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5199,27 +5717,36 @@
           <t>p95 &lt; 300ms</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr"/>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>FR-TEC-03、NFR-Perf-007</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="J82" s="5" t="inlineStr">
         <is>
           <t>SC-05</t>
         </is>
       </c>
-      <c r="J82" s="6" t="inlineStr"/>
       <c r="K82" s="6" t="inlineStr"/>
       <c r="L82" s="6" t="inlineStr"/>
       <c r="M82" s="6" t="inlineStr"/>
-      <c r="N82" s="5" t="inlineStr">
+      <c r="N82" s="6" t="inlineStr"/>
+      <c r="O82" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -5247,27 +5774,36 @@
           <t>429 / 罐頭回覆降級，無雪崩</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr"/>
-      <c r="G83" s="4" t="inlineStr">
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="I83" s="5" t="inlineStr">
         <is>
           <t>NFR-Scal-002</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="J83" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J83" s="6" t="inlineStr"/>
       <c r="K83" s="6" t="inlineStr"/>
       <c r="L83" s="6" t="inlineStr"/>
       <c r="M83" s="6" t="inlineStr"/>
-      <c r="N83" s="5" t="inlineStr">
+      <c r="N83" s="6" t="inlineStr"/>
+      <c r="O83" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5295,27 +5831,36 @@
           <t>事件 lag p99 ≤ 30s</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr"/>
-      <c r="G84" s="4" t="inlineStr">
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="I84" s="5" t="inlineStr">
         <is>
           <t>NFR-Perf-009</t>
         </is>
       </c>
-      <c r="I84" s="5" t="inlineStr">
+      <c r="J84" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J84" s="6" t="inlineStr"/>
       <c r="K84" s="6" t="inlineStr"/>
       <c r="L84" s="6" t="inlineStr"/>
       <c r="M84" s="6" t="inlineStr"/>
-      <c r="N84" s="5" t="inlineStr">
+      <c r="N84" s="6" t="inlineStr"/>
+      <c r="O84" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5343,27 +5888,36 @@
           <t>攔截 ≥ 95%；工具白名單限制爆炸半徑</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr"/>
-      <c r="G85" s="4" t="inlineStr">
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H85" s="5" t="inlineStr">
+      <c r="I85" s="5" t="inlineStr">
         <is>
           <t>NFR-Sec-005</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr">
+      <c r="J85" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J85" s="6" t="inlineStr"/>
       <c r="K85" s="6" t="inlineStr"/>
       <c r="L85" s="6" t="inlineStr"/>
       <c r="M85" s="6" t="inlineStr"/>
-      <c r="N85" s="5" t="inlineStr">
+      <c r="N85" s="6" t="inlineStr"/>
+      <c r="O85" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5391,27 +5945,36 @@
           <t>誤攔 &lt; 1%</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr"/>
-      <c r="G86" s="4" t="inlineStr">
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H86" s="5" t="inlineStr">
+      <c r="I86" s="5" t="inlineStr">
         <is>
           <t>NFR-Sec-006</t>
         </is>
       </c>
-      <c r="I86" s="5" t="inlineStr">
+      <c r="J86" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J86" s="6" t="inlineStr"/>
       <c r="K86" s="6" t="inlineStr"/>
       <c r="L86" s="6" t="inlineStr"/>
       <c r="M86" s="6" t="inlineStr"/>
-      <c r="N86" s="5" t="inlineStr">
+      <c r="N86" s="6" t="inlineStr"/>
+      <c r="O86" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5439,27 +6002,36 @@
           <t>任務成功率 ≥ 90%（n=10 each）</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr"/>
-      <c r="G87" s="4" t="inlineStr">
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr">
+      <c r="I87" s="5" t="inlineStr">
         <is>
           <t>FR-WEB-06、NFR-A11y-002</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr">
+      <c r="J87" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J87" s="6" t="inlineStr"/>
       <c r="K87" s="6" t="inlineStr"/>
       <c r="L87" s="6" t="inlineStr"/>
       <c r="M87" s="6" t="inlineStr"/>
-      <c r="N87" s="5" t="inlineStr">
+      <c r="N87" s="6" t="inlineStr"/>
+      <c r="O87" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5487,27 +6059,36 @@
           <t>WCAG 2.2 AA 全項通過（金額對比升 7:1）</t>
         </is>
       </c>
-      <c r="F88" s="4" t="inlineStr"/>
-      <c r="G88" s="4" t="inlineStr">
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H88" s="5" t="inlineStr">
+      <c r="I88" s="5" t="inlineStr">
         <is>
           <t>NFR-A11y-002</t>
         </is>
       </c>
-      <c r="I88" s="5" t="inlineStr">
+      <c r="J88" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J88" s="6" t="inlineStr"/>
       <c r="K88" s="6" t="inlineStr"/>
       <c r="L88" s="6" t="inlineStr"/>
       <c r="M88" s="6" t="inlineStr"/>
-      <c r="N88" s="5" t="inlineStr">
+      <c r="N88" s="6" t="inlineStr"/>
+      <c r="O88" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5535,27 +6116,36 @@
           <t>兩階段：軟刪即時生效 → T+30 硬刪 cron 執行 + ledger append；記憶（agent.*）與營運資料同步涵蓋</t>
         </is>
       </c>
-      <c r="F89" s="4" t="inlineStr"/>
-      <c r="G89" s="4" t="inlineStr">
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="I89" s="5" t="inlineStr">
         <is>
           <t>FR-API-16、NFR-Comp-004、NFR-Priv-005、NFR-Priv-008</t>
         </is>
       </c>
-      <c r="I89" s="5" t="inlineStr">
+      <c r="J89" s="5" t="inlineStr">
         <is>
           <t>SC-19</t>
         </is>
       </c>
-      <c r="J89" s="6" t="inlineStr"/>
       <c r="K89" s="6" t="inlineStr"/>
       <c r="L89" s="6" t="inlineStr"/>
       <c r="M89" s="6" t="inlineStr"/>
-      <c r="N89" s="5" t="inlineStr">
+      <c r="N89" s="6" t="inlineStr"/>
+      <c r="O89" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -5583,27 +6173,36 @@
           <t>423 拒絕 + 7d 內客戶通知（含預計解除時間）+ audit gdpr_forget_blocked</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr"/>
-      <c r="G90" s="4" t="inlineStr">
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H90" s="5" t="inlineStr">
+      <c r="I90" s="5" t="inlineStr">
         <is>
           <t>FR-API-16、NFR-Comp-004、NFR-Priv-005</t>
         </is>
       </c>
-      <c r="I90" s="5" t="inlineStr">
+      <c r="J90" s="5" t="inlineStr">
         <is>
           <t>SC-19</t>
         </is>
       </c>
-      <c r="J90" s="6" t="inlineStr"/>
       <c r="K90" s="6" t="inlineStr"/>
       <c r="L90" s="6" t="inlineStr"/>
       <c r="M90" s="6" t="inlineStr"/>
-      <c r="N90" s="5" t="inlineStr">
+      <c r="N90" s="6" t="inlineStr"/>
+      <c r="O90" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -5631,27 +6230,36 @@
           <t>無明文手機/完整 PII；識別碼截斷輸出</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr"/>
-      <c r="G91" s="4" t="inlineStr">
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="I91" s="5" t="inlineStr">
         <is>
           <t>NFR-Comp-004</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr">
+      <c r="J91" s="5" t="inlineStr">
         <is>
           <t>SC-19</t>
         </is>
       </c>
-      <c r="J91" s="6" t="inlineStr"/>
       <c r="K91" s="6" t="inlineStr"/>
       <c r="L91" s="6" t="inlineStr"/>
       <c r="M91" s="6" t="inlineStr"/>
-      <c r="N91" s="5" t="inlineStr">
+      <c r="N91" s="6" t="inlineStr"/>
+      <c r="O91" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -5679,27 +6287,36 @@
           <t>過期 media 軟刪且 list 排除；RMA +3y / legal-hold 永久不刪</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr"/>
-      <c r="G92" s="4" t="inlineStr">
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H92" s="5" t="inlineStr">
+      <c r="I92" s="5" t="inlineStr">
         <is>
           <t>FR-API-16、NFR-Comp-004、NFR-Priv-008</t>
         </is>
       </c>
-      <c r="I92" s="5" t="inlineStr">
+      <c r="J92" s="5" t="inlineStr">
         <is>
           <t>SC-19</t>
         </is>
       </c>
-      <c r="J92" s="6" t="inlineStr"/>
       <c r="K92" s="6" t="inlineStr"/>
       <c r="L92" s="6" t="inlineStr"/>
       <c r="M92" s="6" t="inlineStr"/>
-      <c r="N92" s="5" t="inlineStr">
+      <c r="N92" s="6" t="inlineStr"/>
+      <c r="O92" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -5727,27 +6344,36 @@
           <t>必須失敗；覆核率 100%；reviewer 缺席 &gt;24h → 升級 + 暫停 publish</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr"/>
-      <c r="G93" s="4" t="inlineStr">
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H93" s="5" t="inlineStr">
+      <c r="I93" s="5" t="inlineStr">
         <is>
           <t>FR-REF-03、FR-REF-05、NFR-Aud-004、NFR-Comp-002</t>
         </is>
       </c>
-      <c r="I93" s="5" t="inlineStr">
+      <c r="J93" s="5" t="inlineStr">
         <is>
           <t>SC-16</t>
         </is>
       </c>
-      <c r="J93" s="6" t="inlineStr"/>
       <c r="K93" s="6" t="inlineStr"/>
       <c r="L93" s="6" t="inlineStr"/>
       <c r="M93" s="6" t="inlineStr"/>
-      <c r="N93" s="5" t="inlineStr">
+      <c r="N93" s="6" t="inlineStr"/>
+      <c r="O93" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -5775,27 +6401,36 @@
           <t>violation = 0（雙 gate）</t>
         </is>
       </c>
-      <c r="F94" s="4" t="inlineStr"/>
-      <c r="G94" s="4" t="inlineStr">
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H94" s="5" t="inlineStr">
+      <c r="I94" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-11、NFR-Comp-003、NFR-Sec-009</t>
         </is>
       </c>
-      <c r="I94" s="5" t="inlineStr">
+      <c r="J94" s="5" t="inlineStr">
         <is>
           <t>SC-01、SC-06</t>
         </is>
       </c>
-      <c r="J94" s="6" t="inlineStr"/>
       <c r="K94" s="6" t="inlineStr"/>
       <c r="L94" s="6" t="inlineStr"/>
       <c r="M94" s="6" t="inlineStr"/>
-      <c r="N94" s="5" t="inlineStr">
+      <c r="N94" s="6" t="inlineStr"/>
+      <c r="O94" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -5823,27 +6458,36 @@
           <t>識別 ≥ 90%、誤攔 ≤ 1%；連續劣化觸發 block/incident</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr"/>
-      <c r="G95" s="4" t="inlineStr">
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H95" s="5" t="inlineStr">
+      <c r="I95" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-04、NFR-Comp-001</t>
         </is>
       </c>
-      <c r="I95" s="5" t="inlineStr">
+      <c r="J95" s="5" t="inlineStr">
         <is>
           <t>SC-03</t>
         </is>
       </c>
-      <c r="J95" s="6" t="inlineStr"/>
       <c r="K95" s="6" t="inlineStr"/>
       <c r="L95" s="6" t="inlineStr"/>
       <c r="M95" s="6" t="inlineStr"/>
-      <c r="N95" s="5" t="inlineStr">
+      <c r="N95" s="6" t="inlineStr"/>
+      <c r="O95" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -5871,27 +6515,36 @@
           <t>內容嚴格源自 bronze 層；PDF 來源僅 URL 引用；provenance 由 Python 強制覆寫（不信任 LLM 產生）</t>
         </is>
       </c>
-      <c r="F96" s="4" t="inlineStr"/>
-      <c r="G96" s="4" t="inlineStr">
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 未標註</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H96" s="5" t="inlineStr">
+      <c r="I96" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-07、FR-DAT-01、FR-REF-01、FR-REF-04、NFR-DQ-001、NFR-DQ-003</t>
         </is>
       </c>
-      <c r="I96" s="5" t="inlineStr">
+      <c r="J96" s="5" t="inlineStr">
         <is>
           <t>SC-15</t>
         </is>
       </c>
-      <c r="J96" s="6" t="inlineStr"/>
       <c r="K96" s="6" t="inlineStr"/>
       <c r="L96" s="6" t="inlineStr"/>
       <c r="M96" s="6" t="inlineStr"/>
-      <c r="N96" s="5" t="inlineStr">
+      <c r="N96" s="6" t="inlineStr"/>
+      <c r="O96" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -5923,31 +6576,36 @@
           <t>AuthImage 以授權 fetch→Blob URL 顯示；可放大、關閉並 revoke；401/403 顯示失敗佔位，不裸露 token 或造成整頁崩潰</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>權限+例外</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="inlineStr">
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>例外</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>權限</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H97" s="5" t="inlineStr">
+      <c r="I97" s="5" t="inlineStr">
         <is>
           <t>FR-WEB-03、FR-WEB-07</t>
         </is>
       </c>
-      <c r="I97" s="5" t="inlineStr">
+      <c r="J97" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J97" s="6" t="inlineStr"/>
       <c r="K97" s="6" t="inlineStr"/>
       <c r="L97" s="6" t="inlineStr"/>
       <c r="M97" s="6" t="inlineStr"/>
-      <c r="N97" s="5" t="inlineStr">
+      <c r="N97" s="6" t="inlineStr"/>
+      <c r="O97" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5979,31 +6637,36 @@
           <t>有姓名時顯示技師全名；缺姓名時採明確 fallback（非誤顯其他技師）；狀態與 accepted_at 時間一致</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>happy+例外</t>
-        </is>
-      </c>
-      <c r="G98" s="4" t="inlineStr">
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>happy＋例外</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H98" s="5" t="inlineStr">
+      <c r="I98" s="5" t="inlineStr">
         <is>
           <t>FR-WEB-03</t>
         </is>
       </c>
-      <c r="I98" s="5" t="inlineStr">
+      <c r="J98" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J98" s="6" t="inlineStr"/>
       <c r="K98" s="6" t="inlineStr"/>
       <c r="L98" s="6" t="inlineStr"/>
       <c r="M98" s="6" t="inlineStr"/>
-      <c r="N98" s="5" t="inlineStr">
+      <c r="N98" s="6" t="inlineStr"/>
+      <c r="O98" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6035,31 +6698,36 @@
           <t>一個 webhook 只產生一個 Turn；SAVE 失敗記 trace/告警但仍回覆；不重複寫 memory 或重送訊息</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G99" s="4" t="inlineStr">
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H99" s="5" t="inlineStr">
+      <c r="I99" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-02</t>
         </is>
       </c>
-      <c r="I99" s="5" t="inlineStr">
+      <c r="J99" s="5" t="inlineStr">
         <is>
           <t>SC-01、SC-10</t>
         </is>
       </c>
-      <c r="J99" s="6" t="inlineStr"/>
       <c r="K99" s="6" t="inlineStr"/>
       <c r="L99" s="6" t="inlineStr"/>
       <c r="M99" s="6" t="inlineStr"/>
-      <c r="N99" s="5" t="inlineStr">
+      <c r="N99" s="6" t="inlineStr"/>
+      <c r="O99" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6091,31 +6759,36 @@
           <t>未釐清依規則轉真人；已釐清寫 confirmation；低相似度不假稱命中案例</t>
         </is>
       </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G100" s="4" t="inlineStr">
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H100" s="5" t="inlineStr">
+      <c r="I100" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-03</t>
         </is>
       </c>
-      <c r="I100" s="5" t="inlineStr">
+      <c r="J100" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J100" s="6" t="inlineStr"/>
       <c r="K100" s="6" t="inlineStr"/>
       <c r="L100" s="6" t="inlineStr"/>
       <c r="M100" s="6" t="inlineStr"/>
-      <c r="N100" s="5" t="inlineStr">
+      <c r="N100" s="6" t="inlineStr"/>
+      <c r="O100" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6147,31 +6820,36 @@
           <t>5 分鐘內建立可追溯轉人紀錄；第一次失敗不得假稱已派工，重試後只留一筆 escalation</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G101" s="4" t="inlineStr">
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H101" s="5" t="inlineStr">
+      <c r="I101" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-04</t>
         </is>
       </c>
-      <c r="I101" s="5" t="inlineStr">
+      <c r="J101" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J101" s="6" t="inlineStr"/>
       <c r="K101" s="6" t="inlineStr"/>
       <c r="L101" s="6" t="inlineStr"/>
       <c r="M101" s="6" t="inlineStr"/>
-      <c r="N101" s="5" t="inlineStr">
+      <c r="N101" s="6" t="inlineStr"/>
+      <c r="O101" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6203,31 +6881,36 @@
           <t>僅回本租戶可引用事實；不存在或 timeout 回 references／轉人降級，不編造型號或跨租戶內容</t>
         </is>
       </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G102" s="4" t="inlineStr">
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H102" s="5" t="inlineStr">
+      <c r="I102" s="5" t="inlineStr">
         <is>
           <t>FR-AGT-07、FR-DAT-04</t>
         </is>
       </c>
-      <c r="I102" s="5" t="inlineStr">
+      <c r="J102" s="5" t="inlineStr">
         <is>
           <t>SC-15</t>
         </is>
       </c>
-      <c r="J102" s="6" t="inlineStr"/>
       <c r="K102" s="6" t="inlineStr"/>
       <c r="L102" s="6" t="inlineStr"/>
       <c r="M102" s="6" t="inlineStr"/>
-      <c r="N102" s="5" t="inlineStr">
+      <c r="N102" s="6" t="inlineStr"/>
+      <c r="O102" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6259,31 +6942,36 @@
           <t>未完成任一步不得啟用 License；重跑冪等且有 provisioning audit；成功後僅新品牌可登入與進線</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G103" s="4" t="inlineStr">
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H103" s="5" t="inlineStr">
+      <c r="I103" s="5" t="inlineStr">
         <is>
           <t>FR-PLT-03</t>
         </is>
       </c>
-      <c r="I103" s="5" t="inlineStr">
+      <c r="J103" s="5" t="inlineStr">
         <is>
           <t>SC-17</t>
         </is>
       </c>
-      <c r="J103" s="6" t="inlineStr"/>
       <c r="K103" s="6" t="inlineStr"/>
       <c r="L103" s="6" t="inlineStr"/>
       <c r="M103" s="6" t="inlineStr"/>
-      <c r="N103" s="5" t="inlineStr">
+      <c r="N103" s="6" t="inlineStr"/>
+      <c r="O103" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6315,31 +7003,36 @@
           <t>非法檔在發佈前被靜態拒絕且無 runtime side effect；合法版本可審計、可回退</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G104" s="4" t="inlineStr">
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H104" s="5" t="inlineStr">
+      <c r="I104" s="5" t="inlineStr">
         <is>
           <t>FR-PLT-07</t>
         </is>
       </c>
-      <c r="I104" s="5" t="inlineStr">
+      <c r="J104" s="5" t="inlineStr">
         <is>
           <t>SC-18</t>
         </is>
       </c>
-      <c r="J104" s="6" t="inlineStr"/>
       <c r="K104" s="6" t="inlineStr"/>
       <c r="L104" s="6" t="inlineStr"/>
       <c r="M104" s="6" t="inlineStr"/>
-      <c r="N104" s="5" t="inlineStr">
+      <c r="N104" s="6" t="inlineStr"/>
+      <c r="O104" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6371,31 +7064,36 @@
           <t>保護層不可覆寫；失敗時停止擴散並回上一版；版本、審核、測試與 rollback 全留 audit</t>
         </is>
       </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G105" s="4" t="inlineStr">
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H105" s="5" t="inlineStr">
+      <c r="I105" s="5" t="inlineStr">
         <is>
           <t>FR-PLT-08</t>
         </is>
       </c>
-      <c r="I105" s="5" t="inlineStr">
+      <c r="J105" s="5" t="inlineStr">
         <is>
           <t>SC-18</t>
         </is>
       </c>
-      <c r="J105" s="6" t="inlineStr"/>
       <c r="K105" s="6" t="inlineStr"/>
       <c r="L105" s="6" t="inlineStr"/>
       <c r="M105" s="6" t="inlineStr"/>
-      <c r="N105" s="5" t="inlineStr">
+      <c r="N105" s="6" t="inlineStr"/>
+      <c r="O105" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6427,31 +7125,36 @@
           <t>不允許的跨面一律 403；platform 走獨立 guard/資料庫；拒絕前不讀取目標業務資料</t>
         </is>
       </c>
-      <c r="F106" s="4" t="inlineStr">
+      <c r="F106" s="5" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="G106" s="4" t="inlineStr">
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H106" s="5" t="inlineStr">
+      <c r="I106" s="5" t="inlineStr">
         <is>
           <t>FR-PLT-09</t>
         </is>
       </c>
-      <c r="I106" s="5" t="inlineStr">
+      <c r="J106" s="5" t="inlineStr">
         <is>
           <t>SC-12、SC-14、SC-17</t>
         </is>
       </c>
-      <c r="J106" s="6" t="inlineStr"/>
       <c r="K106" s="6" t="inlineStr"/>
       <c r="L106" s="6" t="inlineStr"/>
       <c r="M106" s="6" t="inlineStr"/>
-      <c r="N106" s="5" t="inlineStr">
+      <c r="N106" s="6" t="inlineStr"/>
+      <c r="O106" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6483,31 +7186,36 @@
           <t>僅符合 gate 的資料進 bronze；失敗／重送不產生半成品或跨租戶資料；來源與失敗原因可稽核</t>
         </is>
       </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G107" s="4" t="inlineStr">
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H107" s="5" t="inlineStr">
+      <c r="I107" s="5" t="inlineStr">
         <is>
           <t>FR-DAT-01、FR-REF-01</t>
         </is>
       </c>
-      <c r="I107" s="5" t="inlineStr">
+      <c r="J107" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J107" s="6" t="inlineStr"/>
       <c r="K107" s="6" t="inlineStr"/>
       <c r="L107" s="6" t="inlineStr"/>
       <c r="M107" s="6" t="inlineStr"/>
-      <c r="N107" s="5" t="inlineStr">
+      <c r="N107" s="6" t="inlineStr"/>
+      <c r="O107" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6539,31 +7247,36 @@
           <t>事實只進 fact draft、行為只進 skill diff；未核可 draft 不改既有內容；重跑 append-only 可回溯</t>
         </is>
       </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G108" s="4" t="inlineStr">
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H108" s="5" t="inlineStr">
+      <c r="I108" s="5" t="inlineStr">
         <is>
           <t>FR-REF-02</t>
         </is>
       </c>
-      <c r="I108" s="5" t="inlineStr">
+      <c r="J108" s="5" t="inlineStr">
         <is>
           <t>SC-15</t>
         </is>
       </c>
-      <c r="J108" s="6" t="inlineStr"/>
       <c r="K108" s="6" t="inlineStr"/>
       <c r="L108" s="6" t="inlineStr"/>
       <c r="M108" s="6" t="inlineStr"/>
-      <c r="N108" s="5" t="inlineStr">
+      <c r="N108" s="6" t="inlineStr"/>
+      <c r="O108" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6595,31 +7308,36 @@
           <t>違規均零落地；核可後 facts 帶 tenant/provenance 進 pgvector、行為 append-only 發佈；逾時暫停並升級</t>
         </is>
       </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G109" s="4" t="inlineStr">
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H109" s="5" t="inlineStr">
+      <c r="I109" s="5" t="inlineStr">
         <is>
           <t>FR-REF-03、FR-REF-04、FR-REF-05</t>
         </is>
       </c>
-      <c r="I109" s="5" t="inlineStr">
+      <c r="J109" s="5" t="inlineStr">
         <is>
           <t>SC-15、SC-16</t>
         </is>
       </c>
-      <c r="J109" s="6" t="inlineStr"/>
       <c r="K109" s="6" t="inlineStr"/>
       <c r="L109" s="6" t="inlineStr"/>
       <c r="M109" s="6" t="inlineStr"/>
-      <c r="N109" s="5" t="inlineStr">
+      <c r="N109" s="6" t="inlineStr"/>
+      <c r="O109" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6651,31 +7369,36 @@
           <t>身分只寫 lock_tech；重送冪等；未核可或未授權者永不進候選池</t>
         </is>
       </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G110" s="4" t="inlineStr">
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H110" s="5" t="inlineStr">
+      <c r="I110" s="5" t="inlineStr">
         <is>
           <t>FR-TEC-01</t>
         </is>
       </c>
-      <c r="I110" s="5" t="inlineStr">
+      <c r="J110" s="5" t="inlineStr">
         <is>
           <t>SC-12</t>
         </is>
       </c>
-      <c r="J110" s="6" t="inlineStr"/>
       <c r="K110" s="6" t="inlineStr"/>
       <c r="L110" s="6" t="inlineStr"/>
       <c r="M110" s="6" t="inlineStr"/>
-      <c r="N110" s="5" t="inlineStr">
+      <c r="N110" s="6" t="inlineStr"/>
+      <c r="O110" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6707,31 +7430,36 @@
           <t>撤銷/停權後各品牌候選集立即排除；重送不重複通知；復權前不得自行恢復可派狀態</t>
         </is>
       </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G111" s="4" t="inlineStr">
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H111" s="5" t="inlineStr">
+      <c r="I111" s="5" t="inlineStr">
         <is>
           <t>FR-TEC-08</t>
         </is>
       </c>
-      <c r="I111" s="5" t="inlineStr">
+      <c r="J111" s="5" t="inlineStr">
         <is>
           <t>SC-14</t>
         </is>
       </c>
-      <c r="J111" s="6" t="inlineStr"/>
       <c r="K111" s="6" t="inlineStr"/>
       <c r="L111" s="6" t="inlineStr"/>
       <c r="M111" s="6" t="inlineStr"/>
-      <c r="N111" s="5" t="inlineStr">
+      <c r="N111" s="6" t="inlineStr"/>
+      <c r="O111" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6763,31 +7491,36 @@
           <t>空池只能進 dispatch_pending 並 alert；不合格者永不入選；合格者出現後按急件規則媒合；重試不重複指派或通知</t>
         </is>
       </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G112" s="4" t="inlineStr">
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H112" s="5" t="inlineStr">
+      <c r="I112" s="5" t="inlineStr">
         <is>
           <t>FR-API-05</t>
         </is>
       </c>
-      <c r="I112" s="5" t="inlineStr">
+      <c r="J112" s="5" t="inlineStr">
         <is>
           <t>SC-05、SC-14</t>
         </is>
       </c>
-      <c r="J112" s="6" t="inlineStr"/>
       <c r="K112" s="6" t="inlineStr"/>
       <c r="L112" s="6" t="inlineStr"/>
       <c r="M112" s="6" t="inlineStr"/>
-      <c r="N112" s="5" t="inlineStr">
+      <c r="N112" s="6" t="inlineStr"/>
+      <c r="O112" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6819,31 +7552,36 @@
           <t>拒絕/timeout 不落成功帳；重送至多一筆收款與憑證；dispute 建立可稽核例外且不以重複扣款恢復</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G113" s="4" t="inlineStr">
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H113" s="5" t="inlineStr">
+      <c r="I113" s="5" t="inlineStr">
         <is>
           <t>FR-API-10</t>
         </is>
       </c>
-      <c r="I113" s="5" t="inlineStr">
+      <c r="J113" s="5" t="inlineStr">
         <is>
           <t>SC-08</t>
         </is>
       </c>
-      <c r="J113" s="6" t="inlineStr"/>
       <c r="K113" s="6" t="inlineStr"/>
       <c r="L113" s="6" t="inlineStr"/>
       <c r="M113" s="6" t="inlineStr"/>
-      <c r="N113" s="5" t="inlineStr">
+      <c r="N113" s="6" t="inlineStr"/>
+      <c r="O113" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6875,31 +7613,36 @@
           <t>只呈現白名單路徑或安全導向；不得把非本站頁面當已授權內容載入</t>
         </is>
       </c>
-      <c r="F114" s="4" t="inlineStr">
+      <c r="F114" s="5" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="G114" s="4" t="inlineStr">
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H114" s="5" t="inlineStr">
+      <c r="I114" s="5" t="inlineStr">
         <is>
           <t>FR-WEB-01</t>
         </is>
       </c>
-      <c r="I114" s="5" t="inlineStr">
+      <c r="J114" s="5" t="inlineStr">
         <is>
           <t>SC-12、SC-17</t>
         </is>
       </c>
-      <c r="J114" s="6" t="inlineStr"/>
       <c r="K114" s="6" t="inlineStr"/>
       <c r="L114" s="6" t="inlineStr"/>
       <c r="M114" s="6" t="inlineStr"/>
-      <c r="N114" s="5" t="inlineStr">
+      <c r="N114" s="6" t="inlineStr"/>
+      <c r="O114" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6931,31 +7674,36 @@
           <t>數字、時區與篩選一致；低權角色 403；失敗時不顯示舊租戶資料</t>
         </is>
       </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G115" s="4" t="inlineStr">
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H115" s="5" t="inlineStr">
+      <c r="I115" s="5" t="inlineStr">
         <is>
           <t>FR-WEB-04</t>
         </is>
       </c>
-      <c r="I115" s="5" t="inlineStr">
+      <c r="J115" s="5" t="inlineStr">
         <is>
           <t>SC-08、SC-09</t>
         </is>
       </c>
-      <c r="J115" s="6" t="inlineStr"/>
       <c r="K115" s="6" t="inlineStr"/>
       <c r="L115" s="6" t="inlineStr"/>
       <c r="M115" s="6" t="inlineStr"/>
-      <c r="N115" s="5" t="inlineStr">
+      <c r="N115" s="6" t="inlineStr"/>
+      <c r="O115" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6987,31 +7735,36 @@
           <t>critical a11y=0；焦點、錯誤與對比可用；斷網不靜默遺失表單</t>
         </is>
       </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>boundary+recovery</t>
-        </is>
-      </c>
-      <c r="G116" s="4" t="inlineStr">
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>recovery＋boundary</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H116" s="5" t="inlineStr">
+      <c r="I116" s="5" t="inlineStr">
         <is>
           <t>NFR-A11y-001、NFR-A11y-003、NFR-A11y-004、NFR-A11y-005</t>
         </is>
       </c>
-      <c r="I116" s="5" t="inlineStr">
+      <c r="J116" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J116" s="6" t="inlineStr"/>
       <c r="K116" s="6" t="inlineStr"/>
       <c r="L116" s="6" t="inlineStr"/>
       <c r="M116" s="6" t="inlineStr"/>
-      <c r="N116" s="5" t="inlineStr">
+      <c r="N116" s="6" t="inlineStr"/>
+      <c r="O116" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7043,31 +7796,36 @@
           <t>actor、原因、版本、trace 與 hash 可還原；竄改被驗出；匯出受權限、tenant 與遮罩控制</t>
         </is>
       </c>
-      <c r="F117" s="4" t="inlineStr">
+      <c r="F117" s="5" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="G117" s="4" t="inlineStr">
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H117" s="5" t="inlineStr">
+      <c r="I117" s="5" t="inlineStr">
         <is>
           <t>NFR-Aud-002、NFR-Aud-003、NFR-Aud-005、NFR-Aud-006、NFR-Aud-007</t>
         </is>
       </c>
-      <c r="I117" s="5" t="inlineStr">
+      <c r="J117" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J117" s="6" t="inlineStr"/>
       <c r="K117" s="6" t="inlineStr"/>
       <c r="L117" s="6" t="inlineStr"/>
       <c r="M117" s="6" t="inlineStr"/>
-      <c r="N117" s="5" t="inlineStr">
+      <c r="N117" s="6" t="inlineStr"/>
+      <c r="O117" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7099,31 +7857,36 @@
           <t>各故障走 NFR 指定 fail-closed/降級/重試/DLQ；告警可收到；復原後不重複副作用</t>
         </is>
       </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G118" s="4" t="inlineStr">
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H118" s="5" t="inlineStr">
+      <c r="I118" s="5" t="inlineStr">
         <is>
           <t>NFR-Avail-001、NFR-Avail-002、NFR-Avail-003、NFR-Avail-004、NFR-Avail-005、NFR-Avail-006、NFR-Avail-007、NFR-Avail-008、NFR-Avail-009、NFR-Avail-011</t>
         </is>
       </c>
-      <c r="I118" s="5" t="inlineStr">
+      <c r="J118" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J118" s="6" t="inlineStr"/>
       <c r="K118" s="6" t="inlineStr"/>
       <c r="L118" s="6" t="inlineStr"/>
       <c r="M118" s="6" t="inlineStr"/>
-      <c r="N118" s="5" t="inlineStr">
+      <c r="N118" s="6" t="inlineStr"/>
+      <c r="O118" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7155,31 +7918,36 @@
           <t>四項 DORA 指標可計算且來源一致；rollback 不遺失 migration/audit 證據</t>
         </is>
       </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G119" s="4" t="inlineStr">
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H119" s="5" t="inlineStr">
+      <c r="I119" s="5" t="inlineStr">
         <is>
           <t>NFR-DORA-001、NFR-DORA-002、NFR-DORA-003</t>
         </is>
       </c>
-      <c r="I119" s="5" t="inlineStr">
+      <c r="J119" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J119" s="6" t="inlineStr"/>
       <c r="K119" s="6" t="inlineStr"/>
       <c r="L119" s="6" t="inlineStr"/>
       <c r="M119" s="6" t="inlineStr"/>
-      <c r="N119" s="5" t="inlineStr">
+      <c r="N119" s="6" t="inlineStr"/>
+      <c r="O119" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7211,31 +7979,36 @@
           <t>Python 覆寫不可信 provenance；核可率與誤放率可計算入報表</t>
         </is>
       </c>
-      <c r="F120" s="4" t="inlineStr">
+      <c r="F120" s="5" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="G120" s="4" t="inlineStr">
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H120" s="5" t="inlineStr">
+      <c r="I120" s="5" t="inlineStr">
         <is>
           <t>NFR-DQ-002、NFR-DQ-004</t>
         </is>
       </c>
-      <c r="I120" s="5" t="inlineStr">
+      <c r="J120" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J120" s="6" t="inlineStr"/>
       <c r="K120" s="6" t="inlineStr"/>
       <c r="L120" s="6" t="inlineStr"/>
       <c r="M120" s="6" t="inlineStr"/>
-      <c r="N120" s="5" t="inlineStr">
+      <c r="N120" s="6" t="inlineStr"/>
+      <c r="O120" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7267,31 +8040,36 @@
           <t>CI 在違規處失敗；契約與 ADR/DR 可回查；關鍵流程 E2E 可重跑</t>
         </is>
       </c>
-      <c r="F121" s="4" t="inlineStr">
+      <c r="F121" s="5" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="G121" s="4" t="inlineStr">
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H121" s="5" t="inlineStr">
+      <c r="I121" s="5" t="inlineStr">
         <is>
           <t>NFR-Maint-001、NFR-Maint-002、NFR-Maint-003、NFR-Maint-004、NFR-Maint-005、NFR-Maint-006、NFR-Maint-007、NFR-Maint-008</t>
         </is>
       </c>
-      <c r="I121" s="5" t="inlineStr">
+      <c r="J121" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J121" s="6" t="inlineStr"/>
       <c r="K121" s="6" t="inlineStr"/>
       <c r="L121" s="6" t="inlineStr"/>
       <c r="M121" s="6" t="inlineStr"/>
-      <c r="N121" s="5" t="inlineStr">
+      <c r="N121" s="6" t="inlineStr"/>
+      <c r="O121" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7323,31 +8101,36 @@
           <t>trace 可串接；PII 不外送；dashboard/alert 顯示正確維度與 recovery 狀態</t>
         </is>
       </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G122" s="4" t="inlineStr">
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H122" s="5" t="inlineStr">
+      <c r="I122" s="5" t="inlineStr">
         <is>
           <t>NFR-Obs-001、NFR-Obs-002、NFR-Obs-003、NFR-Obs-004、NFR-Obs-005</t>
         </is>
       </c>
-      <c r="I122" s="5" t="inlineStr">
+      <c r="J122" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J122" s="6" t="inlineStr"/>
       <c r="K122" s="6" t="inlineStr"/>
       <c r="L122" s="6" t="inlineStr"/>
       <c r="M122" s="6" t="inlineStr"/>
-      <c r="N122" s="5" t="inlineStr">
+      <c r="N122" s="6" t="inlineStr"/>
+      <c r="O122" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7379,31 +8162,36 @@
           <t>未核可零落地；更新 append-only；同源檢查失敗即阻擋；跨租戶 default deny</t>
         </is>
       </c>
-      <c r="F123" s="4" t="inlineStr">
+      <c r="F123" s="5" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="G123" s="4" t="inlineStr">
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H123" s="5" t="inlineStr">
+      <c r="I123" s="5" t="inlineStr">
         <is>
           <t>NFR-PUB-001、NFR-PUB-002、NFR-PUB-003、NFR-PUB-004</t>
         </is>
       </c>
-      <c r="I123" s="5" t="inlineStr">
+      <c r="J123" s="5" t="inlineStr">
         <is>
           <t>SC-15</t>
         </is>
       </c>
-      <c r="J123" s="6" t="inlineStr"/>
       <c r="K123" s="6" t="inlineStr"/>
       <c r="L123" s="6" t="inlineStr"/>
       <c r="M123" s="6" t="inlineStr"/>
-      <c r="N123" s="5" t="inlineStr">
+      <c r="N123" s="6" t="inlineStr"/>
+      <c r="O123" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -7435,31 +8223,36 @@
           <t>保存 p95/p99、錯誤率與降級行為；超門檻或資料不足一律 Fail/Blocked，不以估計值通過</t>
         </is>
       </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G124" s="4" t="inlineStr">
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H124" s="5" t="inlineStr">
+      <c r="I124" s="5" t="inlineStr">
         <is>
           <t>NFR-Perf-001、NFR-Perf-002、NFR-Perf-003、NFR-Perf-004、NFR-Perf-005、NFR-Perf-006、NFR-Perf-007、NFR-Perf-008、NFR-Perf-010、NFR-Perf-011、NFR-Perf-012</t>
         </is>
       </c>
-      <c r="I124" s="5" t="inlineStr">
+      <c r="J124" s="5" t="inlineStr">
         <is>
           <t>SC-01、SC-05、SC-18</t>
         </is>
       </c>
-      <c r="J124" s="6" t="inlineStr"/>
       <c r="K124" s="6" t="inlineStr"/>
       <c r="L124" s="6" t="inlineStr"/>
       <c r="M124" s="6" t="inlineStr"/>
-      <c r="N124" s="5" t="inlineStr">
+      <c r="N124" s="6" t="inlineStr"/>
+      <c r="O124" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -7491,31 +8284,36 @@
           <t>加密/遮罩/最小權限生效；legal hold 阻止刪除；保留期限與第三方處理可稽核</t>
         </is>
       </c>
-      <c r="F125" s="4" t="inlineStr">
+      <c r="F125" s="5" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="G125" s="4" t="inlineStr">
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H125" s="5" t="inlineStr">
+      <c r="I125" s="5" t="inlineStr">
         <is>
           <t>NFR-Priv-001、NFR-Priv-002、NFR-Priv-003、NFR-Priv-004、NFR-Priv-007、NFR-Priv-009、NFR-Priv-010</t>
         </is>
       </c>
-      <c r="I125" s="5" t="inlineStr">
+      <c r="J125" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J125" s="6" t="inlineStr"/>
       <c r="K125" s="6" t="inlineStr"/>
       <c r="L125" s="6" t="inlineStr"/>
       <c r="M125" s="6" t="inlineStr"/>
-      <c r="N125" s="5" t="inlineStr">
+      <c r="N125" s="6" t="inlineStr"/>
+      <c r="O125" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7547,31 +8345,36 @@
           <t>不遺失案件、不重複副作用；真承諾一定有 escalation/問題卡；恢復後可對帳</t>
         </is>
       </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G126" s="4" t="inlineStr">
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H126" s="5" t="inlineStr">
+      <c r="I126" s="5" t="inlineStr">
         <is>
           <t>NFR-Rel-001、NFR-Rel-002、NFR-Rel-003</t>
         </is>
       </c>
-      <c r="I126" s="5" t="inlineStr">
+      <c r="J126" s="5" t="inlineStr">
         <is>
           <t>SC-02、SC-03</t>
         </is>
       </c>
-      <c r="J126" s="6" t="inlineStr"/>
       <c r="K126" s="6" t="inlineStr"/>
       <c r="L126" s="6" t="inlineStr"/>
       <c r="M126" s="6" t="inlineStr"/>
-      <c r="N126" s="5" t="inlineStr">
+      <c r="N126" s="6" t="inlineStr"/>
+      <c r="O126" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -7603,31 +8406,36 @@
           <t>相同輸入產同結構結果；保存不足時明確阻擋並保留稽核</t>
         </is>
       </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G127" s="4" t="inlineStr">
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H127" s="5" t="inlineStr">
+      <c r="I127" s="5" t="inlineStr">
         <is>
           <t>NFR-Rep-001、NFR-Rep-002</t>
         </is>
       </c>
-      <c r="I127" s="5" t="inlineStr">
+      <c r="J127" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J127" s="6" t="inlineStr"/>
       <c r="K127" s="6" t="inlineStr"/>
       <c r="L127" s="6" t="inlineStr"/>
       <c r="M127" s="6" t="inlineStr"/>
-      <c r="N127" s="5" t="inlineStr">
+      <c r="N127" s="6" t="inlineStr"/>
+      <c r="O127" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7659,31 +8467,36 @@
           <t>邊界判定正確；標紅、retry、email fallback 與升級鏈可觀測且不重複通知</t>
         </is>
       </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G128" s="4" t="inlineStr">
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H128" s="5" t="inlineStr">
+      <c r="I128" s="5" t="inlineStr">
         <is>
           <t>NFR-SLA-001、NFR-SLA-002、NFR-SLA-003</t>
         </is>
       </c>
-      <c r="I128" s="5" t="inlineStr">
+      <c r="J128" s="5" t="inlineStr">
         <is>
           <t>SC-05、SC-06</t>
         </is>
       </c>
-      <c r="J128" s="6" t="inlineStr"/>
       <c r="K128" s="6" t="inlineStr"/>
       <c r="L128" s="6" t="inlineStr"/>
       <c r="M128" s="6" t="inlineStr"/>
-      <c r="N128" s="5" t="inlineStr">
+      <c r="N128" s="6" t="inlineStr"/>
+      <c r="O128" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -7715,31 +8528,36 @@
           <t>容量指標、限流與降級符合 NFR；無跨租戶事件、雙重排程或無聲遺失</t>
         </is>
       </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G129" s="4" t="inlineStr">
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H129" s="5" t="inlineStr">
+      <c r="I129" s="5" t="inlineStr">
         <is>
           <t>NFR-Scal-003、NFR-Scal-004、NFR-Scal-005、NFR-Scal-006、NFR-Scal-007、NFR-Scal-008</t>
         </is>
       </c>
-      <c r="I129" s="5" t="inlineStr">
+      <c r="J129" s="5" t="inlineStr">
         <is>
           <t>SC-05</t>
         </is>
       </c>
-      <c r="J129" s="6" t="inlineStr"/>
       <c r="K129" s="6" t="inlineStr"/>
       <c r="L129" s="6" t="inlineStr"/>
       <c r="M129" s="6" t="inlineStr"/>
-      <c r="N129" s="5" t="inlineStr">
+      <c r="N129" s="6" t="inlineStr"/>
+      <c r="O129" s="5" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -7771,31 +8589,36 @@
           <t>migrations 可重套、drift 被擋、只允許 forward 演進；備份/還原證據可回查</t>
         </is>
       </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>failure+recovery</t>
-        </is>
-      </c>
-      <c r="G130" s="4" t="inlineStr">
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>failure＋recovery</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H130" s="5" t="inlineStr">
+      <c r="I130" s="5" t="inlineStr">
         <is>
           <t>NFR-Sch-001、NFR-Sch-003</t>
         </is>
       </c>
-      <c r="I130" s="5" t="inlineStr">
+      <c r="J130" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J130" s="6" t="inlineStr"/>
       <c r="K130" s="6" t="inlineStr"/>
       <c r="L130" s="6" t="inlineStr"/>
       <c r="M130" s="6" t="inlineStr"/>
-      <c r="N130" s="5" t="inlineStr">
+      <c r="N130" s="6" t="inlineStr"/>
+      <c r="O130" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7827,40 +8650,45 @@
           <t>未授權與違規輸出 fail-closed；secret/CVE 在時限內告警與追蹤；無敏感副作用</t>
         </is>
       </c>
-      <c r="F131" s="4" t="inlineStr">
+      <c r="F131" s="5" t="inlineStr">
         <is>
           <t>failure</t>
         </is>
       </c>
-      <c r="G131" s="4" t="inlineStr">
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H131" s="5" t="inlineStr">
+      <c r="I131" s="5" t="inlineStr">
         <is>
           <t>NFR-Sec-001、NFR-Sec-002、NFR-Sec-004、NFR-Sec-007、NFR-Sec-013、NFR-Sec-014</t>
         </is>
       </c>
-      <c r="I131" s="5" t="inlineStr">
+      <c r="J131" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J131" s="6" t="inlineStr"/>
       <c r="K131" s="6" t="inlineStr"/>
       <c r="L131" s="6" t="inlineStr"/>
       <c r="M131" s="6" t="inlineStr"/>
-      <c r="N131" s="5" t="inlineStr">
+      <c r="N131" s="6" t="inlineStr"/>
+      <c r="O131" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N131"/>
+  <autoFilter ref="A1:O131"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="只能填 Pass/Fail/Blocked/N/A" type="list">
+    <dataValidation sqref="K2:K131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="只能填 Pass/Fail/Blocked/N/A" type="list">
       <formula1>"Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_整合測試計畫.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_整合測試計畫.xlsx
@@ -11,11 +11,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② 測試案例主表" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 需求覆蓋（需求 × 案例）" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④ 旅程驗收腳本" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤ UAT 走查腳本（UAT-01–UAT-09）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 測試案例主表'!$A$1:$O$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 需求覆蓋（需求 × 案例）'!$A$1:$I$172</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'④ 旅程驗收腳本'!$A$1:$K$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'⑤ UAT 走查腳本（UAT-01–UAT-09）'!$A$1:$K$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -55,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -102,6 +104,11 @@
         <fgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -129,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -166,6 +173,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -532,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -571,145 +581,257 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>② 是可執行清單：篩優先級與章節 → 逐列跑 → 在黃色欄填結果、日期、缺陷單。③ 回答「這條需求測夠了沒」，④ 回答「這條旅程驗得完嗎」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>② 是可執行清單：篩優先級與章節 → 逐列跑 → 在黃色欄填結果、日期、缺陷單。③ 回答「這條需求測夠了沒」，④ 回答「這條旅程驗得完嗎」，⑤ 是 UAT 當天照著走的腳本。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
+          <t>④ 與 ⑤ 差在哪（最常被搞混）</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>④ 一列一條旅程（SC），是「簽核的單位」——19 條旅程各自算過或不過，在 Plane 也各自是一條 Test Run。⑤ 一列一場走查（UAT-01–UAT-09），是「執行的單位」——UAT 當天照著一支腳本從頭走到尾，一場會跑完 1–4 條旅程。兩者多對一，誰也取代不了誰：只有 ⑤ 答不出「自助解決那段到底過了沒」，只有 ④ 則沒人知道當天要怎麼走。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
           <t>兩層測什麼不一樣</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>旅程測「順不順」——整條走得完、接縫不掉；需求測「對不對」——單一性質恆常成立。兩層都要，缺一邊的測試計畫都會在 UAT 前兩週爆炸。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="1" t="inlineStr">
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>③ 的 kind 欄是重點</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>happy / boundary / failure / recovery。只有 happy 的需求等於沒測——訪談只問 1–4 題（不問「什麼情況算失敗」）產出的規格就長這樣。P0 旅程的需求若缺 failure/recovery，會在該列標紅並進規劃書缺口清單（V10）。</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>② 的「路徑類型」與「驗證面向」為什麼分兩欄</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>它們是正交的兩件事：路徑＝這個案例走哪條路（happy / failure / boundary / recovery / timeout / 例外 / 狀態轉移），面向＝它在驗哪一種性質（功能 / 權限 / 非功能 / 冪等）。一條功能需求的驗收條件完全可能包含一個效能門檻——用同一欄表達兩件事，篩「所有失敗路徑」時就會漏掉標成「權限」的那些。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>為什麼有 52 條標「⚠ 未標註」</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>那些案例的原始 kind 要嘛空白、要嘛只寫了面向（例如只寫「權限」而沒說走哪條路）。不填預設值是刻意的——把它們預設成 happy 會讓「這條需求只測了正常路徑」這個真正的缺口消失。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>④ 的缺口怎麼讀</t>
+          <t>為什麼有 52 條標「⚠ 未標註」</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>V9＝這條旅程宣告需要某需求，但它的 UAT 腳本沒跑到任何驗證該需求的案例。這是規格治理裡最容易漏報的狀態：在只有一欄「對應場景」的表裡，它永遠不會現形。</t>
+          <t>那些案例的原始 kind 要嘛空白、要嘛只寫了面向（例如只寫「權限」而沒說走哪條路）。不填預設值是刻意的——把它們預設成 happy 會讓「這條需求只測了正常路徑」這個真正的缺口消失。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>④ 的缺口怎麼讀</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>V9＝這條旅程宣告需要某需求，但它的 UAT 腳本沒跑到任何驗證該需求的案例。這是規格治理裡最容易漏報的狀態：在只有一欄「對應場景」的表裡，它永遠不會現形。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
           <t>scope: global 的需求</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>可用性、稽核鏈、安全矩陣、migration 可重現、效能降級沒有客戶旅程，不會出現在業務端的驗收控制表，但 QA 一樣要測——它們在 ③ 標成「全域地板」。</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="1" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr"/>
-    </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Plane 詞彙對照</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>本書的列在 Plane 專案管理系統裡叫什麼（依《Plane QA 工程守則》Part B）。跨系統討論一律用右欄的名字——同一件事兩個名字，是對帳失敗最常見的起點。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  驗收契約</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Plane 的 Test Case。守則把 FR／驗收條件／BDD／測試案例壓成「同一個物件」——案例就是驗收條件，省掉一整層追蹤。所以本書講「案例」與講「契約」是同一件事。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  驗收腳本 ＝ 一條旅程一條</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>本欄就是這條 SC 在 Plane 的 Test Run（19 條 SC＝19 條 run），內容是該 SC 宣告的那批案例。建立 run 時把每張案例釘在當時的版本，所以舊紀錄不會被日後改版影響。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  括號裡的 UAT-01…UAT-09</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>22_UAT_Report §4 的走查腳本編號，是「旅程的上層分組」：一支走查涵蓋 1–4 條旅程（UAT-01 撐 SC-01/02/03、UAT-02 撐 SC-04–07）。它回答「這次 UAT 要走哪條路線」，而旅程回答「路線裡的這一段」。⚠️ 它在 Plane 沒有對應物件，只被寫進 run 名稱當註記。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  標「不走 UAT 走查」的旅程</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>那條旅程宣告 uat: null——它一樣有自己的 run 與案例，只是不掛在任何一支走查腳本下。月結 cron、七帳本對帳這類後端受控驗收沒有人能「走一遍」給你看，硬編一支走查腳本只是造假。它不是缺口，V9 也不會報它；空著不寫才會跟「漏填」混在一起。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  執行結果</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Plane 的 Test Result。「只增不改」——重測是新增一筆，不覆寫前次失敗。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  缺陷</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Plane 的 Defect＝一張真的 work item，不是測試系統的內部物件；它回到拆解軸走一般流程，這也是整條鏈閉環的地方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ③ 的 kind 欄 ＝ DoR</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>守則的 Definition of Ready：一條 Story 不算 ready，除非至少連結一個 happy path 與一個 unhappy path 的契約。③ 的「涵蓋 kind」就是這條的檢查，V10 是它的告警。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="1" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>黃色欄位</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>只有人能填。系統不會、也不該幫你填。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>灰色欄位</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>生成欄，手改會在下次重跑被覆蓋。要改請改上游 Markdown 或 _relations/*.yaml。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>白色欄位</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>正典敘述，同樣改上游。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="1" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="1" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>四個狀態軸不得互推</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>程式檔存在 ≠ 工程完成；工程完成 ≠ 測試通過；測試通過 ≠ 驗收通過。需求定版(SA) / 工程證據(RD) / 測試執行(QA) / 驗收通過(業務 Owner) 各有唯一 owner，任何一格都不得由另一軸自動帶出。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>怎麼重生</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>改上游正典 → 在 規格統控整理/ 跑 python3 _build_workbooks.py。xlsx 是單向快照，永遠不要直接改 xlsx 再往回抄。</t>
         </is>
@@ -814,7 +936,7 @@
       </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
-          <t>缺陷單 / 備註</t>
+          <t>缺陷（Defect）/ 備註</t>
         </is>
       </c>
       <c r="O1" s="3" t="inlineStr">
@@ -8754,7 +8876,7 @@
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>指定案例</t>
+          <t>指定契約（TestCase）</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
@@ -15792,7 +15914,7 @@
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="56" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
@@ -15820,7 +15942,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>UAT 腳本</t>
+          <t>UAT 走查腳本</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -15877,7 +15999,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>UAT-01</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
@@ -15887,7 +16009,7 @@
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>S1 步驟 1、3——自助回答、紅線與去重；含 Turn SAVE、記憶/工具拒絕及首回應/RAG 壓測的可觀測抽驗</t>
+          <t>UAT-01 步驟 1、3——自助回答、紅線與去重；含 Turn SAVE、記憶/工具拒絕及首回應/RAG 壓測的可觀測抽驗</t>
         </is>
       </c>
       <c r="G2" s="5" t="n">
@@ -15920,7 +16042,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>UAT-01</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -15930,7 +16052,7 @@
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>S1 步驟 2——追問後轉真人與草擬卡；含 internal ingest、記憶隔離、工作台可見性及中斷重送</t>
+          <t>UAT-01 步驟 2——追問後轉真人與草擬卡；含 internal ingest、記憶隔離、工作台可見性及中斷重送</t>
         </is>
       </c>
       <c r="G3" s="5" t="n">
@@ -15963,7 +16085,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>UAT-01</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -15973,7 +16095,7 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>S1 驗收點「負面情緒被識別並升級」＋急件建單、4h 補審與重送不蒸發</t>
+          <t>UAT-01 驗收點「負面情緒被識別並升級」＋急件建單、4h 補審與重送不蒸發</t>
         </is>
       </c>
       <c r="G4" s="5" t="n">
@@ -16006,7 +16128,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>UAT-02</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -16016,7 +16138,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>S2 步驟 1-2——補齊卡→確認→報價內外雙視圖→客戶 LIFF 確認；缺地址與未確認報價須被擋</t>
+          <t>UAT-02 步驟 1-2——補齊卡→確認→報價內外雙視圖→客戶 LIFF 確認；缺地址與未確認報價須被擋</t>
         </is>
       </c>
       <c r="G5" s="5" t="n">
@@ -16049,7 +16171,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>UAT-02</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -16059,7 +16181,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>S2 步驟 3——自動媒合 + 手動 override + 接單/逾時；含候選池空、通知恢復、投影、效能與容量抽驗</t>
+          <t>UAT-02 步驟 3——自動媒合 + 手動 override + 接單/逾時；含候選池空、通知恢復、投影、效能與容量抽驗</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
@@ -16092,7 +16214,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>UAT-02</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -16102,7 +16224,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>S2 步驟 5——完工硬閘三種缺件各擋一次，補齊後通過，主管 override、取消費、技師投影與 SLA 留痕</t>
+          <t>UAT-02 步驟 5——完工硬閘三種缺件各擋一次，補齊後通過，主管 override、取消費、技師投影與 SLA 留痕</t>
         </is>
       </c>
       <c r="G7" s="5" t="n">
@@ -16135,7 +16257,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>UAT-02</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -16145,7 +16267,7 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>S2 步驟 4——現場加價三檔位各走一遍；requote 由技師端發起且不含金額</t>
+          <t>UAT-02 步驟 4——現場加價三檔位各走一遍；requote 由技師端發起且不含金額</t>
         </is>
       </c>
       <c r="G8" s="5" t="n">
@@ -16178,7 +16300,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>UAT-04</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -16188,7 +16310,7 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>S4 步驟 2-3——退款雙簽同人被擋、額度分層升級、各階段取消費點測</t>
+          <t>UAT-04 步驟 2-3——退款雙簽同人被擋、額度分層升級、各階段取消費點測</t>
         </is>
       </c>
       <c r="G9" s="5" t="n">
@@ -16219,7 +16341,11 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>不走走查</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
           <t>TC-SETTLE-01、TC-SETTLE-02、TC-EXC-01、TC-WEB-REPORT-01</t>
@@ -16260,7 +16386,7 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>UAT-06</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -16270,7 +16396,7 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>S6——接管後 AI 靜音、雙方訊息全量入庫；旗標/寫入故障不得讓案件蒸發</t>
+          <t>UAT-06——接管後 AI 靜音、雙方訊息全量入庫；旗標/寫入故障不得讓案件蒸發</t>
         </is>
       </c>
       <c r="G11" s="5" t="n">
@@ -16303,7 +16429,7 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>UAT-04</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -16313,7 +16439,7 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>S4 步驟 2 的 SoD 面；含逾期排程、越權拒絕及可匯出的裁決稽核</t>
+          <t>UAT-04 步驟 2 的 SoD 面；含逾期排程、越權拒絕及可匯出的裁決稽核</t>
         </is>
       </c>
       <c r="G12" s="5" t="n">
@@ -16346,7 +16472,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>UAT-07</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
@@ -16356,7 +16482,7 @@
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>S7——技師身分、KYC、品牌授權與候選池隔離的准入閘門</t>
+          <t>UAT-07——技師身分、KYC、品牌授權與候選池隔離的准入閘門</t>
         </is>
       </c>
       <c r="G13" s="5" t="n">
@@ -16387,7 +16513,11 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="D14" s="10" t="n"/>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>不走走查</t>
+        </is>
+      </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
           <t>TC-SETTLE-08、TC-EXC-06、TC-DISPATCH-05</t>
@@ -16428,7 +16558,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>UAT-08</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -16438,7 +16568,7 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>S8——撤銷事件跨品牌傳播、候選池排除與進行中工單改派</t>
+          <t>UAT-08——撤銷事件跨品牌傳播、候選池排除與進行中工單改派</t>
         </is>
       </c>
       <c r="G15" s="5" t="n">
@@ -16471,7 +16601,7 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>UAT-03</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -16481,7 +16611,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>S3 步驟 1–3——bronze 來源、分流、核可 gate、雙路發布及發布後檢索效果</t>
+          <t>UAT-03 步驟 1–3——bronze 來源、分流、核可 gate、雙路發布及發布後檢索效果</t>
         </is>
       </c>
       <c r="G16" s="5" t="n">
@@ -16514,7 +16644,7 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>UAT-03</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
@@ -16524,7 +16654,7 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>S3 步驟 2——未經家族覆核、越權角色或跨租戶發布均必須失敗</t>
+          <t>UAT-03 步驟 2——未經家族覆核、越權角色或跨租戶發布均必須失敗</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
@@ -16557,7 +16687,7 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>UAT-09</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
@@ -16567,7 +16697,7 @@
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>S9——品牌申請、建庫、License、LINE 綁定與 portal 開通的可重跑流程</t>
+          <t>UAT-09——品牌申請、建庫、License、LINE 綁定與 portal 開通的可重跑流程</t>
         </is>
       </c>
       <c r="G18" s="5" t="n">
@@ -16600,7 +16730,7 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>UAT-05</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -16610,7 +16740,7 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>S5 步驟 1–3——DSL/config 的治理、受保護層拒絕、版本化、可觀測回滾與稽核</t>
+          <t>UAT-05 步驟 1–3——DSL/config 的治理、受保護層拒絕、版本化、可觀測回滾與稽核</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
@@ -16643,7 +16773,7 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>UAT-04</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -16653,7 +16783,7 @@
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>S4 步驟 1、4——軟刪即時、T+30 硬刪、legal-hold 拒絕、稽核匯出與 hash 驗證</t>
+          <t>UAT-04 步驟 1、4——軟刪即時、T+30 硬刪、legal-hold 拒絕、稽核匯出與 hash 驗證</t>
         </is>
       </c>
       <c r="G20" s="5" t="n">
@@ -16677,4 +16807,495 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="78" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>走查腳本</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>涵蓋旅程</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>旅程數</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>案例數</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>步驟（逐項勾選）</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>驗收點</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>走查結果</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>執行日</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>主持人</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>異常紀錄</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>UAT-01</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>消費者 LINE 自助 →（必要時）轉真人</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>SC-01、SC-02、SC-03</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. 消費者加官方帳號，詢問產品知識（如換電池）→ AI 依知識庫正確回答，不建卡。
+2. 回報故障並要求派師傅 → AI 追問品牌/型號 → 觸發轉真人 → 後台出現 AI 草擬卡（badge + 待補欄位）。
+3. 詢價誘導 → AI 不給確定金額、轉真人。</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>回答準確、紅線零違反、卡片欄位與對話事實一致、負面情緒訊息被識別並升級。</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr"/>
+      <c r="I2" s="6" t="inlineStr"/>
+      <c r="J2" s="6" t="inlineStr"/>
+      <c r="K2" s="6" t="inlineStr"/>
+    </row>
+    <row r="3" ht="86" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>UAT-02</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>派工 → 報價確認 → 現場 → 完工</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>SC-04、SC-05、SC-06、SC-07</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 客服補齊草擬卡（品牌/型號/地址）→ confirm → 轉工單（缺地址須被擋）。
+2. 建報價 → 內部核准 → 客戶 LIFF 確認（客戶端不見成本欄）。
+3. 派工（自動媒合 + 手動 override）→ 師傅 web 接單 → 到場簽到。
+4. 現場加價各檔位走一遍（≤500 自確 / 501–2000 客戶 LIFF / &gt;2000 主管覆核）。
+5. 完工硬閘：照片不足/無簽名/安裝缺 serial 均被擋；補齊後通過；主管 override 留痕。</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>狀態機每步正確、金額正確、Evidence 角色可見性正確（品牌角色不見客戶環境照且 404 不洩存在性）。</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr"/>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr"/>
+      <c r="K3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>UAT-03</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>SOP 知識螺旋（HITL）</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>SC-15、SC-16</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 由客服回饋觸發 SOP draft → 雙人審核 → 家族覆核 → 發布。
+2. 未經家族覆核嘗試發布 → 必須失敗。
+3. 發布後 agent 行為更新生效；事實 chunk 灌入語料。</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>未核可零落地；覆核率 100%；ledger 不可篡改。</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr"/>
+      <c r="K4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="72" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>UAT-04</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>合規稽核（GDPR / 退款 / 取消）</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>SC-08、SC-11、SC-19</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 客戶提 GDPR forget → 軟刪即時 → 觀察 T+30 硬刪排程；legal-hold 案拒絕 + 通知。
+2. 退款雙簽：同人連簽被擋（403 SOD_VIOLATION）；額度分層升級正確。
+3. 各階段取消費點測，金額與費率表一致；主管 override 留 reason。
+4. 稽核匯出：audit-events 查詢/匯出 tenant-scoped。</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>法務/DPO 簽核；金額零錯帳。</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
+      <c r="K5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>UAT-05</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>品牌自助配置（Agent Studio / config 治理）</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>SC-18</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. 租戶 Admin 於後台調整領域配置（費率/文案/skill 客製層）→ 版本化 + 審核 → 生效。
+2. 受保護層（escalation / domain-safety）嘗試 override → 被擋。
+3. 一鍵 rollback → ≤1min 內回前版；audit 完整。</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>配置變更不需改碼、回滾即時、非 owner 角色不可改。</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>UAT-06</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>人工接管與對話不蒸發</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>SC-10</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 客戶完成 escalation 後，小編從派工工作台接管；持續由客戶與小編雙向發訊息。
+2. 在每個 turn 前檢查 handover flag；接管期間注入旗標查詢 timeout、訊息寫入失敗與重送。
+3. 解除接管後再送一則一般問題，核對 AI 僅在已解除後回覆。</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>接管中 AI 零插話；客戶與人工訊息皆可依 sender_role 完整追溯；故障/重送不遺漏或重複對話，且 timeout 不阻斷客戶訊息。</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>UAT-07</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>技師註冊、KYC 到品牌授權</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>SC-12</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 新技師由技師 portal 註冊，填 profile、技能與服務品牌並上傳 KYC／認證文件。
+2. 分別以文件不齊、未核可、已核可未授權、已核可已授權狀態嘗試進入候選池與接單。
+3. 以另一品牌與 platform token 交叉檢查資料面及入口；重送註冊請求。</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>身分獨立於品牌租戶；僅核可且被品牌授權的技師可進正確候選池；越權一律拒絕；重送不建立重複身分或授權。</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>UAT-08</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>認證撤銷與停權即時廣播</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>SC-14</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 建立同一技師在兩品牌皆可派工、且其中一筆已接單的情境。
+2. 由平台撤銷認證與停權，觀察兩邊候選池、通知與進行中工單的改派；重送撤銷事件。
+3. 恢復身分後檢查未經重新核可/授權前不能自行回到候選池。</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>撤銷後所有品牌一致排除；既有工作有可追溯人工或自動承接；事件重送不重複通知，且無任一品牌仍派給已撤銷技師。</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>UAT-09</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>品牌申請到 License 開通上線</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>SC-17</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 於 landing 提交品牌申請，平台核准後執行建庫、組織／帳號建立、License 開通與 LINE sandbox 綁定。
+2. 在建庫與綁定兩個中間點刻意失敗後重跑 provisioning。
+3. 以新品牌、既有品牌與 platform 帳號登入／進線，檢查資料庫與 portal 邊界。</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>任一步未完成不得啟用 License；重跑冪等且留下 provisioning audit；新品牌僅能看到自身資料與入口，既有品牌不受影響。</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr"/>
+      <c r="K10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>不走 UAT 走查 —— 後端受控驗收，沒有人能「走一遍」給你看</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>受控驗收（月結 cron、帳本對帳等）</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>SC-09、SC-13</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>無走查步驟：這些旅程宣告 uat: null，改由各自的案例與證據直接判定。</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>案例全綠且證據齊備即可簽核；不因缺走查腳本而視為缺口（V9 不報）。</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+      <c r="K12" s="6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K12"/>
+  <mergeCells count="1">
+    <mergeCell ref="A11:K11"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="H2:H12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="只能填 Pass/Fail/Blocked/Not Run" type="list">
+      <formula1>"Pass,Fail,Blocked,Not Run"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_整合測試計畫.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_整合測試計畫.xlsx
@@ -20,6 +20,366 @@
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Codex</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Plane level 0。沒有確認的策略成果就留白。</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>同一 Epic ID 的名稱必須一致。</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Plane level 1，是 Story 的唯一 parent；不得由舊 SC 自動帶入。</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>以功能能力分組，不是測試情境或執行批次。</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Plane 的唯一直接量測點；沿用現有 FR/NFR 編號作穩定外部 ID。</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>一列一個可驗收的價值切片。</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>從舊業務旅程與 Persona 預填，由 PM/SA 確認。</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>說明為什麼要做；不寫技術解法。</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>功能用『作為…我需要…以便…』；品質需求可直寫業務保障，不強迫套句型。</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>匯入 Plane 時映射 Issue.requirement_kind=functional/quality。</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>FR 寫系統行為；NFR 寫場景、指標與目標值。</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>本次承諾的行為或品質邊界。</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>本版明確不做什麼。</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>P0/P1/P2/P3/未定；匯入時再映射 Plane priority。</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>負責價值、範圍與優先序。</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>負責規則清楚且可測。</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>只是需求軸；不得由 Task、TC 或簽核狀態自動推進。</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>只保留語意背景；SC 不再是 Feature、Test Run 或簽核單位。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Codex</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>AC 不是 Plane 獨立物件；匯入時收進 Story 敘述與 TC 追溯資訊。</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>必須存在於 01_需求收斂。</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>與 Story requirement_kind 一致。</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>只分驗收意圖；測試路徑在 04 另列。</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>來自 SRS/NFR 正典。</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>情境開始前必須成立什麼。</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>觸發行為，或 NFR 的量測方式與資料量。</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>明確的過／不過判準。</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>商業規則、邊界、拒絕或回復行為。</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>NFR 必填；FR 可留白。</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>NFR 必須可判定；沒數字就明寫本版不承諾。</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>在哪個環境、用什麼資料與量測點驗證。</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>負責可測表述。</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>確認這個結果是不是業務要的。</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>只顯示 TC 設計是否同時有正常與非正常路徑；不會自動推進需求狀態。</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>PM/SA/QA 對焦後才能選『是』，不由公式帶出。</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>舊 FR/NFR 文件行號；不是 Plane object。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Codex</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Plane level 3；確認後再建立。</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Task 只能有一個 Story parent；多候選必須先拆分。</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>從舊 WBS delivers 擷取，僅供人工選 parent。</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>工程師明天可以開工的切片；不重寫 Story 價值。</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>SD/DEV 實作 owner。</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>匯入前先讀 Plane project states，不在 Excel 猜 UUID。</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>時間箱，與 parent 無關。</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>能力切面，多值用 ; 分隔。</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>交付檢查點，單值 FK。</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>不可自指或形成循環。</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>完成 Task 的工程判準，不等於 TC passed 或業務驗收通過。</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>只保留 enabler/rebuild 候選；archive/merge 不重建為 Task。</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Story parent 唯一且內容重審後才可選『是』。</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>舊 WBS ID/狀態，不直接當 Plane state。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Codex</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Plane Test Case 外部穩定識別；建議放在 title 前綴與 tag。</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>用 ; 分隔；匯入時逐一建 TestCaseWorkItemLink。</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>需對應 02 中的 AC；舊資料為決定性草案 ID。</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>舊 TS 只當領域分組，不是 Test Scenario 物件。</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>回答『在什麼狀況下驗』；不含實際步驟與證據。</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>只有 happy/boundary/failure/recovery；多路徑的舊案例應拆分。</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>與路徑正交；回答這個案例在驗什麼性質。</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>具體帳號、狀態、環境與輸入資料。</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>可執行的具體步驟；不是業務旅程大綱。</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>每一步或案例結束時的可觀察判準。</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>P0/P1/P2/P3/未定。</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>負責測試設計；實際執行人與結果進 Plane。</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>只顯示關聯/路徑/面向/前置的設計問題。</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>人工確認後才能匯入。</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>舊 case kind/章節/文件行號；不包含舊 SC/UAT 物件。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -181,366 +541,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Codex</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Plane level 0。沒有確認的策略成果就留白。</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>同一 Epic ID 的名稱必須一致。</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>Plane level 1，是 Story 的唯一 parent；不得由舊 SC 自動帶入。</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>以功能能力分組，不是測試情境或執行批次。</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Plane 的唯一直接量測點；沿用現有 FR/NFR 編號作穩定外部 ID。</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>一列一個可驗收的價值切片。</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>從舊業務旅程與 Persona 預填，由 PM/SA 確認。</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>說明為什麼要做；不寫技術解法。</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>功能用『作為…我需要…以便…』；品質需求可直寫業務保障，不強迫套句型。</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>匯入 Plane 時映射 Issue.requirement_kind=functional/quality。</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>FR 寫系統行為；NFR 寫場景、指標與目標值。</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>本次承諾的行為或品質邊界。</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t>本版明確不做什麼。</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t>P0/P1/P2/P3/未定；匯入時再映射 Plane priority。</t>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
-      <text>
-        <t>負責價值、範圍與優先序。</t>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
-      <text>
-        <t>負責規則清楚且可測。</t>
-      </text>
-    </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
-      <text>
-        <t>只是需求軸；不得由 Task、TC 或簽核狀態自動推進。</t>
-      </text>
-    </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
-      <text>
-        <t>只保留語意背景；SC 不再是 Feature、Test Run 或簽核單位。</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Codex</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>AC 不是 Plane 獨立物件；匯入時收進 Story 敘述與 TC 追溯資訊。</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>必須存在於 01_需求收斂。</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>與 Story requirement_kind 一致。</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>只分驗收意圖；測試路徑在 04 另列。</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>來自 SRS/NFR 正典。</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>情境開始前必須成立什麼。</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>觸發行為，或 NFR 的量測方式與資料量。</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>明確的過／不過判準。</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>商業規則、邊界、拒絕或回復行為。</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>NFR 必填；FR 可留白。</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>NFR 必須可判定；沒數字就明寫本版不承諾。</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>在哪個環境、用什麼資料與量測點驗證。</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t>負責可測表述。</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t>確認這個結果是不是業務要的。</t>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
-      <text>
-        <t>只顯示 TC 設計是否同時有正常與非正常路徑；不會自動推進需求狀態。</t>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
-      <text>
-        <t>PM/SA/QA 對焦後才能選『是』，不由公式帶出。</t>
-      </text>
-    </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
-      <text>
-        <t>舊 FR/NFR 文件行號；不是 Plane object。</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Codex</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Plane level 3；確認後再建立。</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>Task 只能有一個 Story parent；多候選必須先拆分。</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>從舊 WBS delivers 擷取，僅供人工選 parent。</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>工程師明天可以開工的切片；不重寫 Story 價值。</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>SD/DEV 實作 owner。</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>匯入前先讀 Plane project states，不在 Excel 猜 UUID。</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>時間箱，與 parent 無關。</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>能力切面，多值用 ; 分隔。</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>交付檢查點，單值 FK。</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>不可自指或形成循環。</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>完成 Task 的工程判準，不等於 TC passed 或業務驗收通過。</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>只保留 enabler/rebuild 候選；archive/merge 不重建為 Task。</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t>Story parent 唯一且內容重審後才可選『是』。</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t>舊 WBS ID/狀態，不直接當 Plane state。</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Codex</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Plane Test Case 外部穩定識別；建議放在 title 前綴與 tag。</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>用 ; 分隔；匯入時逐一建 TestCaseWorkItemLink。</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>需對應 02 中的 AC；舊資料為決定性草案 ID。</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>舊 TS 只當領域分組，不是 Test Scenario 物件。</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>回答『在什麼狀況下驗』；不含實際步驟與證據。</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>只有 happy/boundary/failure/recovery；多路徑的舊案例應拆分。</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>與路徑正交；回答這個案例在驗什麼性質。</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>具體帳號、狀態、環境與輸入資料。</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>可執行的具體步驟；不是業務旅程大綱。</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>每一步或案例結束時的可觀察判準。</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>P0/P1/P2/P3/未定。</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>負責測試設計；實際執行人與結果進 Plane。</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t>只顯示關聯/路徑/面向/前置的設計問題。</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t>人工確認後才能匯入。</t>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
-      <text>
-        <t>舊 case kind/章節/文件行號；不包含舊 SC/UAT 物件。</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
